--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aeu.00037_19470820.7" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="aeu.00037_19470820.7" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,19 +581,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 70%) :: C Ã© cile Isabel, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.7.txt</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -935,12 +931,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -3881,7 +3877,7 @@
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | possible duplicated/overlap line with previous line (similarity 70%) :: C Ã© cile Isabel, Ã© cole consolidee, Falher</t>
+          <t>L336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: C Ã© cile Isabel, Ã© cole consolidee, Falher</t>
         </is>
       </c>
       <c r="K66" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.7.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="aeu.00037_19470820.7" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aeu.00037_19470820.7" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -604,21 +604,25 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
+          <t>L330: punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, écol eThibeault .........</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland B Ã© rub Ã©. Beaumont</t>
+          <t>L583: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Pierrette Soumis, Ã©cole Thibeault ......</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM](Suite de la page 6)</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM](Suite de la page 6)</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 80</t>
@@ -632,7 +636,7 @@
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Pierrette Soumis, Ã©cole Thibeault ......</t>
+          <t>L2: punctuation artifact: repeated periods :: Pierrette Soumis, école Thibeault ......</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -682,14 +686,10 @@
           <t>L388: punctuation artifact: repeated periods | suspicious token(s): 96I (letter/digit mix) :: ...96I</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Yolande Robert, Ã© cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Lapointe, Bonnyville ...........</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -707,13 +707,13 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Lapointe, Bonnyville ...........</t>
+          <t>L3: punctuation artifact: repeated periods :: Thérèse Lapointe, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L627: punctuation artifact: repeated periods | line starts with lowercase prefix glued to capitalized word | suspicious token(s): iJacques (odd internal casing) :: iJacques Gagnon, Bonnyville......................</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -757,14 +757,10 @@
           <t>L414: suspicious token(s): 94i (letter/digit mix) :: 94i</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© erard l'Abb, ecole consolidee, Falher</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bordeleau, Bonnyville ...........</t>
+          <t>L1877: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Victor Beaudry</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -782,11 +778,15 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bordeleau, Bonnyville ...........</t>
+          <t>L4: punctuation artifact: repeated periods :: Cécile Bordeleau, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L627: punctuation artifact: repeated periods | line starts with lowercase prefix glued to capitalized word | suspicious token(s): iJacques (odd internal casing) :: iJacques Gagnon, Bonnyville......................</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -802,19 +802,19 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>268</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>802</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | candidate OCR token mismatch vs other OCR: "ecole" vs "cole" :: LÃ©on Schayes, ecole Thibeault</t>
+          <t>L292: candidate OCR token mismatch vs other OCR: "ecole" vs "cole" :: Léon Schayes, ecole Thibeault</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr"/>
@@ -824,16 +824,8 @@
           <t>L436: punctuation artifact: repeated periods | suspicious token(s): 92I (letter/digit mix) :: ....92I</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claudette B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Cannelle Latour, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -853,7 +845,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1877: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Victor Beaudry</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -888,19 +884,11 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© erard Magnan, couvent Notre-Dame</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Beaudoin, Tangente ...............</t>
-        </is>
-      </c>
+          <t>L623: punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1Cécile Lacombe, Bonnyville.................</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -916,7 +904,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Cannelle Latour, Ã©cole Grandin .........</t>
+          <t>L6: punctuation artifact: repeated periods :: Cannelle Latour, école Grandin .........</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -958,16 +946,8 @@
           <t>L627: punctuation artifact: repeated periods | line starts with lowercase prefix glued to capitalized word | suspicious token(s): iJacques (odd internal casing) :: iJacques Gagnon, Bonnyville......................</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gilbert Proulx, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: HÃ©lÃ¨ne Dansereau, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1018,19 +998,11 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
-        </is>
-      </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Noel Ch Ã© nard, Tangente</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Schayes, Ã©cole Thibeault ........</t>
-        </is>
-      </c>
+          <t>L1095: punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. école consolidée, Donnelly ............7C</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1046,7 +1018,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Beaudoin, Tangente ...............</t>
+          <t>L8: punctuation artifact: repeated periods :: Irène Beaudoin, Tangente ...............</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1081,19 +1053,11 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Picard, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Meunier, Ã©cole Thibeault .......</t>
-        </is>
-      </c>
+          <t>L1312: punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) :: 86Edouard Garneau, école Grandin ..........</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1129,12 +1093,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1147,16 +1111,8 @@
           <t>L1665: punctuation artifact: repeated periods | suspicious token(s): 82i (letter/digit mix) :: ...82i</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Fran Ã§ coise Turcotte, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Adrienne Thivierge, Ã©cole Grandin ......</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1197,7 +1153,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1207,19 +1163,11 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L1814: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut prÃ©sentÃ©e Ã l'artiste1</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claudette Turcotte, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Madeleine Meunier, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+          <t>L1814: suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut présentée à l'artiste1</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1255,7 +1203,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>261</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1273,16 +1221,8 @@
           <t>L1901: suspicious token(s): 1er (letter/digit mix) :: National avant le 1er septembre 1947.</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ronald Patry, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Germaine Roy, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1298,7 +1238,7 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L12: punctuation artifact: repeated periods :: FranÃ§ois McMahon, Saint-Paul ...........</t>
+          <t>L12: punctuation artifact: repeated periods :: François McMahon, Saint-Paul ...........</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
@@ -1333,19 +1273,11 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L2048: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | suspicious token(s): sa1 (letter/digit mix) :: Ã l'Ã¢ge de 77 ans. Cinq ans avant sa1</t>
-        </is>
-      </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorette Tellier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Roy, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+          <t>L2048: suspicious token(s): sa1 (letter/digit mix) :: à l'âge de 77 ans. Cinq ans avant sa1</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1386,7 +1318,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1395,16 +1327,8 @@
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Henri Roy, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond CÃ´tÃ©, Couvent Notre-Dame .......</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1454,16 +1378,8 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Despins, Ã© cole consolid, Falher</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Doucet, Saint-Paul ...............</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1479,7 +1395,7 @@
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Schayes, Ã©cole Thibeault ........</t>
+          <t>L16: punctuation artifact: repeated periods :: Cécile Schayes, école Thibeault ........</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1513,16 +1429,8 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marie-Rose Garneau, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine Cloutier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1538,7 +1446,7 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Meunier, Ã©cole Thibeault .......</t>
+          <t>L17: punctuation artifact: repeated periods :: Lorette Meunier, école Thibeault .......</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1572,16 +1480,8 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Andr Ã© Beaupr Ã©, Bonnyville â€¦.</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o Garand, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1619,16 +1519,8 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel Arcand, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannette Morin, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1644,7 +1536,7 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Adrienne Thivierge, Ã©cole Grandin ......</t>
+          <t>L19: punctuation artifact: repeated periods :: Adrienne Thivierge, école Grandin ......</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
@@ -1666,16 +1558,8 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© erald Dusseault, ecole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ClÃ©ment BÃ©rubÃ©, Beaumont ...............</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1713,16 +1597,8 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: H Ã© lien Richard, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Gosselin, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1738,7 +1614,7 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L21: punctuation artifact: repeated periods :: FranÃ§oise Ouellette, Legal .............</t>
+          <t>L21: punctuation artifact: repeated periods :: Françoise Ouellette, Legal .............</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1760,16 +1636,8 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoinette Casavant, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Armand Robert, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1807,16 +1675,8 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jacques Voyer, Ã© coie Thibeault</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on HÃ©bert, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1832,7 +1692,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Madeleine Meunier, Ã©cole Thibeault .....</t>
+          <t>L23: punctuation artifact: repeated periods :: Madeleine Meunier, école Thibeault .....</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1854,16 +1714,8 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Tarcienne Meunier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Adolphe Boissonneault, Ã©cole Thibeault .</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -1901,16 +1753,8 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude Charrois, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jean-Louis Champagne, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -1948,16 +1792,8 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Pariseau, Ã© cole consolid Ã© e, Donnelly</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Lajoie, ThÃ©rien ................</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -1995,16 +1831,8 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gerard Garand, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Chalifoux, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2020,7 +1848,7 @@
       <c r="P26" s="1" t="inlineStr"/>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L27: punctuation artifact: repeated periods :: Marie-Rose-NoÃ«lla Croteau, Fort Kent ...</t>
+          <t>L27: punctuation artifact: repeated periods :: Marie-Rose-Noëlla Croteau, Fort Kent ...</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2042,16 +1870,8 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Bachand, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul LabontÃ©. Ã©cole Thibeault .......</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
@@ -2067,7 +1887,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Roy, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L29: punctuation artifact: repeated periods :: René Roy, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2089,16 +1909,8 @@
       <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: R Ã© al Demers, Beaumont</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Bachand, Ã©cole Thibeault ........</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
@@ -2136,16 +1948,8 @@
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert Sabourin, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Legault, Bonnyville ...........</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
@@ -2161,7 +1965,7 @@
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond CÃ´tÃ©, Couvent Notre-Dame .......</t>
+          <t>L31: punctuation artifact: repeated periods :: Raymond Côté, Couvent Notre-Dame .......</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2183,16 +1987,8 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Beauchamp, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Gemma Girard, Ã©cole Grandin ...</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
@@ -2230,16 +2026,8 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Philippe H Ã© bert, Saint-Vincent</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Picard, Ã©cole Grandin ...</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
@@ -2277,16 +2065,8 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ad Ã© elard S Ã© Eguin, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©da Bonin, La Corey ........................</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
@@ -2324,16 +2104,8 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gis SÃ©guin, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marie-Rose Garneau, Ã©cole Dunrobin ..........</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
@@ -2349,7 +2121,7 @@
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Doucet, Saint-Paul ...............</t>
+          <t>L35: punctuation artifact: repeated periods :: André Doucet, Saint-Paul ...............</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2371,16 +2143,8 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L179: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland Seguin, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: HÃ©lÃ¨ne Richard, Bonnyville ..................</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
@@ -2418,16 +2182,8 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Bruneau, Ã© cole consolid Ã© e, Falher</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Casavant, Ã©cole Dunrobin .........</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
@@ -2443,7 +2199,7 @@
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o Garand, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L38: punctuation artifact: repeated periods :: Léo Garand, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2465,16 +2221,8 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L184: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Albert Anctil, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Philippe Lemire, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
@@ -2512,16 +2260,8 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L188: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: jeanne I'Oiseau, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le Aubin, Ã©cole consolidÃ©e, Falher ......</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
@@ -2559,16 +2299,8 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: EugÃ©nie F Forcier, ecole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hector Letourneau, Ã©cole Grandin ............</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
@@ -2606,16 +2338,8 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carmen Tellier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: EugÃ©nie Forcier, Ã©cole consolidÃ©e, Donnelly .</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
@@ -2653,16 +2377,8 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Th Ã© berge, Legal</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Sauvageau, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
@@ -2700,16 +2416,8 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L195: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'Edouard Garneau, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Mercier, Fort Kent ...................</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
@@ -2725,7 +2433,7 @@
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannette Morin, Ã©cole Grandin .........</t>
+          <t>L44: punctuation artifact: repeated periods :: Jeannette Morin, école Grandin .........</t>
         </is>
       </c>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2747,16 +2455,8 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L197: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Muriel Walker, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Dusseault, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
@@ -2772,7 +2472,7 @@
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ClÃ©ment BÃ©rubÃ©, Beaumont ...............</t>
+          <t>L45: punctuation artifact: repeated periods :: Clément Bérubé, Beaumont ...............</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2794,16 +2494,8 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L199: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Alice Aquin, Ã© cole Thibeault.</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Brien, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
@@ -2841,16 +2533,8 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert B Ã© rub Ã©. Beaumont</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Loiseau, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
@@ -2866,7 +2550,7 @@
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Gosselin, Ã©cole Thibeault .....</t>
+          <t>L47: punctuation artifact: repeated periods :: Jeannine Gosselin, école Thibeault .....</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2888,16 +2572,8 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L218: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorne Beaupr Ã©, Bonnyville</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Garneau, Ã©cole Dunrobin ..............</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
@@ -2913,7 +2589,7 @@
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Armand Robert, Ã©cole Thibeault .........</t>
+          <t>L48: punctuation artifact: repeated periods :: Armand Robert, école Thibeault .........</t>
         </is>
       </c>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2935,16 +2611,8 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L223: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierrette Lauzon, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Laplante, Ã©cole Dunrobin ...............</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
@@ -2982,16 +2650,8 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannette Sylvestre, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ona Verreault, Tangente ...................</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
@@ -3007,7 +2667,7 @@
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on HÃ©bert, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L50: punctuation artifact: repeated periods :: Léon Hébert, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3029,16 +2689,8 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond P Ã© trin, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Johnson, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
@@ -3076,16 +2728,8 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Irene Paul, Ã© cole consolidee, Fâ€™alher</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ¼lberte Mencke, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
@@ -3101,7 +2745,7 @@
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jean-Louis Champagne, Ã©cole Thibeault ..</t>
+          <t>L53: punctuation artifact: repeated periods :: Jean-Louis Champagne, école Thibeault ..</t>
         </is>
       </c>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3123,16 +2767,8 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gertrude Brochu. Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Martineau, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
@@ -3148,7 +2784,7 @@
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Lajoie, ThÃ©rien ................</t>
+          <t>L54: punctuation artifact: repeated periods :: Georges Lajoie, Thérien ................</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3170,16 +2806,8 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L246: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© Meunier, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Emard, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
@@ -3217,16 +2845,8 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: G Ã© rald Lapointe, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Dame, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
@@ -3264,16 +2884,8 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L253: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Loiseau, Ã© ecle consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denis Gallant, Ã©cole Grandin .........</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
@@ -3311,16 +2923,8 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Maurier, Legal</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard KÃ©roack, Ã©cole Grandin...............</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
@@ -3358,16 +2962,8 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Billy Dubois, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marguerite Albinati, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
@@ -3383,7 +2979,7 @@
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine Chalifoux, Ã©cole Thibeault .....</t>
+          <t>L59: punctuation artifact: repeated periods :: Jeannine Chalifoux, école Thibeault .....</t>
         </is>
       </c>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3405,16 +3001,8 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Tieuli Ã©, Legal</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice Riopel, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
@@ -3430,7 +3018,7 @@
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul LabontÃ©. Ã©cole Thibeault .......</t>
+          <t>L61: punctuation artifact: repeated periods :: Paul Labonté. école Thibeault .......</t>
         </is>
       </c>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3452,16 +3040,8 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jacques Johnson, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Tanguay, Ã©cole consolidÃ©e, Donnelly ...</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
@@ -3477,7 +3057,7 @@
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Bachand, Ã©cole Thibeault ........</t>
+          <t>L62: punctuation artifact: repeated periods :: Guy Bachand, école Thibeault ........</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3499,16 +3079,8 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | candidate OCR token mismatch vs other OCR: "ecole" vs "cole" :: LÃ©on Schayes, ecole Thibeault</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger DesfossÃ©s, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
@@ -3524,7 +3096,7 @@
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Legault, Bonnyville ...........</t>
+          <t>L63: punctuation artifact: repeated periods :: Adèle Legault, Bonnyville ...........</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr"/>
@@ -3546,16 +3118,8 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© La Brie, Fort Kent</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Norman Courchesne, Ã©cole consolidÃ©e: Falher</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
@@ -3593,16 +3157,8 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L307: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Lapiante, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o RÃ©millard, Legal ........................</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
@@ -3640,16 +3196,8 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre Despins, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Aquin, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
@@ -3665,7 +3213,7 @@
       <c r="P61" s="1" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Gemma Girard, Ã©cole Grandin ...</t>
+          <t>L67: punctuation artifact: repeated periods :: Gemma Girard, école Grandin ...</t>
         </is>
       </c>
       <c r="R61" s="1" t="inlineStr"/>
@@ -3687,16 +3235,8 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Th Ã© RÃ¨se Jubinville, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hermas Martin, ThÃ©rien ......................</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
@@ -3712,7 +3252,7 @@
       <c r="P62" s="1" t="inlineStr"/>
       <c r="Q62" s="1" t="inlineStr">
         <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Picard, Ã©cole Grandin ...</t>
+          <t>L68: punctuation artifact: repeated periods :: André Picard, école Grandin ...</t>
         </is>
       </c>
       <c r="R62" s="1" t="inlineStr"/>
@@ -3734,16 +3274,8 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L318: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claire Petersen, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Gratton, ThÃ©rien ...................-.....</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
@@ -3759,7 +3291,7 @@
       <c r="P63" s="1" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©da Bonin, La Corey ........................</t>
+          <t>L69: punctuation artifact: repeated periods :: Léda Bonin, La Corey ........................</t>
         </is>
       </c>
       <c r="R63" s="1" t="inlineStr"/>
@@ -3781,16 +3313,8 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Johnson, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................â€ž.....</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
@@ -3828,16 +3352,8 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: berte Mencke, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rose-Anna Paquette, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
@@ -3875,16 +3391,8 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: C Ã© cile Isabel, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland TieuliÃ©, Legal ...........................</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
@@ -3900,7 +3408,7 @@
       <c r="P66" s="1" t="inlineStr"/>
       <c r="Q66" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marie-Rose Garneau, Ã©cole Dunrobin ..........</t>
+          <t>L73: punctuation artifact: repeated periods :: Marie-Rose Garneau, école Dunrobin ..........</t>
         </is>
       </c>
       <c r="R66" s="1" t="inlineStr"/>
@@ -3922,16 +3430,8 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Annette Lessard, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmela ChÃ©nard, Tangente ......................</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
@@ -3969,16 +3469,8 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L344: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Martineau, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: 63 AurÃ¨le Morneau, Bonnyville ...................</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
@@ -4016,16 +3508,8 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L345: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: C Ã© line Coulombe, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 62 Juliette Houle, Ã©cole Thibeault ..............</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
@@ -4041,7 +3525,7 @@
       <c r="P69" s="1" t="inlineStr"/>
       <c r="Q69" s="1" t="inlineStr">
         <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: HÃ©lÃ¨ne Richard, Bonnyville ..................</t>
+          <t>L76: punctuation artifact: repeated periods :: Hélène Richard, Bonnyville ..................</t>
         </is>
       </c>
       <c r="R69" s="1" t="inlineStr"/>
@@ -4063,16 +3547,8 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L347: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Fortin, Tangente</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice McNamara, Ã©cole Grandin .................</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
@@ -4110,16 +3586,8 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© Bouchard, Tangente</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elizabeth Meunier, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
@@ -4135,7 +3603,7 @@
       <c r="P71" s="1" t="inlineStr"/>
       <c r="Q71" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Casavant, Ã©cole Dunrobin .........</t>
+          <t>L78: punctuation artifact: repeated periods :: Antoinette Casavant, école Dunrobin .........</t>
         </is>
       </c>
       <c r="R71" s="1" t="inlineStr"/>
@@ -4157,16 +3625,8 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine Emard, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile VallÃ©e, Beaumont ....................</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
@@ -4182,7 +3642,7 @@
       <c r="P72" s="1" t="inlineStr"/>
       <c r="Q72" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le Aubin, Ã©cole consolidÃ©e, Falher ......</t>
+          <t>L80: punctuation artifact: repeated periods :: Gisèle Aubin, école consolidée, Falher ......</t>
         </is>
       </c>
       <c r="R72" s="1" t="inlineStr"/>
@@ -4204,16 +3664,8 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L358: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Th Ã© Ã©rÃ¨se Rochette, Tangente</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©andre Dansereau, Beaumont</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
@@ -4229,7 +3681,7 @@
       <c r="P73" s="1" t="inlineStr"/>
       <c r="Q73" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hector Letourneau, Ã©cole Grandin ............</t>
+          <t>L81: punctuation artifact: repeated periods :: Hector Letourneau, école Grandin ............</t>
         </is>
       </c>
       <c r="R73" s="1" t="inlineStr"/>
@@ -4251,16 +3703,8 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L362: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert Dame, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rald Royer, Beaumont .........................</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
@@ -4298,16 +3742,8 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger B Ã© land, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 59 Laurier Rousseau, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
@@ -4345,16 +3781,8 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Lussier, Tangente</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 57 Claude Proulx, Ã©cole consolidÃ©e, Falher .</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
@@ -4392,16 +3820,8 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denis Gallant, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel LabontÃ©, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
@@ -4439,16 +3859,8 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Doran, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Della BÃ©langer, Plamondon .......................</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
@@ -4486,16 +3898,8 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L385: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Michel Voyer, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L204: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Augustine Thibault, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
@@ -4511,7 +3915,7 @@
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Mercier, Fort Kent ...................</t>
+          <t>L89: punctuation artifact: repeated periods :: Cécile Mercier, Fort Kent ...................</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr"/>
@@ -4533,16 +3937,8 @@
       <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>L387: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Th Ã© Ã©rÃ¨se Gauthier, Plamondon</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: ThÃ©rÃ¨se Courchesne, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
@@ -4558,7 +3954,7 @@
       <c r="P80" s="1" t="inlineStr"/>
       <c r="Q80" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Dusseault, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L90: punctuation artifact: repeated periods :: Roger Dusseault, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R80" s="1" t="inlineStr"/>
@@ -4580,16 +3976,8 @@
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rom Ã© o Bedard, Tangente</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: CÃ©cile BussiÃ¨re, pensionnat de l'Assomption ..........64</t>
-        </is>
-      </c>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
@@ -4627,16 +4015,8 @@
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>L398: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Therese Ch Ã© nard. Tangente</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul Roy, Ã©cole consolidÃ©e, Donnelly .......</t>
-        </is>
-      </c>
+      <c r="J82" s="1" t="inlineStr"/>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
@@ -4674,16 +4054,8 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>L408: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Despins, Ã© cole Dunrobin</t>
-        </is>
-      </c>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Roy, Fort Kent ......................</t>
-        </is>
-      </c>
+      <c r="J83" s="1" t="inlineStr"/>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
@@ -4721,16 +4093,8 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>L418: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antonia Villeneuve, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L228: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Joseph Girard, Ã©cole Grandin ...............</t>
-        </is>
-      </c>
+      <c r="J84" s="1" t="inlineStr"/>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
@@ -4746,7 +4110,7 @@
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Antoinette Brien, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L94: punctuation artifact: repeated periods :: Antoinette Brien, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R84" s="1" t="inlineStr"/>
@@ -4768,16 +4132,8 @@
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>L420: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bernard roack, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L234: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: AndrÃ© Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J85" s="1" t="inlineStr"/>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
@@ -4793,7 +4149,7 @@
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Loiseau, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L95: punctuation artifact: repeated periods :: Roger Loiseau, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R85" s="1" t="inlineStr"/>
@@ -4815,16 +4171,8 @@
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>L422: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine G Ã© linas, pensionnat de I'Assomption</t>
-        </is>
-      </c>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Roy, Ã©cole consolidÃ©e, Falher ................60</t>
-        </is>
-      </c>
+      <c r="J86" s="1" t="inlineStr"/>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
@@ -4862,16 +4210,8 @@
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Boulet, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L240: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurier Arcand, Ã©cole Grandin ........................60</t>
-        </is>
-      </c>
+      <c r="J87" s="1" t="inlineStr"/>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
@@ -4909,16 +4249,8 @@
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marguerite Albinati, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L242: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Pariseau, Ã©cole consolidÃ©e, Donnelly ..........</t>
-        </is>
-      </c>
+      <c r="J88" s="1" t="inlineStr"/>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
@@ -4956,16 +4288,8 @@
       <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Riopel, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine CÃ´tÃ©, Ã©cole consolidÃ©e, Donnelly ............</t>
-        </is>
-      </c>
+      <c r="J89" s="1" t="inlineStr"/>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
@@ -5003,16 +4327,8 @@
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorraine B Ã© rub Ã©. Beaumont</t>
-        </is>
-      </c>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 86 Denise Maure, Ã©cole consolidÃ©e, Falher .............</t>
-        </is>
-      </c>
+      <c r="J90" s="1" t="inlineStr"/>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
@@ -5028,7 +4344,7 @@
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Garneau, Ã©cole Dunrobin ..............</t>
+          <t>L100: punctuation artifact: repeated periods :: Cécile Garneau, école Dunrobin ..............</t>
         </is>
       </c>
       <c r="R90" s="1" t="inlineStr"/>
@@ -5050,16 +4366,8 @@
       <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Therese Tanguay, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 Yolande Garneau, Ã©cole Granlin .....................</t>
-        </is>
-      </c>
+      <c r="J91" s="1" t="inlineStr"/>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
@@ -5075,7 +4383,7 @@
       <c r="P91" s="1" t="inlineStr"/>
       <c r="Q91" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Laplante, Ã©cole Dunrobin ...............</t>
+          <t>L101: punctuation artifact: repeated periods :: Rita Laplante, école Dunrobin ...............</t>
         </is>
       </c>
       <c r="R91" s="1" t="inlineStr"/>
@@ -5097,16 +4405,8 @@
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Alberta Labont Ã©, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Levasseur, Ã©cole Grandin ......................</t>
-        </is>
-      </c>
+      <c r="J92" s="1" t="inlineStr"/>
+      <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
@@ -5122,7 +4422,7 @@
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ona Verreault, Tangente ...................</t>
+          <t>L102: punctuation artifact: repeated periods :: Léona Verreault, Tangente ...................</t>
         </is>
       </c>
       <c r="R92" s="1" t="inlineStr"/>
@@ -5144,16 +4444,8 @@
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude B Ã© rub Ã©, Beaumont</t>
-        </is>
-      </c>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yvette Normand, ThÃ©rien ..............................</t>
-        </is>
-      </c>
+      <c r="J93" s="1" t="inlineStr"/>
+      <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
@@ -5169,7 +4461,7 @@
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Johnson, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L103: punctuation artifact: repeated periods :: Denise Johnson, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R93" s="1" t="inlineStr"/>
@@ -5191,16 +4483,8 @@
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>L460: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Desfoss, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond Sylvestre, Ã©cole Thibeault ...................</t>
-        </is>
-      </c>
+      <c r="J94" s="1" t="inlineStr"/>
+      <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
@@ -5216,7 +4500,7 @@
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ¼lberte Mencke, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L104: punctuation artifact: repeated periods :: Gülberte Mencke, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R94" s="1" t="inlineStr"/>
@@ -5238,16 +4522,8 @@
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: H Ã© Ã©lÃ¨ne Chouinard, La Corey</t>
-        </is>
-      </c>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 CÃ©cile Doucet. Tangente ............................</t>
-        </is>
-      </c>
+      <c r="J95" s="1" t="inlineStr"/>
+      <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
@@ -5263,7 +4539,7 @@
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© Martineau, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L105: punctuation artifact: repeated periods :: André Martineau, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R95" s="1" t="inlineStr"/>
@@ -5285,16 +4561,8 @@
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Andr Ã© a Trudel, Saint-Paul</t>
-        </is>
-      </c>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rodrigue HÃ©bert. Saint-Vincent 79</t>
-        </is>
-      </c>
+      <c r="J96" s="1" t="inlineStr"/>
+      <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
@@ -5310,7 +4578,7 @@
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Dame, Ã©cole Grandin ..................</t>
+          <t>L107: punctuation artifact: repeated periods :: Robert Dame, école Grandin ..................</t>
         </is>
       </c>
       <c r="R96" s="1" t="inlineStr"/>
@@ -5332,16 +4600,8 @@
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>L470: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Norman Courchesne, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Suzanne VallÃ©e, Bonnyville .....................79</t>
-        </is>
-      </c>
+      <c r="J97" s="1" t="inlineStr"/>
+      <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
@@ -5357,7 +4617,7 @@
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denis Gallant, Ã©cole Grandin .........</t>
+          <t>L109: punctuation artifact: repeated periods :: Denis Gallant, école Grandin .........</t>
         </is>
       </c>
       <c r="R97" s="1" t="inlineStr"/>
@@ -5379,16 +4639,8 @@
       <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Leo R Ã© millard, Legal</t>
-        </is>
-      </c>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoinette BÃ©dard, Tangente ....................79</t>
-        </is>
-      </c>
+      <c r="J98" s="1" t="inlineStr"/>
+      <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
@@ -5426,16 +4678,8 @@
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>L482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© ontine Aubin, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L288: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul-AndrÃ© Cloutier, Ã©cole consolidÃ©e, Donnelly 79</t>
-        </is>
-      </c>
+      <c r="J99" s="1" t="inlineStr"/>
+      <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
@@ -5473,16 +4717,8 @@
       <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurette Lafond, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©ona Saint-Jean, Legal ........................78</t>
-        </is>
-      </c>
+      <c r="J100" s="1" t="inlineStr"/>
+      <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
@@ -5520,16 +4756,8 @@
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gerard Aquin, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Constance HÃ©bert, Legal ........................78</t>
-        </is>
-      </c>
+      <c r="J101" s="1" t="inlineStr"/>
+      <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
@@ -5567,16 +4795,8 @@
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Doreen Stelte, Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rollande Boulet, Ã©cole consolidÃ©e, Donnelly ..</t>
-        </is>
-      </c>
+      <c r="J102" s="1" t="inlineStr"/>
+      <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
@@ -5592,7 +4812,7 @@
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard KÃ©roack, Ã©cole Grandin...............</t>
+          <t>L115: punctuation artifact: repeated periods :: Bernard Kéroack, école Grandin...............</t>
         </is>
       </c>
       <c r="R102" s="1" t="inlineStr"/>
@@ -5614,16 +4834,8 @@
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucien Gratton, Th Ã© rien Village</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L296: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RÃ©ginald Lussier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J103" s="1" t="inlineStr"/>
+      <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
@@ -5639,7 +4851,7 @@
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr">
         <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marguerite Albinati, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L116: punctuation artifact: repeated periods :: Marguerite Albinati, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R103" s="1" t="inlineStr"/>
@@ -5661,16 +4873,8 @@
       <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© Magant, Sainte-Lina</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Annette LaverdiÃ¨re, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J104" s="1" t="inlineStr"/>
+      <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
@@ -5686,7 +4890,7 @@
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr">
         <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice Riopel, Ã©cole Thibeault ..</t>
+          <t>L117: punctuation artifact: repeated periods :: Maurice Riopel, école Thibeault ..</t>
         </is>
       </c>
       <c r="R104" s="1" t="inlineStr"/>
@@ -5708,16 +4912,8 @@
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucille Fortier, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rachel LabontÃ©, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J105" s="1" t="inlineStr"/>
+      <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
@@ -5733,7 +4929,7 @@
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Tanguay, Ã©cole consolidÃ©e, Donnelly ...</t>
+          <t>L119: punctuation artifact: repeated periods :: Thérèse Tanguay, école consolidée, Donnelly ...</t>
         </is>
       </c>
       <c r="R105" s="1" t="inlineStr"/>
@@ -5755,16 +4951,8 @@
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ren Ã© e Meunier Ã© cole Thibeault</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Patricia BÃ©land. Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
@@ -5780,7 +4968,7 @@
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger DesfossÃ©s, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L120: punctuation artifact: repeated periods :: Roger Desfossés, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R106" s="1" t="inlineStr"/>
@@ -5802,16 +4990,8 @@
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>L542: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucien Roy, Ã© cole consolidee, Falher</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard LabontÃ©, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="J107" s="1" t="inlineStr"/>
+      <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
@@ -5827,7 +5007,7 @@
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr">
         <is>
-          <t>L123: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©o RÃ©millard, Legal ........................</t>
+          <t>L123: punctuation artifact: repeated periods :: Léo Rémillard, Legal ........................</t>
         </is>
       </c>
       <c r="R107" s="1" t="inlineStr"/>
@@ -5849,16 +5029,8 @@
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© vis Chiasson, Sainte-Lina</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Caouette, Bonnyville ................</t>
-        </is>
-      </c>
+      <c r="J108" s="1" t="inlineStr"/>
+      <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
@@ -5874,7 +5046,7 @@
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Aquin, Ã©cole Thibeault ...............</t>
+          <t>L124: punctuation artifact: repeated periods :: Gérard Aquin, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R108" s="1" t="inlineStr"/>
@@ -5896,16 +5068,8 @@
       <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>L547: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claire H Ã© bert, Saint-Vincent</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Sylvia Yakimchuk, ThÃ©rien Village ........</t>
-        </is>
-      </c>
+      <c r="J109" s="1" t="inlineStr"/>
+      <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
@@ -5921,7 +5085,7 @@
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Hermas Martin, ThÃ©rien ......................</t>
+          <t>L125: punctuation artifact: repeated periods :: Hermas Martin, Thérien ......................</t>
         </is>
       </c>
       <c r="R109" s="1" t="inlineStr"/>
@@ -5943,16 +5107,8 @@
       <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel Legris, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucille MahÃ©, Legal .......</t>
-        </is>
-      </c>
+      <c r="J110" s="1" t="inlineStr"/>
+      <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
@@ -5990,16 +5146,8 @@
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Albert Benoit, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L324: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§ois Blackburn, Ã©cole Grandin ........</t>
-        </is>
-      </c>
+      <c r="J111" s="1" t="inlineStr"/>
+      <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
@@ -6037,16 +5185,8 @@
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carole Lefebvre, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
-        </is>
-      </c>
+      <c r="J112" s="1" t="inlineStr"/>
+      <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
@@ -6084,16 +5224,8 @@
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rose-Anna Paquette, Ã© cole consolidee, Donnelly</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Portelance. Tangente ..............</t>
-        </is>
-      </c>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
@@ -6109,7 +5241,7 @@
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Gratton, ThÃ©rien ...................-.....</t>
+          <t>L130: punctuation artifact: repeated periods :: Claire Gratton, Thérien ...................-.....</t>
         </is>
       </c>
       <c r="R113" s="1" t="inlineStr"/>
@@ -6131,16 +5263,8 @@
       <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marc Voyer, Ã© cole Grandin</t>
-        </is>
-      </c>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre Lacroix, Ã©cole consolidÃ©e, Donnelly .</t>
-        </is>
-      </c>
+      <c r="J114" s="1" t="inlineStr"/>
+      <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
@@ -6178,16 +5302,8 @@
       <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roland Tieuli Ã©, Legal</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: |Normand SÃ©guin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J115" s="1" t="inlineStr"/>
+      <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
@@ -6225,16 +5341,8 @@
       <c r="G116" s="1" t="inlineStr"/>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr"/>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>L581: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: on classe l'historien am Ã© ricain School-</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marielle BÃ©land, Bonnyville ................</t>
-        </is>
-      </c>
+      <c r="J116" s="1" t="inlineStr"/>
+      <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
@@ -6272,16 +5380,8 @@
       <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr"/>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>L582: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Une le Ã§ on de r Ã© alisme</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Thibault, Ã©cole consolidÃ©e, Donnelly ...</t>
-        </is>
-      </c>
+      <c r="J117" s="1" t="inlineStr"/>
+      <c r="K117" s="1" t="inlineStr"/>
       <c r="L117" s="1" t="inlineStr"/>
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
@@ -6297,7 +5397,7 @@
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="inlineStr">
         <is>
-          <t>L136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................â€ž.....</t>
+          <t>L136: punctuation artifact: repeated periods :: Elizabeth Nadon, La Corey .................„.....</t>
         </is>
       </c>
       <c r="R117" s="1" t="inlineStr"/>
@@ -6319,16 +5419,8 @@
       <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr"/>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: craft, qui s'en servit pour p Ã© n Ã© trer au</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: RenÃ© CÃ´tÃ©, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J118" s="1" t="inlineStr"/>
+      <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
@@ -6344,7 +5436,7 @@
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rose-Anna Paquette, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L138: punctuation artifact: repeated periods :: Rose-Anna Paquette, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R118" s="1" t="inlineStr"/>
@@ -6366,16 +5458,8 @@
       <c r="G119" s="1" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr"/>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>L589: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: : coeur des tribus indiennes et les Ã© tudier</t>
-        </is>
-      </c>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ! Germaine Ethier, Ã©cole Thibault ..........</t>
-        </is>
-      </c>
+      <c r="J119" s="1" t="inlineStr"/>
+      <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
@@ -6413,16 +5497,8 @@
       <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr"/>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>L594: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Autre fondateur de vile am Ã© ricaine,</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: |Raymond Ouellette. ThÃ©rien Village........</t>
-        </is>
-      </c>
+      <c r="J120" s="1" t="inlineStr"/>
+      <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
@@ -6438,7 +5514,7 @@
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr">
         <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland TieuliÃ©, Legal ...........................</t>
+          <t>L140: punctuation artifact: repeated periods :: Roland Tieulié, Legal ...........................</t>
         </is>
       </c>
       <c r="R120" s="1" t="inlineStr"/>
@@ -6460,16 +5536,8 @@
       <c r="G121" s="1" t="inlineStr"/>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr"/>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: d'aventures, dont il ne se tira que grÃ¢ce</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: | Madeleine Brissette, Ã©cole Grandin........</t>
-        </is>
-      </c>
+      <c r="J121" s="1" t="inlineStr"/>
+      <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
@@ -6507,16 +5575,8 @@
       <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr"/>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>L600: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tableau qui comportait un homme d Ã© ca-</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Despins, Ã©cole Dunrobin. Vimy</t>
-        </is>
-      </c>
+      <c r="J122" s="1" t="inlineStr"/>
+      <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
@@ -6554,16 +5614,8 @@
       <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr"/>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>L603: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pit. Le grand seigneur appr Ã© cia l'art:</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>L371: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Aurore Martel, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J123" s="1" t="inlineStr"/>
+      <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
@@ -6601,16 +5653,8 @@
       <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr"/>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>L608: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'Italien; n Ã© anmoins, il releva un</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Laplante, Ã©cole Dunrobin ............</t>
-        </is>
-      </c>
+      <c r="J124" s="1" t="inlineStr"/>
+      <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
@@ -6648,16 +5692,8 @@
       <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr"/>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>L609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Loi sur la Taxation des Surplus de b Ã© n Ã© fices</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Yvette Deslauriers, Ã©cole Thibeault.</t>
-        </is>
-      </c>
+      <c r="J125" s="1" t="inlineStr"/>
+      <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
@@ -6673,7 +5709,7 @@
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="inlineStr">
         <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmela ChÃ©nard, Tangente ......................</t>
+          <t>L159: punctuation artifact: repeated periods :: Carmela Chénard, Tangente ......................</t>
         </is>
       </c>
       <c r="R125" s="1" t="inlineStr"/>
@@ -6695,16 +5731,8 @@
       <c r="G126" s="1" t="inlineStr"/>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr"/>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>L610: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nous avons donne, la semaine der- missionnaire des vivres pour lâ€™armee du NOU-OUTS. I fit ensuite le</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Laurier Coulombe, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J126" s="1" t="inlineStr"/>
+      <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
@@ -6720,7 +5748,7 @@
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr">
         <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: 63 AurÃ¨le Morneau, Bonnyville ...................</t>
+          <t>L163: punctuation artifact: repeated periods :: 63 Aurèle Morneau, Bonnyville ...................</t>
         </is>
       </c>
       <c r="R126" s="1" t="inlineStr"/>
@@ -6742,16 +5770,8 @@
       <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr"/>
-      <c r="J127" s="1" t="inlineStr">
-        <is>
-          <t>L612: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: sr Ã© rÃ©guliÃ¨re. Il suivit, en cette qualit, les commerce des fourrures pour son comp-</t>
-        </is>
-      </c>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>L460: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pauline Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J127" s="1" t="inlineStr"/>
+      <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
@@ -6767,7 +5787,7 @@
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 62 Juliette Houle, Ã©cole Thibeault ..............</t>
+          <t>L165: punctuation artifact: repeated periods :: 62 Juliette Houle, école Thibeault ..............</t>
         </is>
       </c>
       <c r="R127" s="1" t="inlineStr"/>
@@ -6789,16 +5809,8 @@
       <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr"/>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>L613: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre M Ã© nard</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jeannine ChÃ©nier, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J128" s="1" t="inlineStr"/>
+      <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
@@ -6836,16 +5848,8 @@
       <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr"/>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: miÃ¨re, une courte biographie de trois</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Guibault, ThÃ©rien Village ...................</t>
-        </is>
-      </c>
+      <c r="J129" s="1" t="inlineStr"/>
+      <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
@@ -6883,16 +5887,8 @@
       <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr"/>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ments qui se rendaient a Washing-te et finit par s 'Ã© tablir, en 1853,Ã Supe-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeanne Charlier, Ã©cole Dunrobin ...................</t>
-        </is>
-      </c>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
@@ -6908,7 +5904,7 @@
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr">
         <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Maurice McNamara, Ã©cole Grandin .................</t>
+          <t>L171: punctuation artifact: repeated periods :: Maurice McNamara, école Grandin .................</t>
         </is>
       </c>
       <c r="R130" s="1" t="inlineStr"/>
@@ -6930,16 +5926,8 @@
       <c r="G131" s="1" t="inlineStr"/>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr"/>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: te n 'Ã© tait pas telle qu'il fallait.</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Trottier, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
@@ -6955,7 +5943,7 @@
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elizabeth Meunier, Ã©cole Thibeault .............</t>
+          <t>L173: punctuation artifact: repeated periods :: Elizabeth Meunier, école Thibeault .............</t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr"/>
@@ -6977,16 +5965,8 @@
       <c r="G132" s="1" t="inlineStr"/>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr"/>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Demande concernant les b Ã© n Ã© fices normaux</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcelle BÃ©langer, Plamondon ......................</t>
-        </is>
-      </c>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
@@ -7002,7 +5982,7 @@
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile VallÃ©e, Beaumont ....................</t>
+          <t>L178: punctuation artifact: repeated periods :: Cécile Vallée, Beaumont ....................</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr"/>
@@ -7024,16 +6004,8 @@
       <c r="G133" s="1" t="inlineStr"/>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr"/>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>L619: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00A9 COPYRIGHT SIGN :: des n Å� stres qui ont fond Ã© des villes aux</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>L482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elsie Loch, ThÃ©rien Village .......................</t>
-        </is>
-      </c>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
@@ -7049,7 +6021,7 @@
       <c r="P133" s="1" t="inlineStr"/>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rald Royer, Beaumont .........................</t>
+          <t>L182: punctuation artifact: repeated periods :: Gérald Royer, Beaumont .........................</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr"/>
@@ -7071,16 +6043,8 @@
       <c r="G134" s="1" t="inlineStr"/>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr"/>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€” Quand un homme est d Ã© capit Ã©, dit-</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Colette Morin, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
@@ -7118,16 +6082,8 @@
       <c r="G135" s="1" t="inlineStr"/>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr"/>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>L626: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: les noms sont inscrits dans le d Ã© velop-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Pilon, Ã©cole Grandin ......................</t>
-        </is>
-      </c>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
@@ -7165,16 +6121,8 @@
       <c r="G136" s="1" t="inlineStr"/>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr"/>
-      <c r="J136" s="1" t="inlineStr">
-        <is>
-          <t>L632: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pement de la grande r Ã© publique amÃ©ri</t>
-        </is>
-      </c>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Henri VallÃ©e, Beaumont ............................</t>
-        </is>
-      </c>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
@@ -7190,7 +6138,7 @@
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>L200: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Della BÃ©langer, Plamondon .......................</t>
+          <t>L200: punctuation artifact: repeated periods :: Della Bélanger, Plamondon .......................</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr"/>
@@ -7212,16 +6160,8 @@
       <c r="G137" s="1" t="inlineStr"/>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr"/>
-      <c r="J137" s="1" t="inlineStr">
-        <is>
-          <t>L641: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vres avec l'Etat. Il est vrai que ce n 'Ã© tait</t>
-        </is>
-      </c>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Laplante, Couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
@@ -7259,16 +6199,8 @@
       <c r="G138" s="1" t="inlineStr"/>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr"/>
-      <c r="J138" s="1" t="inlineStr">
-        <is>
-          <t>L642: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nom, crit Tass Ã©, mais I'ann Ã© e suivante, honneur a leur pays d'origine que Pierre</t>
-        </is>
-      </c>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marcel BÃ©dard, Tangente</t>
-        </is>
-      </c>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
@@ -7306,16 +6238,8 @@
       <c r="G139" s="1" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr"/>
-      <c r="J139" s="1" t="inlineStr">
-        <is>
-          <t>L643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: clave tomba et fut pr Ã© sent Ã© e a l'artiste</t>
-        </is>
-      </c>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: UldÃ©ric Rochette, Tangente</t>
-        </is>
-      </c>
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
@@ -7353,16 +6277,8 @@
       <c r="G140" s="1" t="inlineStr"/>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr"/>
-      <c r="J140" s="1" t="inlineStr">
-        <is>
-          <t>L646: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M Ã© nard.</t>
-        </is>
-      </c>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: IrÃ¨ne Lussier, Tangente</t>
-        </is>
-      </c>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
@@ -7400,16 +6316,8 @@
       <c r="G141" s="1" t="inlineStr"/>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr"/>
-      <c r="J141" s="1" t="inlineStr">
-        <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: De r Ã© centes modifications apport Ã© es a la loi ci-dessus</t>
-        </is>
-      </c>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roch Proulx, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
@@ -7447,16 +6355,8 @@
       <c r="G142" s="1" t="inlineStr"/>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr"/>
-      <c r="J142" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il naquit Ã Qu Ã© bec en 1767. A dix-neuf</t>
-        </is>
-      </c>
-      <c r="K142" s="1" t="inlineStr">
-        <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Yvette Thivierge, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
@@ -7494,16 +6394,8 @@
       <c r="G143" s="1" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr"/>
-      <c r="J143" s="1" t="inlineStr">
-        <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: portent que toute demande concernant les b Ã© n Ã© fices</t>
-        </is>
-      </c>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on Handfield, Beaumont ..........................</t>
-        </is>
-      </c>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
@@ -7519,7 +6411,7 @@
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Paul Roy, Ã©cole consolidÃ©e, Donnelly .......</t>
+          <t>L222: punctuation artifact: repeated periods :: Paul Roy, école consolidée, Donnelly .......</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr"/>
@@ -7541,16 +6433,8 @@
       <c r="G144" s="1" t="inlineStr"/>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr"/>
-      <c r="J144" s="1" t="inlineStr">
-        <is>
-          <t>L655: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: geaient rien moins qu'a d Ã© ner Chica-</t>
-        </is>
-      </c>
-      <c r="K144" s="1" t="inlineStr">
-        <is>
-          <t>L537: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Eveline PichÃ©, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
       <c r="L144" s="1" t="inlineStr"/>
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
@@ -7566,7 +6450,7 @@
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr">
         <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Roy, Fort Kent ......................</t>
+          <t>L224: punctuation artifact: repeated periods :: Cécile Roy, Fort Kent ......................</t>
         </is>
       </c>
       <c r="R144" s="1" t="inlineStr"/>
@@ -7588,16 +6472,8 @@
       <c r="G145" s="1" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr"/>
-      <c r="J145" s="1" t="inlineStr">
-        <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bellini fut tellement Ã© pouvant, qu'il</t>
-        </is>
-      </c>
-      <c r="K145" s="1" t="inlineStr">
-        <is>
-          <t>L544: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: IrÃ¨ne Bruneau, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
@@ -7635,16 +6511,8 @@
       <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr"/>
-      <c r="J146" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans la soci Ã© t Ã© commerciale Lisa &amp; Cie,</t>
-        </is>
-      </c>
-      <c r="K146" s="1" t="inlineStr">
-        <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Paquette, Bonnyville ......................</t>
-        </is>
-      </c>
+      <c r="J146" s="1" t="inlineStr"/>
+      <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
@@ -7660,7 +6528,7 @@
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr">
         <is>
-          <t>L228: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Joseph Girard, Ã©cole Grandin ...............</t>
+          <t>L228: punctuation artifact: repeated periods :: Joseph Girard, école Grandin ...............</t>
         </is>
       </c>
       <c r="R146" s="1" t="inlineStr"/>
@@ -7682,16 +6550,8 @@
       <c r="G147" s="1" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr"/>
-      <c r="J147" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Personne n'a manifest Ã© plus d'esprit</t>
-        </is>
-      </c>
-      <c r="K147" s="1" t="inlineStr">
-        <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: PhilomÃ¨ne Frigon, Saint-Vincent ...................</t>
-        </is>
-      </c>
+      <c r="J147" s="1" t="inlineStr"/>
+      <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
@@ -7729,16 +6589,8 @@
       <c r="G148" s="1" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
-      <c r="J148" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l Ã© e a devenir l'entrepot des produits du</t>
-        </is>
-      </c>
-      <c r="K148" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Dame, Ã©cole Grandin .........................</t>
-        </is>
-      </c>
+      <c r="J148" s="1" t="inlineStr"/>
+      <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
@@ -7776,16 +6628,8 @@
       <c r="G149" s="1" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr"/>
-      <c r="J149" s="1" t="inlineStr">
-        <is>
-          <t>L667: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dont ies rations s 'Ã© tendaient jus-</t>
-        </is>
-      </c>
-      <c r="K149" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alfred ThÃ©berge, Legal ............................</t>
-        </is>
-      </c>
+      <c r="J149" s="1" t="inlineStr"/>
+      <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
@@ -7801,7 +6645,7 @@
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr">
         <is>
-          <t>L242: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Pariseau, Ã©cole consolidÃ©e, Donnelly ..........</t>
+          <t>L242: punctuation artifact: repeated periods :: Cécile Pariseau, école consolidée, Donnelly ..........</t>
         </is>
       </c>
       <c r="R149" s="1" t="inlineStr"/>
@@ -7823,16 +6667,8 @@
       <c r="G150" s="1" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr"/>
-      <c r="J150" s="1" t="inlineStr">
-        <is>
-          <t>L668: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: promptement un tel maÃ®tre.</t>
-        </is>
-      </c>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bonin, La Corey ............................</t>
-        </is>
-      </c>
+      <c r="J150" s="1" t="inlineStr"/>
+      <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
@@ -7848,7 +6684,7 @@
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeannine CÃ´tÃ©, Ã©cole consolidÃ©e, Donnelly ............</t>
+          <t>L244: punctuation artifact: repeated periods :: Jeannine Côté, école consolidée, Donnelly ............</t>
         </is>
       </c>
       <c r="R150" s="1" t="inlineStr"/>
@@ -7870,16 +6706,8 @@
       <c r="G151" s="1" t="inlineStr"/>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr"/>
-      <c r="J151" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: veau proce Ã© d Ã© pour la fonte des mine-</t>
-        </is>
-      </c>
-      <c r="K151" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: I NoÃ«l ChÃ©nard, Tangente ........................</t>
-        </is>
-      </c>
+      <c r="J151" s="1" t="inlineStr"/>
+      <c r="K151" s="1" t="inlineStr"/>
       <c r="L151" s="1" t="inlineStr"/>
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
@@ -7917,16 +6745,8 @@
       <c r="G152" s="1" t="inlineStr"/>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
-      <c r="J152" s="1" t="inlineStr">
-        <is>
-          <t>L671: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'initiative dans le d Ã© veloppement de</t>
-        </is>
-      </c>
-      <c r="K152" s="1" t="inlineStr">
-        <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Anita St-Arneault, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="J152" s="1" t="inlineStr"/>
+      <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
@@ -7964,16 +6784,8 @@
       <c r="G153" s="1" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
-      <c r="J153" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Nord-Ouest, le port le plus fr Ã© quent de</t>
-        </is>
-      </c>
-      <c r="K153" s="1" t="inlineStr">
-        <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claudette Turcotte, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J153" s="1" t="inlineStr"/>
+      <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
@@ -7989,7 +6801,7 @@
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 86 Denise Maure, Ã©cole consolidÃ©e, Falher .............</t>
+          <t>L250: punctuation artifact: repeated periods :: 86 Denise Maure, école consolidée, Falher .............</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr"/>
@@ -8011,16 +6823,8 @@
       <c r="G154" s="1" t="inlineStr"/>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
-      <c r="J154" s="1" t="inlineStr">
-        <is>
-          <t>L674: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qu'aux Rocheuses. Nomm Ã© plus tard a-</t>
-        </is>
-      </c>
-      <c r="K154" s="1" t="inlineStr">
-        <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Tellier, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="J154" s="1" t="inlineStr"/>
+      <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
@@ -8058,16 +6862,8 @@
       <c r="G155" s="1" t="inlineStr"/>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
-      <c r="J155" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: l'Ouest am Ã© ricain que les frÃ¨res Beau-</t>
-        </is>
-      </c>
-      <c r="K155" s="1" t="inlineStr">
-        <is>
-          <t>L578: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©cile Collins, Fort Kent</t>
-        </is>
-      </c>
+      <c r="J155" s="1" t="inlineStr"/>
+      <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
@@ -8105,16 +6901,8 @@
       <c r="G156" s="1" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
-      <c r="J156" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: lui assur Ã¨ rent un revenu au considÃ©rable.</t>
-        </is>
-      </c>
-      <c r="K156" s="1" t="inlineStr">
-        <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© BeauprÃ©, Bonnyville .......................</t>
-        </is>
-      </c>
+      <c r="J156" s="1" t="inlineStr"/>
+      <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
@@ -8152,16 +6940,8 @@
       <c r="G157" s="1" t="inlineStr"/>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
-      <c r="J157" s="1" t="inlineStr">
-        <is>
-          <t>L683: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la Cit Ã© du Sup Ã© rieur n'avait pas encore</t>
-        </is>
-      </c>
-      <c r="K157" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rald Dusseault, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J157" s="1" t="inlineStr"/>
+      <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
@@ -8199,16 +6979,8 @@
       <c r="G158" s="1" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
-      <c r="J158" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des Etats-Unis, il r Ã© ussit a conclure des</t>
-        </is>
-      </c>
-      <c r="K158" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland Carriere, Ã©cole Dunrobin .................</t>
-        </is>
-      </c>
+      <c r="J158" s="1" t="inlineStr"/>
+      <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
@@ -8246,16 +7018,8 @@
       <c r="G159" s="1" t="inlineStr"/>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
-      <c r="J159" s="1" t="inlineStr">
-        <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: derri elle de campagnes cultiv Ã© es, ni</t>
-        </is>
-      </c>
-      <c r="K159" s="1" t="inlineStr">
-        <is>
-          <t>L588: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Houle, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J159" s="1" t="inlineStr"/>
+      <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
@@ -8293,16 +7057,8 @@
       <c r="G160" s="1" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr"/>
-      <c r="J160" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: me une voie ferr Ã© e. Aussi elle est pas-</t>
-        </is>
-      </c>
-      <c r="K160" s="1" t="inlineStr">
-        <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: HervÃ© Ouellette, Sainte-Lina ....................</t>
-        </is>
-      </c>
+      <c r="J160" s="1" t="inlineStr"/>
+      <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
@@ -8318,7 +7074,7 @@
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 Yolande Garneau, Ã©cole Granlin .....................</t>
+          <t>L264: punctuation artifact: repeated periods :: 85 Yolande Garneau, école Granlin .....................</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr"/>
@@ -8340,16 +7096,8 @@
       <c r="G161" s="1" t="inlineStr"/>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr"/>
-      <c r="J161" s="1" t="inlineStr">
-        <is>
-          <t>L691: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: trait Ã© s avec plusieurs tribus. Aux Ã© lec-</t>
-        </is>
-      </c>
-      <c r="K161" s="1" t="inlineStr">
-        <is>
-          <t>L596: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude Charrois, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J161" s="1" t="inlineStr"/>
+      <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
@@ -8387,16 +7135,8 @@
       <c r="G162" s="1" t="inlineStr"/>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
-      <c r="J162" s="1" t="inlineStr">
-        <is>
-          <t>L695: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: tions de 1803, il obtint un siÃ¨ge Ã la</t>
-        </is>
-      </c>
-      <c r="K162" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Juliette Williams, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J162" s="1" t="inlineStr"/>
+      <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
@@ -8412,7 +7152,7 @@
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard Levasseur, Ã©cole Grandin ......................</t>
+          <t>L268: punctuation artifact: repeated periods :: Gérard Levasseur, école Grandin ......................</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr"/>
@@ -8434,16 +7174,8 @@
       <c r="G163" s="1" t="inlineStr"/>
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
-      <c r="J163" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: earri presque aussi Ã© tonnante. Il na-</t>
-        </is>
-      </c>
-      <c r="K163" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Philippe HÃ©bert, Saint-Vincent ..................</t>
-        </is>
-      </c>
+      <c r="J163" s="1" t="inlineStr"/>
+      <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
@@ -8459,7 +7191,7 @@
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr">
         <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yvette Normand, ThÃ©rien ..............................</t>
+          <t>L270: punctuation artifact: repeated periods :: Yvette Normand, Thérien ..............................</t>
         </is>
       </c>
       <c r="R163" s="1" t="inlineStr"/>
@@ -8481,16 +7213,8 @@
       <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr"/>
-      <c r="J164" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s Ã© e, la pauvre ville, comme passent les</t>
-        </is>
-      </c>
-      <c r="K164" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le SÃ©guin, Bonnyville........................</t>
-        </is>
-      </c>
+      <c r="J164" s="1" t="inlineStr"/>
+      <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
@@ -8506,7 +7230,7 @@
       <c r="P164" s="1" t="inlineStr"/>
       <c r="Q164" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Raymond Sylvestre, Ã©cole Thibeault ...................</t>
+          <t>L272: punctuation artifact: repeated periods :: Raymond Sylvestre, école Thibeault ...................</t>
         </is>
       </c>
       <c r="R164" s="1" t="inlineStr"/>
@@ -8528,16 +7252,8 @@
       <c r="G165" s="1" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr"/>
-      <c r="J165" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dire autant que " t Ã© moin ", et pour avoir</t>
-        </is>
-      </c>
-      <c r="K165" s="1" t="inlineStr">
-        <is>
-          <t>L610: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Couture, Bonnyville .......................</t>
-        </is>
-      </c>
+      <c r="J165" s="1" t="inlineStr"/>
+      <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
@@ -8553,7 +7269,7 @@
       <c r="P165" s="1" t="inlineStr"/>
       <c r="Q165" s="1" t="inlineStr">
         <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 85 CÃ©cile Doucet. Tangente ............................</t>
+          <t>L274: punctuation artifact: repeated periods :: 85 Cécile Doucet. Tangente ............................</t>
         </is>
       </c>
       <c r="R165" s="1" t="inlineStr"/>
@@ -8575,16 +7291,8 @@
       <c r="G166" s="1" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr"/>
-      <c r="J166" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã© t Ã© tout remp Ã© du sang des chr Ã© tiens,</t>
-        </is>
-      </c>
-      <c r="K166" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gordon Miniely, ThÃ©rien Village</t>
-        </is>
-      </c>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
       <c r="L166" s="1" t="inlineStr"/>
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
@@ -8622,16 +7330,8 @@
       <c r="G167" s="1" t="inlineStr"/>
       <c r="H167" s="1" t="inlineStr"/>
       <c r="I167" s="1" t="inlineStr"/>
-      <c r="J167" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d Ã© signa unanimement comme pr Ã© sident</t>
-        </is>
-      </c>
-      <c r="K167" s="1" t="inlineStr">
-        <is>
-          <t>L616: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ;GrÃ©goire Ouellet, La Corey</t>
-        </is>
-      </c>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
       <c r="L167" s="1" t="inlineStr"/>
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
@@ -8647,7 +7347,7 @@
       <c r="P167" s="1" t="inlineStr"/>
       <c r="Q167" s="1" t="inlineStr">
         <is>
-          <t>L294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rollande Boulet, Ã©cole consolidÃ©e, Donnelly ..</t>
+          <t>L294: punctuation artifact: repeated periods :: Rollande Boulet, école consolidée, Donnelly ..</t>
         </is>
       </c>
       <c r="R167" s="1" t="inlineStr"/>
@@ -8669,16 +7369,8 @@
       <c r="G168" s="1" t="inlineStr"/>
       <c r="H168" s="1" t="inlineStr"/>
       <c r="I168" s="1" t="inlineStr"/>
-      <c r="J168" s="1" t="inlineStr">
-        <is>
-          <t>L708: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: f Ã© vrier 1831. II n'avait que dix-hut ans</t>
-        </is>
-      </c>
-      <c r="K168" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ! Jeannette Sylvestre, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
       <c r="L168" s="1" t="inlineStr"/>
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
@@ -8694,7 +7386,7 @@
       <c r="P168" s="1" t="inlineStr"/>
       <c r="Q168" s="1" t="inlineStr">
         <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rachel LabontÃ©, Ã©cole Thibeault ...........</t>
+          <t>L300: punctuation artifact: repeated periods :: Rachel Labonté, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R168" s="1" t="inlineStr"/>
@@ -8716,16 +7408,8 @@
       <c r="G169" s="1" t="inlineStr"/>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr"/>
-      <c r="J169" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: aussi les menaces de la ruine d Ã© finitive.</t>
-        </is>
-      </c>
-      <c r="K169" s="1" t="inlineStr">
-        <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: â€¢ IrÃ¨ne Lambert, Bonnyville .....................</t>
-        </is>
-      </c>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
       <c r="L169" s="1" t="inlineStr"/>
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
@@ -8741,7 +7425,7 @@
       <c r="P169" s="1" t="inlineStr"/>
       <c r="Q169" s="1" t="inlineStr">
         <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Patricia BÃ©land. Ã©cole Thibeault ...........</t>
+          <t>L302: punctuation artifact: repeated periods :: Patricia Béland. école Thibeault ...........</t>
         </is>
       </c>
       <c r="R169" s="1" t="inlineStr"/>
@@ -8763,16 +7447,8 @@
       <c r="G170" s="1" t="inlineStr"/>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr"/>
-      <c r="J170" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " Lefebvre Ã© tait l'un des plus intr</t>
-        </is>
-      </c>
-      <c r="K170" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
-        </is>
-      </c>
+      <c r="J170" s="1" t="inlineStr"/>
+      <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
@@ -8810,16 +7486,8 @@
       <c r="G171" s="1" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr"/>
-      <c r="J171" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: du Â· Conseil gislatif. Le scrutin m Ã© me</t>
-        </is>
-      </c>
-      <c r="K171" s="1" t="inlineStr">
-        <is>
-          <t>L635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
       <c r="L171" s="1" t="inlineStr"/>
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
@@ -8835,7 +7503,7 @@
       <c r="P171" s="1" t="inlineStr"/>
       <c r="Q171" s="1" t="inlineStr">
         <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard LabontÃ©, Ã©cole Thibeault .........</t>
+          <t>L306: punctuation artifact: repeated periods :: Léonard Labonté, école Thibeault .........</t>
         </is>
       </c>
       <c r="R171" s="1" t="inlineStr"/>
@@ -8857,16 +7525,8 @@
       <c r="G172" s="1" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr"/>
-      <c r="J172" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sorte que lâ€™erreur peut bien avoir eu des</t>
-        </is>
-      </c>
-      <c r="K172" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: 61 ThÃ©rÃ¨se Jubinville, Saint-Paul</t>
-        </is>
-      </c>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
       <c r="L172" s="1" t="inlineStr"/>
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
@@ -8904,16 +7564,8 @@
       <c r="G173" s="1" t="inlineStr"/>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr"/>
-      <c r="J173" s="1" t="inlineStr">
-        <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ment f Ã© d Ã© ral.</t>
-        </is>
-      </c>
-      <c r="K173" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 581 AndrÃ© Bouchard, Tangente ..........</t>
-        </is>
-      </c>
+      <c r="J173" s="1" t="inlineStr"/>
+      <c r="K173" s="1" t="inlineStr"/>
       <c r="L173" s="1" t="inlineStr"/>
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
@@ -8951,16 +7603,8 @@
       <c r="G174" s="1" t="inlineStr"/>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr"/>
-      <c r="J174" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: eut a subir, il r Ã© ussit Ã se constituer une</t>
-        </is>
-      </c>
-      <c r="K174" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorraine Lussier, Ã©cole consolidÃ©e, Donnelly 77</t>
-        </is>
-      </c>
+      <c r="J174" s="1" t="inlineStr"/>
+      <c r="K174" s="1" t="inlineStr"/>
       <c r="L174" s="1" t="inlineStr"/>
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
@@ -8998,16 +7642,8 @@
       <c r="G175" s="1" t="inlineStr"/>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr"/>
-      <c r="J175" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: " victimes ", quelquefois me trÃ¨s di-</t>
-        </is>
-      </c>
-      <c r="K175" s="1" t="inlineStr">
-        <is>
-          <t>L681: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Casavant, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J175" s="1" t="inlineStr"/>
+      <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
@@ -9023,7 +7659,7 @@
       <c r="P175" s="1" t="inlineStr"/>
       <c r="Q175" s="1" t="inlineStr">
         <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: IrÃ¨ne Caouette, Bonnyville ................</t>
+          <t>L314: punctuation artifact: repeated periods :: Irène Caouette, Bonnyville ................</t>
         </is>
       </c>
       <c r="R175" s="1" t="inlineStr"/>
@@ -9045,16 +7681,8 @@
       <c r="G176" s="1" t="inlineStr"/>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr"/>
-      <c r="J176" s="1" t="inlineStr">
-        <is>
-          <t>L721: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les renseignements pertinents exig Ã© s dans la formule</t>
-        </is>
-      </c>
-      <c r="K176" s="1" t="inlineStr">
-        <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Maurice Chevalier, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
       <c r="L176" s="1" t="inlineStr"/>
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
@@ -9070,7 +7698,7 @@
       <c r="P176" s="1" t="inlineStr"/>
       <c r="Q176" s="1" t="inlineStr">
         <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Sylvia Yakimchuk, ThÃ©rien Village ........</t>
+          <t>L316: punctuation artifact: repeated periods :: Sylvia Yakimchuk, Thérien Village ........</t>
         </is>
       </c>
       <c r="R176" s="1" t="inlineStr"/>
@@ -9092,16 +7720,8 @@
       <c r="G177" s="1" t="inlineStr"/>
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr"/>
-      <c r="J177" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: apr que l'on eut modifi Ã© sp Ã© cialement</t>
-        </is>
-      </c>
-      <c r="K177" s="1" t="inlineStr">
-        <is>
-          <t>L689: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Annette Comeau, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J177" s="1" t="inlineStr"/>
+      <c r="K177" s="1" t="inlineStr"/>
       <c r="L177" s="1" t="inlineStr"/>
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
@@ -9139,16 +7759,8 @@
       <c r="G178" s="1" t="inlineStr"/>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr"/>
-      <c r="J178" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: diens fran attir Ã© s par les d Ã© couver-</t>
-        </is>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©a Ricard, couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
       <c r="L178" s="1" t="inlineStr"/>
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
@@ -9186,16 +7798,8 @@
       <c r="G179" s="1" t="inlineStr"/>
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr"/>
-      <c r="J179" s="1" t="inlineStr">
-        <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnes de piti Ã©; mais la v Ã© rit Ã© seule a des</t>
-        </is>
-      </c>
-      <c r="K179" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: EvangÃ©line Gillon, Tangente .................</t>
-        </is>
-      </c>
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
       <c r="L179" s="1" t="inlineStr"/>
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
@@ -9211,7 +7815,7 @@
       <c r="P179" s="1" t="inlineStr"/>
       <c r="Q179" s="1" t="inlineStr">
         <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucille MahÃ©, Legal .......</t>
+          <t>L322: punctuation artifact: repeated periods :: Lucille Mahé, Legal .......</t>
         </is>
       </c>
       <c r="R179" s="1" t="inlineStr"/>
@@ -9233,16 +7837,8 @@
       <c r="G180" s="1" t="inlineStr"/>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr"/>
-      <c r="J180" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: " martyrs ". Ainsi l'ont entendu les P Ã¨-</t>
-        </is>
-      </c>
-      <c r="K180" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Euclide BÃ©rubÃ©, Beaumont .........</t>
-        </is>
-      </c>
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
       <c r="L180" s="1" t="inlineStr"/>
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
@@ -9258,7 +7854,7 @@
       <c r="P180" s="1" t="inlineStr"/>
       <c r="Q180" s="1" t="inlineStr">
         <is>
-          <t>L324: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§ois Blackburn, Ã©cole Grandin ........</t>
+          <t>L324: punctuation artifact: repeated periods :: François Blackburn, école Grandin ........</t>
         </is>
       </c>
       <c r="R180" s="1" t="inlineStr"/>
@@ -9280,16 +7876,8 @@
       <c r="G181" s="1" t="inlineStr"/>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr"/>
-      <c r="J181" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ses jambes. La diligence Ã© tait inconnue</t>
-        </is>
-      </c>
-      <c r="K181" s="1" t="inlineStr">
-        <is>
-          <t>L702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Ouellette, Ste-Lina</t>
-        </is>
-      </c>
+      <c r="J181" s="1" t="inlineStr"/>
+      <c r="K181" s="1" t="inlineStr"/>
       <c r="L181" s="1" t="inlineStr"/>
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
@@ -9327,16 +7915,8 @@
       <c r="G182" s="1" t="inlineStr"/>
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr"/>
-      <c r="J182" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: acceptÃ©es.</t>
-        </is>
-      </c>
-      <c r="K182" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Houde, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
       <c r="L182" s="1" t="inlineStr"/>
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
@@ -9374,16 +7954,8 @@
       <c r="G183" s="1" t="inlineStr"/>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr"/>
-      <c r="J183" s="1" t="inlineStr">
-        <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vait pas encore fait retentir les Ã© chos du</t>
-        </is>
-      </c>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marguerite Sabourin, Ã©cole Grandin</t>
-        </is>
-      </c>
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
       <c r="L183" s="1" t="inlineStr"/>
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
@@ -9399,7 +7971,7 @@
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, Ã©col eThibeault .........</t>
+          <t>L330: punctuation artifact: repeated periods | suspicious token(s): eThibeault (odd internal casing) :: Lorraine Tellier, écol eThibeault .........</t>
         </is>
       </c>
       <c r="R183" s="1" t="inlineStr"/>
@@ -9421,16 +7993,8 @@
       <c r="G184" s="1" t="inlineStr"/>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr"/>
-      <c r="J184" s="1" t="inlineStr">
-        <is>
-          <t>L749: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: compagnie de son frÃ¨re, Prudent, il or-</t>
-        </is>
-      </c>
-      <c r="K184" s="1" t="inlineStr">
-        <is>
-          <t>L718: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Juliette BÃ©rubÃ©, Beaumont</t>
-        </is>
-      </c>
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
       <c r="L184" s="1" t="inlineStr"/>
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
@@ -9468,16 +8032,8 @@
       <c r="G185" s="1" t="inlineStr"/>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr"/>
-      <c r="J185" s="1" t="inlineStr">
-        <is>
-          <t>L751: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: lac Sup Ã© rieur." Les voyageurs ne pou-</t>
-        </is>
-      </c>
-      <c r="K185" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Lemire, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="J185" s="1" t="inlineStr"/>
+      <c r="K185" s="1" t="inlineStr"/>
       <c r="L185" s="1" t="inlineStr"/>
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
@@ -9493,7 +8049,7 @@
       <c r="P185" s="1" t="inlineStr"/>
       <c r="Q185" s="1" t="inlineStr">
         <is>
-          <t>L334: punctuation artifact: repeated periods :: NoÃ«l Jacob, Tangente ..........</t>
+          <t>L334: punctuation artifact: repeated periods :: Noël Jacob, Tangente ..........</t>
         </is>
       </c>
       <c r="R185" s="1" t="inlineStr"/>
@@ -9515,16 +8071,8 @@
       <c r="G186" s="1" t="inlineStr"/>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr"/>
-      <c r="J186" s="1" t="inlineStr">
-        <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ti Ã© de la nuit Ã jouer. En se s Ã© parant,</t>
-        </is>
-      </c>
-      <c r="K186" s="1" t="inlineStr">
-        <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Dolores Comeau, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="J186" s="1" t="inlineStr"/>
+      <c r="K186" s="1" t="inlineStr"/>
       <c r="L186" s="1" t="inlineStr"/>
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
@@ -9562,16 +8110,8 @@
       <c r="G187" s="1" t="inlineStr"/>
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr"/>
-      <c r="J187" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: L'hon. Menard avait su l'acqu Ã© rir grÃ¢ce</t>
-        </is>
-      </c>
-      <c r="K187" s="1" t="inlineStr">
-        <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yolande Robert, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="J187" s="1" t="inlineStr"/>
+      <c r="K187" s="1" t="inlineStr"/>
       <c r="L187" s="1" t="inlineStr"/>
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
@@ -9609,16 +8149,8 @@
       <c r="G188" s="1" t="inlineStr"/>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr"/>
-      <c r="J188" s="1" t="inlineStr">
-        <is>
-          <t>L765: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chacun a gagn Ã© 40 francs, et que per-</t>
-        </is>
-      </c>
-      <c r="K188" s="1" t="inlineStr">
-        <is>
-          <t>L740: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Magnan, couvent Notre-Dame</t>
-        </is>
-      </c>
+      <c r="J188" s="1" t="inlineStr"/>
+      <c r="K188" s="1" t="inlineStr"/>
       <c r="L188" s="1" t="inlineStr"/>
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
@@ -9634,7 +8166,7 @@
       <c r="P188" s="1" t="inlineStr"/>
       <c r="Q188" s="1" t="inlineStr">
         <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Portelance. Tangente ..............</t>
+          <t>L340: punctuation artifact: repeated periods :: Thérèse Portelance. Tangente ..............</t>
         </is>
       </c>
       <c r="R188" s="1" t="inlineStr"/>
@@ -9656,16 +8188,8 @@
       <c r="G189" s="1" t="inlineStr"/>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr"/>
-      <c r="J189" s="1" t="inlineStr">
-        <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: r Ã© e presque l Ã© gendaire jusqu nos jours.</t>
-        </is>
-      </c>
-      <c r="K189" s="1" t="inlineStr">
-        <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Ronald Patry, Ã©cole Thibeault .....</t>
-        </is>
-      </c>
+      <c r="J189" s="1" t="inlineStr"/>
+      <c r="K189" s="1" t="inlineStr"/>
       <c r="L189" s="1" t="inlineStr"/>
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
@@ -9703,16 +8227,8 @@
       <c r="G190" s="1" t="inlineStr"/>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr"/>
-      <c r="J190" s="1" t="inlineStr">
-        <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mort les autorit Ã© s avaient donn Ã© le nom</t>
-        </is>
-      </c>
-      <c r="K190" s="1" t="inlineStr">
-        <is>
-          <t>L759: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Charles Bachand, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="J190" s="1" t="inlineStr"/>
+      <c r="K190" s="1" t="inlineStr"/>
       <c r="L190" s="1" t="inlineStr"/>
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
@@ -9750,16 +8266,8 @@
       <c r="G191" s="1" t="inlineStr"/>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr"/>
-      <c r="J191" s="1" t="inlineStr">
-        <is>
-          <t>L777: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Comment cela peut-il se faire?</t>
-        </is>
-      </c>
-      <c r="K191" s="1" t="inlineStr">
-        <is>
-          <t>L770: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 89 Roger Pariseau, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="J191" s="1" t="inlineStr"/>
+      <c r="K191" s="1" t="inlineStr"/>
       <c r="L191" s="1" t="inlineStr"/>
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
@@ -9775,7 +8283,7 @@
       <c r="P191" s="1" t="inlineStr"/>
       <c r="Q191" s="1" t="inlineStr">
         <is>
-          <t>L350: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marielle BÃ©land, Bonnyville ................</t>
+          <t>L350: punctuation artifact: repeated periods :: Marielle Béland, Bonnyville ................</t>
         </is>
       </c>
       <c r="R191" s="1" t="inlineStr"/>
@@ -9797,16 +8305,8 @@
       <c r="G192" s="1" t="inlineStr"/>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr"/>
-      <c r="J192" s="1" t="inlineStr">
-        <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Parkman a d Ã© sign Ã© Pierre M Ã© nard</t>
-        </is>
-      </c>
-      <c r="K192" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Bachand, Ã©cole Dunrobin.</t>
-        </is>
-      </c>
+      <c r="J192" s="1" t="inlineStr"/>
+      <c r="K192" s="1" t="inlineStr"/>
       <c r="L192" s="1" t="inlineStr"/>
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
@@ -9822,7 +8322,7 @@
       <c r="P192" s="1" t="inlineStr"/>
       <c r="Q192" s="1" t="inlineStr">
         <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roger Thibault, Ã©cole consolidÃ©e, Donnelly ...</t>
+          <t>L352: punctuation artifact: repeated periods :: Roger Thibault, école consolidée, Donnelly ...</t>
         </is>
       </c>
       <c r="R192" s="1" t="inlineStr"/>
@@ -9844,16 +8344,8 @@
       <c r="G193" s="1" t="inlineStr"/>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr"/>
-      <c r="J193" s="1" t="inlineStr">
-        <is>
-          <t>L782: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de M Ã© nard Ã l'un des comt Ã© s les plus</t>
-        </is>
-      </c>
-      <c r="K193" s="1" t="inlineStr">
-        <is>
-          <t>L774: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="J193" s="1" t="inlineStr"/>
+      <c r="K193" s="1" t="inlineStr"/>
       <c r="L193" s="1" t="inlineStr"/>
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
@@ -9891,16 +8383,8 @@
       <c r="G194" s="1" t="inlineStr"/>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr"/>
-      <c r="J194" s="1" t="inlineStr">
-        <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: terrible guerre de s Ã© cession lui permit</t>
-        </is>
-      </c>
-      <c r="K194" s="1" t="inlineStr">
-        <is>
-          <t>L780: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Anctil, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="J194" s="1" t="inlineStr"/>
+      <c r="K194" s="1" t="inlineStr"/>
       <c r="L194" s="1" t="inlineStr"/>
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
@@ -9916,7 +8400,7 @@
       <c r="P194" s="1" t="inlineStr"/>
       <c r="Q194" s="1" t="inlineStr">
         <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ! Germaine Ethier, Ã©cole Thibault ..........</t>
+          <t>L357: punctuation artifact: repeated periods :: ! Germaine Ethier, école Thibault ..........</t>
         </is>
       </c>
       <c r="R194" s="1" t="inlineStr"/>
@@ -9938,16 +8422,8 @@
       <c r="G195" s="1" t="inlineStr"/>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr"/>
-      <c r="J195" s="1" t="inlineStr">
-        <is>
-          <t>L784: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: - C'est que tous les quatre sont des les fatigues de la journÃ©e. Parmi ceux</t>
-        </is>
-      </c>
-      <c r="K195" s="1" t="inlineStr">
-        <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges ThÃ©berge, Legal</t>
-        </is>
-      </c>
+      <c r="J195" s="1" t="inlineStr"/>
+      <c r="K195" s="1" t="inlineStr"/>
       <c r="L195" s="1" t="inlineStr"/>
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
@@ -9963,7 +8439,7 @@
       <c r="P195" s="1" t="inlineStr"/>
       <c r="Q195" s="1" t="inlineStr">
         <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: |Raymond Ouellette. ThÃ©rien Village........</t>
+          <t>L359: punctuation artifact: repeated periods :: |Raymond Ouellette. Thérien Village........</t>
         </is>
       </c>
       <c r="R195" s="1" t="inlineStr"/>
@@ -9985,16 +8461,8 @@
       <c r="G196" s="1" t="inlineStr"/>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="1" t="inlineStr"/>
-      <c r="J196" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: qui beneficierent de ses connaissances, comme " le v Ã© n Ã© rable patriarche de l'Tl-</t>
-        </is>
-      </c>
-      <c r="K196" s="1" t="inlineStr">
-        <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Aquin, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="J196" s="1" t="inlineStr"/>
+      <c r="K196" s="1" t="inlineStr"/>
       <c r="L196" s="1" t="inlineStr"/>
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
@@ -10032,16 +8500,8 @@
       <c r="G197" s="1" t="inlineStr"/>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr"/>
-      <c r="J197" s="1" t="inlineStr">
-        <is>
-          <t>L787: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: de jouer un rÃ´le important. Il devint joueurs de violon.</t>
-        </is>
-      </c>
-      <c r="K197" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: i Colette BÃ©dard, Tangente</t>
-        </is>
-      </c>
+      <c r="J197" s="1" t="inlineStr"/>
+      <c r="K197" s="1" t="inlineStr"/>
       <c r="L197" s="1" t="inlineStr"/>
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
@@ -10057,7 +8517,7 @@
       <c r="P197" s="1" t="inlineStr"/>
       <c r="Q197" s="1" t="inlineStr">
         <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: | Madeleine Brissette, Ã©cole Grandin........</t>
+          <t>L363: punctuation artifact: repeated periods :: | Madeleine Brissette, école Grandin........</t>
         </is>
       </c>
       <c r="R197" s="1" t="inlineStr"/>
@@ -10080,11 +8540,7 @@
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr"/>
       <c r="J198" s="1" t="inlineStr"/>
-      <c r="K198" s="1" t="inlineStr">
-        <is>
-          <t>L873: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: JosÃ©phine L'Heureux, pensionnat de l'Assomption 51</t>
-        </is>
-      </c>
+      <c r="K198" s="1" t="inlineStr"/>
       <c r="L198" s="1" t="inlineStr"/>
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
@@ -10123,11 +8579,7 @@
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr"/>
       <c r="J199" s="1" t="inlineStr"/>
-      <c r="K199" s="1" t="inlineStr">
-        <is>
-          <t>L877: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Faucher, Saint-Paul ........................50</t>
-        </is>
-      </c>
+      <c r="K199" s="1" t="inlineStr"/>
       <c r="L199" s="1" t="inlineStr"/>
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
@@ -10166,11 +8618,7 @@
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr"/>
       <c r="J200" s="1" t="inlineStr"/>
-      <c r="K200" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Normand Maisonneuve, Ã©cole consolidÃ©e, Donnelly 50</t>
-        </is>
-      </c>
+      <c r="K200" s="1" t="inlineStr"/>
       <c r="L200" s="1" t="inlineStr"/>
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
@@ -10209,11 +8657,7 @@
       <c r="H201" s="1" t="inlineStr"/>
       <c r="I201" s="1" t="inlineStr"/>
       <c r="J201" s="1" t="inlineStr"/>
-      <c r="K201" s="1" t="inlineStr">
-        <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette PrÃ©fentaine, Legal ........</t>
-        </is>
-      </c>
+      <c r="K201" s="1" t="inlineStr"/>
       <c r="L201" s="1" t="inlineStr"/>
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
@@ -10252,11 +8696,7 @@
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr"/>
       <c r="J202" s="1" t="inlineStr"/>
-      <c r="K202" s="1" t="inlineStr">
-        <is>
-          <t>L964: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ferdinand Coulombe, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="K202" s="1" t="inlineStr"/>
       <c r="L202" s="1" t="inlineStr"/>
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
@@ -10295,11 +8735,7 @@
       <c r="H203" s="1" t="inlineStr"/>
       <c r="I203" s="1" t="inlineStr"/>
       <c r="J203" s="1" t="inlineStr"/>
-      <c r="K203" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Despins, Ã©cole Dunrobin .......</t>
-        </is>
-      </c>
+      <c r="K203" s="1" t="inlineStr"/>
       <c r="L203" s="1" t="inlineStr"/>
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
@@ -10338,11 +8774,7 @@
       <c r="H204" s="1" t="inlineStr"/>
       <c r="I204" s="1" t="inlineStr"/>
       <c r="J204" s="1" t="inlineStr"/>
-      <c r="K204" s="1" t="inlineStr">
-        <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Huguette HÃ©tu. Bonnyville .....................</t>
-        </is>
-      </c>
+      <c r="K204" s="1" t="inlineStr"/>
       <c r="L204" s="1" t="inlineStr"/>
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
@@ -10381,11 +8813,7 @@
       <c r="H205" s="1" t="inlineStr"/>
       <c r="I205" s="1" t="inlineStr"/>
       <c r="J205" s="1" t="inlineStr"/>
-      <c r="K205" s="1" t="inlineStr">
-        <is>
-          <t>L974: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doris Aubin, Ã©cole consolidÃ©e, Falher .........</t>
-        </is>
-      </c>
+      <c r="K205" s="1" t="inlineStr"/>
       <c r="L205" s="1" t="inlineStr"/>
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
@@ -10424,11 +8852,7 @@
       <c r="H206" s="1" t="inlineStr"/>
       <c r="I206" s="1" t="inlineStr"/>
       <c r="J206" s="1" t="inlineStr"/>
-      <c r="K206" s="1" t="inlineStr">
-        <is>
-          <t>L978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rosemary Heppeler, Ã©cole Thibeault ............</t>
-        </is>
-      </c>
+      <c r="K206" s="1" t="inlineStr"/>
       <c r="L206" s="1" t="inlineStr"/>
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
@@ -10467,11 +8891,7 @@
       <c r="H207" s="1" t="inlineStr"/>
       <c r="I207" s="1" t="inlineStr"/>
       <c r="J207" s="1" t="inlineStr"/>
-      <c r="K207" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland BÃ©rubÃ©. Beaumont .......................</t>
-        </is>
-      </c>
+      <c r="K207" s="1" t="inlineStr"/>
       <c r="L207" s="1" t="inlineStr"/>
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
@@ -10510,11 +8930,7 @@
       <c r="H208" s="1" t="inlineStr"/>
       <c r="I208" s="1" t="inlineStr"/>
       <c r="J208" s="1" t="inlineStr"/>
-      <c r="K208" s="1" t="inlineStr">
-        <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claudette BÃ©rubÃ©, Beaumont ....................</t>
-        </is>
-      </c>
+      <c r="K208" s="1" t="inlineStr"/>
       <c r="L208" s="1" t="inlineStr"/>
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
@@ -10553,11 +8969,7 @@
       <c r="H209" s="1" t="inlineStr"/>
       <c r="I209" s="1" t="inlineStr"/>
       <c r="J209" s="1" t="inlineStr"/>
-      <c r="K209" s="1" t="inlineStr">
-        <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Turcotte, Ã©cole Grandin .............</t>
-        </is>
-      </c>
+      <c r="K209" s="1" t="inlineStr"/>
       <c r="L209" s="1" t="inlineStr"/>
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
@@ -10596,11 +9008,7 @@
       <c r="H210" s="1" t="inlineStr"/>
       <c r="I210" s="1" t="inlineStr"/>
       <c r="J210" s="1" t="inlineStr"/>
-      <c r="K210" s="1" t="inlineStr">
-        <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Henri Roy, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K210" s="1" t="inlineStr"/>
       <c r="L210" s="1" t="inlineStr"/>
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
@@ -10639,11 +9047,7 @@
       <c r="H211" s="1" t="inlineStr"/>
       <c r="I211" s="1" t="inlineStr"/>
       <c r="J211" s="1" t="inlineStr"/>
-      <c r="K211" s="1" t="inlineStr">
-        <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Arcand, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="K211" s="1" t="inlineStr"/>
       <c r="L211" s="1" t="inlineStr"/>
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
@@ -10682,11 +9086,7 @@
       <c r="H212" s="1" t="inlineStr"/>
       <c r="I212" s="1" t="inlineStr"/>
       <c r="J212" s="1" t="inlineStr"/>
-      <c r="K212" s="1" t="inlineStr">
-        <is>
-          <t>L1012: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard HÃ©bert, Saint-Vincent .................</t>
-        </is>
-      </c>
+      <c r="K212" s="1" t="inlineStr"/>
       <c r="L212" s="1" t="inlineStr"/>
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
@@ -10725,11 +9125,7 @@
       <c r="H213" s="1" t="inlineStr"/>
       <c r="I213" s="1" t="inlineStr"/>
       <c r="J213" s="1" t="inlineStr"/>
-      <c r="K213" s="1" t="inlineStr">
-        <is>
-          <t>L1014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Tarcienne Meunier, Ã©cole Thibeault ............</t>
-        </is>
-      </c>
+      <c r="K213" s="1" t="inlineStr"/>
       <c r="L213" s="1" t="inlineStr"/>
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
@@ -10768,11 +9164,7 @@
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr"/>
       <c r="J214" s="1" t="inlineStr"/>
-      <c r="K214" s="1" t="inlineStr">
-        <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AdÃ©lard SÃ©guin, Bonnyville ....................</t>
-        </is>
-      </c>
+      <c r="K214" s="1" t="inlineStr"/>
       <c r="L214" s="1" t="inlineStr"/>
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
@@ -10811,11 +9203,7 @@
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr"/>
       <c r="J215" s="1" t="inlineStr"/>
-      <c r="K215" s="1" t="inlineStr">
-        <is>
-          <t>L1026: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RenÃ© Bruneau, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K215" s="1" t="inlineStr"/>
       <c r="L215" s="1" t="inlineStr"/>
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
@@ -10854,11 +9242,7 @@
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr"/>
       <c r="J216" s="1" t="inlineStr"/>
-      <c r="K216" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmen Tellier, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="K216" s="1" t="inlineStr"/>
       <c r="L216" s="1" t="inlineStr"/>
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
@@ -10897,11 +9281,7 @@
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr"/>
       <c r="J217" s="1" t="inlineStr"/>
-      <c r="K217" s="1" t="inlineStr">
-        <is>
-          <t>L1030: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Muriel Walker, Ã©cole Thibeault ...............</t>
-        </is>
-      </c>
+      <c r="K217" s="1" t="inlineStr"/>
       <c r="L217" s="1" t="inlineStr"/>
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
@@ -10940,11 +9320,7 @@
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr"/>
       <c r="J218" s="1" t="inlineStr"/>
-      <c r="K218" s="1" t="inlineStr">
-        <is>
-          <t>L1036: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lilianne Sabourin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="K218" s="1" t="inlineStr"/>
       <c r="L218" s="1" t="inlineStr"/>
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
@@ -10983,11 +9359,7 @@
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr"/>
       <c r="J219" s="1" t="inlineStr"/>
-      <c r="K219" s="1" t="inlineStr">
-        <is>
-          <t>L1038: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond PÃ©trin, Ã©cole Dunrobin</t>
-        </is>
-      </c>
+      <c r="K219" s="1" t="inlineStr"/>
       <c r="L219" s="1" t="inlineStr"/>
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
@@ -11026,11 +9398,7 @@
       <c r="H220" s="1" t="inlineStr"/>
       <c r="I220" s="1" t="inlineStr"/>
       <c r="J220" s="1" t="inlineStr"/>
-      <c r="K220" s="1" t="inlineStr">
-        <is>
-          <t>L1042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard-Meunier, Ã©cole Thibeault ..</t>
-        </is>
-      </c>
+      <c r="K220" s="1" t="inlineStr"/>
       <c r="L220" s="1" t="inlineStr"/>
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
@@ -11069,11 +9437,7 @@
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr"/>
       <c r="J221" s="1" t="inlineStr"/>
-      <c r="K221" s="1" t="inlineStr">
-        <is>
-          <t>L1081: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard Sauvageau. Ã©cole consolidÃ©e, Falher ............71</t>
-        </is>
-      </c>
+      <c r="K221" s="1" t="inlineStr"/>
       <c r="L221" s="1" t="inlineStr"/>
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
@@ -11089,7 +9453,7 @@
       <c r="P221" s="1" t="inlineStr"/>
       <c r="Q221" s="1" t="inlineStr">
         <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Laplante, Ã©cole Dunrobin ............</t>
+          <t>L452: punctuation artifact: repeated periods :: Albert Laplante, école Dunrobin ............</t>
         </is>
       </c>
       <c r="R221" s="1" t="inlineStr"/>
@@ -11112,11 +9476,7 @@
       <c r="H222" s="1" t="inlineStr"/>
       <c r="I222" s="1" t="inlineStr"/>
       <c r="J222" s="1" t="inlineStr"/>
-      <c r="K222" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Georges Voyer, Ã©cole Grandin ...........................70</t>
-        </is>
-      </c>
+      <c r="K222" s="1" t="inlineStr"/>
       <c r="L222" s="1" t="inlineStr"/>
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
@@ -11155,11 +9515,7 @@
       <c r="H223" s="1" t="inlineStr"/>
       <c r="I223" s="1" t="inlineStr"/>
       <c r="J223" s="1" t="inlineStr"/>
-      <c r="K223" s="1" t="inlineStr">
-        <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
-        </is>
-      </c>
+      <c r="K223" s="1" t="inlineStr"/>
       <c r="L223" s="1" t="inlineStr"/>
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
@@ -11198,11 +9554,7 @@
       <c r="H224" s="1" t="inlineStr"/>
       <c r="I224" s="1" t="inlineStr"/>
       <c r="J224" s="1" t="inlineStr"/>
-      <c r="K224" s="1" t="inlineStr">
-        <is>
-          <t>L1097: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Raymond Labrecque, Ã©cole consolidÃ©e, Donnelly .........70</t>
-        </is>
-      </c>
+      <c r="K224" s="1" t="inlineStr"/>
       <c r="L224" s="1" t="inlineStr"/>
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
@@ -11241,11 +9593,7 @@
       <c r="H225" s="1" t="inlineStr"/>
       <c r="I225" s="1" t="inlineStr"/>
       <c r="J225" s="1" t="inlineStr"/>
-      <c r="K225" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Hector Huot, Ã©cole Dunrobin ............................70</t>
-        </is>
-      </c>
+      <c r="K225" s="1" t="inlineStr"/>
       <c r="L225" s="1" t="inlineStr"/>
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
@@ -11261,7 +9609,7 @@
       <c r="P225" s="1" t="inlineStr"/>
       <c r="Q225" s="1" t="inlineStr">
         <is>
-          <t>L468: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rita Guibault, ThÃ©rien Village ...................</t>
+          <t>L468: punctuation artifact: repeated periods :: Rita Guibault, Thérien Village ...................</t>
         </is>
       </c>
       <c r="R225" s="1" t="inlineStr"/>
@@ -11284,11 +9632,7 @@
       <c r="H226" s="1" t="inlineStr"/>
       <c r="I226" s="1" t="inlineStr"/>
       <c r="J226" s="1" t="inlineStr"/>
-      <c r="K226" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rard l'AbbÃ©, Ã©cole consolidÃ©e, Falher ................70</t>
-        </is>
-      </c>
+      <c r="K226" s="1" t="inlineStr"/>
       <c r="L226" s="1" t="inlineStr"/>
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
@@ -11327,11 +9671,7 @@
       <c r="H227" s="1" t="inlineStr"/>
       <c r="I227" s="1" t="inlineStr"/>
       <c r="J227" s="1" t="inlineStr"/>
-      <c r="K227" s="1" t="inlineStr">
-        <is>
-          <t>L1103: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gilbert Proulx, Ã©cole consolidÃ©e, Falher ..............70</t>
-        </is>
-      </c>
+      <c r="K227" s="1" t="inlineStr"/>
       <c r="L227" s="1" t="inlineStr"/>
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
@@ -11347,7 +9687,7 @@
       <c r="P227" s="1" t="inlineStr"/>
       <c r="Q227" s="1" t="inlineStr">
         <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jeanne Charlier, Ã©cole Dunrobin ...................</t>
+          <t>L476: punctuation artifact: repeated periods :: Jeanne Charlier, école Dunrobin ...................</t>
         </is>
       </c>
       <c r="R227" s="1" t="inlineStr"/>
@@ -11370,11 +9710,7 @@
       <c r="H228" s="1" t="inlineStr"/>
       <c r="I228" s="1" t="inlineStr"/>
       <c r="J228" s="1" t="inlineStr"/>
-      <c r="K228" s="1" t="inlineStr">
-        <is>
-          <t>L1107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Emma GagnÃ©, Sainte-Lina ................................70</t>
-        </is>
-      </c>
+      <c r="K228" s="1" t="inlineStr"/>
       <c r="L228" s="1" t="inlineStr"/>
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
@@ -11390,7 +9726,7 @@
       <c r="P228" s="1" t="inlineStr"/>
       <c r="Q228" s="1" t="inlineStr">
         <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Trottier, Ã©cole Thibeault ...............</t>
+          <t>L478: punctuation artifact: repeated periods :: Françoise Trottier, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R228" s="1" t="inlineStr"/>
@@ -11413,11 +9749,7 @@
       <c r="H229" s="1" t="inlineStr"/>
       <c r="I229" s="1" t="inlineStr"/>
       <c r="J229" s="1" t="inlineStr"/>
-      <c r="K229" s="1" t="inlineStr">
-        <is>
-          <t>L1113: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RenÃ© Despins, Ã©cole consolidÃ©e, Falher .................68</t>
-        </is>
-      </c>
+      <c r="K229" s="1" t="inlineStr"/>
       <c r="L229" s="1" t="inlineStr"/>
       <c r="M229" s="1" t="inlineStr"/>
       <c r="N229" s="1" t="inlineStr">
@@ -11433,7 +9765,7 @@
       <c r="P229" s="1" t="inlineStr"/>
       <c r="Q229" s="1" t="inlineStr">
         <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcelle BÃ©langer, Plamondon ......................</t>
+          <t>L480: punctuation artifact: repeated periods :: Marcelle Bélanger, Plamondon ......................</t>
         </is>
       </c>
       <c r="R229" s="1" t="inlineStr"/>
@@ -11456,11 +9788,7 @@
       <c r="H230" s="1" t="inlineStr"/>
       <c r="I230" s="1" t="inlineStr"/>
       <c r="J230" s="1" t="inlineStr"/>
-      <c r="K230" s="1" t="inlineStr">
-        <is>
-          <t>L1115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger Lauzon, Ã©cole consolidÃ©e, Falher .................68</t>
-        </is>
-      </c>
+      <c r="K230" s="1" t="inlineStr"/>
       <c r="L230" s="1" t="inlineStr"/>
       <c r="M230" s="1" t="inlineStr"/>
       <c r="N230" s="1" t="inlineStr">
@@ -11476,7 +9804,7 @@
       <c r="P230" s="1" t="inlineStr"/>
       <c r="Q230" s="1" t="inlineStr">
         <is>
-          <t>L482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elsie Loch, ThÃ©rien Village .......................</t>
+          <t>L482: punctuation artifact: repeated periods :: Elsie Loch, Thérien Village .......................</t>
         </is>
       </c>
       <c r="R230" s="1" t="inlineStr"/>
@@ -11499,11 +9827,7 @@
       <c r="H231" s="1" t="inlineStr"/>
       <c r="I231" s="1" t="inlineStr"/>
       <c r="J231" s="1" t="inlineStr"/>
-      <c r="K231" s="1" t="inlineStr">
-        <is>
-          <t>L1268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Denise Beauchamp, Ã©cole consolidÃ©e, Donnelly ......68</t>
-        </is>
-      </c>
+      <c r="K231" s="1" t="inlineStr"/>
       <c r="L231" s="1" t="inlineStr"/>
       <c r="M231" s="1" t="inlineStr"/>
       <c r="N231" s="1" t="inlineStr">
@@ -11542,11 +9866,7 @@
       <c r="H232" s="1" t="inlineStr"/>
       <c r="I232" s="1" t="inlineStr"/>
       <c r="J232" s="1" t="inlineStr"/>
-      <c r="K232" s="1" t="inlineStr">
-        <is>
-          <t>L1270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Emilia Collin, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K232" s="1" t="inlineStr"/>
       <c r="L232" s="1" t="inlineStr"/>
       <c r="M232" s="1" t="inlineStr"/>
       <c r="N232" s="1" t="inlineStr">
@@ -11585,11 +9905,7 @@
       <c r="H233" s="1" t="inlineStr"/>
       <c r="I233" s="1" t="inlineStr"/>
       <c r="J233" s="1" t="inlineStr"/>
-      <c r="K233" s="1" t="inlineStr">
-        <is>
-          <t>L1272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fernande TieuliÃ©, Legal .................</t>
-        </is>
-      </c>
+      <c r="K233" s="1" t="inlineStr"/>
       <c r="L233" s="1" t="inlineStr"/>
       <c r="M233" s="1" t="inlineStr"/>
       <c r="N233" s="1" t="inlineStr">
@@ -11628,11 +9944,7 @@
       <c r="H234" s="1" t="inlineStr"/>
       <c r="I234" s="1" t="inlineStr"/>
       <c r="J234" s="1" t="inlineStr"/>
-      <c r="K234" s="1" t="inlineStr">
-        <is>
-          <t>L1274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Tessier, Ã©cole Grandin ..............</t>
-        </is>
-      </c>
+      <c r="K234" s="1" t="inlineStr"/>
       <c r="L234" s="1" t="inlineStr"/>
       <c r="M234" s="1" t="inlineStr"/>
       <c r="N234" s="1" t="inlineStr">
@@ -11671,11 +9983,7 @@
       <c r="H235" s="1" t="inlineStr"/>
       <c r="I235" s="1" t="inlineStr"/>
       <c r="J235" s="1" t="inlineStr"/>
-      <c r="K235" s="1" t="inlineStr">
-        <is>
-          <t>L1276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jacques Voyer, Ã©cole Thibeault .........</t>
-        </is>
-      </c>
+      <c r="K235" s="1" t="inlineStr"/>
       <c r="L235" s="1" t="inlineStr"/>
       <c r="M235" s="1" t="inlineStr"/>
       <c r="N235" s="1" t="inlineStr">
@@ -11691,7 +9999,7 @@
       <c r="P235" s="1" t="inlineStr"/>
       <c r="Q235" s="1" t="inlineStr">
         <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Georges Pilon, Ã©cole Grandin ......................</t>
+          <t>L498: punctuation artifact: repeated periods :: Georges Pilon, école Grandin ......................</t>
         </is>
       </c>
       <c r="R235" s="1" t="inlineStr"/>
@@ -11714,11 +10022,7 @@
       <c r="H236" s="1" t="inlineStr"/>
       <c r="I236" s="1" t="inlineStr"/>
       <c r="J236" s="1" t="inlineStr"/>
-      <c r="K236" s="1" t="inlineStr">
-        <is>
-          <t>L1280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: BÃ©atrice Hurtubise, Saint-Paul .......</t>
-        </is>
-      </c>
+      <c r="K236" s="1" t="inlineStr"/>
       <c r="L236" s="1" t="inlineStr"/>
       <c r="M236" s="1" t="inlineStr"/>
       <c r="N236" s="1" t="inlineStr">
@@ -11734,7 +10038,7 @@
       <c r="P236" s="1" t="inlineStr"/>
       <c r="Q236" s="1" t="inlineStr">
         <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Henri VallÃ©e, Beaumont ............................</t>
+          <t>L500: punctuation artifact: repeated periods :: Henri Vallée, Beaumont ............................</t>
         </is>
       </c>
       <c r="R236" s="1" t="inlineStr"/>
@@ -11757,11 +10061,7 @@
       <c r="H237" s="1" t="inlineStr"/>
       <c r="I237" s="1" t="inlineStr"/>
       <c r="J237" s="1" t="inlineStr"/>
-      <c r="K237" s="1" t="inlineStr">
-        <is>
-          <t>L1290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: !GÃ©rard Garand, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K237" s="1" t="inlineStr"/>
       <c r="L237" s="1" t="inlineStr"/>
       <c r="M237" s="1" t="inlineStr"/>
       <c r="N237" s="1" t="inlineStr">
@@ -11800,11 +10100,7 @@
       <c r="H238" s="1" t="inlineStr"/>
       <c r="I238" s="1" t="inlineStr"/>
       <c r="J238" s="1" t="inlineStr"/>
-      <c r="K238" s="1" t="inlineStr">
-        <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86 RÃ©al Demers, Beaumont..........................</t>
-        </is>
-      </c>
+      <c r="K238" s="1" t="inlineStr"/>
       <c r="L238" s="1" t="inlineStr"/>
       <c r="M238" s="1" t="inlineStr"/>
       <c r="N238" s="1" t="inlineStr">
@@ -11843,11 +10139,7 @@
       <c r="H239" s="1" t="inlineStr"/>
       <c r="I239" s="1" t="inlineStr"/>
       <c r="J239" s="1" t="inlineStr"/>
-      <c r="K239" s="1" t="inlineStr">
-        <is>
-          <t>L1294: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita Beauchamp, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K239" s="1" t="inlineStr"/>
       <c r="L239" s="1" t="inlineStr"/>
       <c r="M239" s="1" t="inlineStr"/>
       <c r="N239" s="1" t="inlineStr">
@@ -11886,11 +10178,7 @@
       <c r="H240" s="1" t="inlineStr"/>
       <c r="I240" s="1" t="inlineStr"/>
       <c r="J240" s="1" t="inlineStr"/>
-      <c r="K240" s="1" t="inlineStr">
-        <is>
-          <t>L1302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K240" s="1" t="inlineStr"/>
       <c r="L240" s="1" t="inlineStr"/>
       <c r="M240" s="1" t="inlineStr"/>
       <c r="N240" s="1" t="inlineStr">
@@ -11929,11 +10217,7 @@
       <c r="H241" s="1" t="inlineStr"/>
       <c r="I241" s="1" t="inlineStr"/>
       <c r="J241" s="1" t="inlineStr"/>
-      <c r="K241" s="1" t="inlineStr">
-        <is>
-          <t>L1304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86, Roland SÃ©guin, Ã©cole Dunrobin .................</t>
-        </is>
-      </c>
+      <c r="K241" s="1" t="inlineStr"/>
       <c r="L241" s="1" t="inlineStr"/>
       <c r="M241" s="1" t="inlineStr"/>
       <c r="N241" s="1" t="inlineStr">
@@ -11972,11 +10256,7 @@
       <c r="H242" s="1" t="inlineStr"/>
       <c r="I242" s="1" t="inlineStr"/>
       <c r="J242" s="1" t="inlineStr"/>
-      <c r="K242" s="1" t="inlineStr">
-        <is>
-          <t>L1310: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 86 RÃ©jeanne l'Oiseau, Ã©cole consolidÃ©e, Falher.</t>
-        </is>
-      </c>
+      <c r="K242" s="1" t="inlineStr"/>
       <c r="L242" s="1" t="inlineStr"/>
       <c r="M242" s="1" t="inlineStr"/>
       <c r="N242" s="1" t="inlineStr">
@@ -11992,7 +10272,7 @@
       <c r="P242" s="1" t="inlineStr"/>
       <c r="Q242" s="1" t="inlineStr">
         <is>
-          <t>L534: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©on Handfield, Beaumont ..........................</t>
+          <t>L534: punctuation artifact: repeated periods :: Léon Handfield, Beaumont ..........................</t>
         </is>
       </c>
       <c r="R242" s="1" t="inlineStr"/>
@@ -12015,11 +10295,7 @@
       <c r="H243" s="1" t="inlineStr"/>
       <c r="I243" s="1" t="inlineStr"/>
       <c r="J243" s="1" t="inlineStr"/>
-      <c r="K243" s="1" t="inlineStr">
-        <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
-        </is>
-      </c>
+      <c r="K243" s="1" t="inlineStr"/>
       <c r="L243" s="1" t="inlineStr"/>
       <c r="M243" s="1" t="inlineStr"/>
       <c r="N243" s="1" t="inlineStr">
@@ -12058,11 +10334,7 @@
       <c r="H244" s="1" t="inlineStr"/>
       <c r="I244" s="1" t="inlineStr"/>
       <c r="J244" s="1" t="inlineStr"/>
-      <c r="K244" s="1" t="inlineStr">
-        <is>
-          <t>L1376: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lorne BeauprÃ©, Bonnyville</t>
-        </is>
-      </c>
+      <c r="K244" s="1" t="inlineStr"/>
       <c r="L244" s="1" t="inlineStr"/>
       <c r="M244" s="1" t="inlineStr"/>
       <c r="N244" s="1" t="inlineStr">
@@ -12101,11 +10373,7 @@
       <c r="H245" s="1" t="inlineStr"/>
       <c r="I245" s="1" t="inlineStr"/>
       <c r="J245" s="1" t="inlineStr"/>
-      <c r="K245" s="1" t="inlineStr">
-        <is>
-          <t>L1380: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gertrude Brochu, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="K245" s="1" t="inlineStr"/>
       <c r="L245" s="1" t="inlineStr"/>
       <c r="M245" s="1" t="inlineStr"/>
       <c r="N245" s="1" t="inlineStr">
@@ -12121,7 +10389,7 @@
       <c r="P245" s="1" t="inlineStr"/>
       <c r="Q245" s="1" t="inlineStr">
         <is>
-          <t>L542: punctuation artifact: repeated periods :: NoÃ«l Ouellette, Sainte-Lina .......................</t>
+          <t>L542: punctuation artifact: repeated periods :: Noël Ouellette, Sainte-Lina .......................</t>
         </is>
       </c>
       <c r="R245" s="1" t="inlineStr"/>
@@ -12144,11 +10412,7 @@
       <c r="H246" s="1" t="inlineStr"/>
       <c r="I246" s="1" t="inlineStr"/>
       <c r="J246" s="1" t="inlineStr"/>
-      <c r="K246" s="1" t="inlineStr">
-        <is>
-          <t>L1386: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ernest Aquin, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="K246" s="1" t="inlineStr"/>
       <c r="L246" s="1" t="inlineStr"/>
       <c r="M246" s="1" t="inlineStr"/>
       <c r="N246" s="1" t="inlineStr">
@@ -12164,7 +10428,7 @@
       <c r="P246" s="1" t="inlineStr"/>
       <c r="Q246" s="1" t="inlineStr">
         <is>
-          <t>L546: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Paquette, Bonnyville ......................</t>
+          <t>L546: punctuation artifact: repeated periods :: Thérèse Paquette, Bonnyville ......................</t>
         </is>
       </c>
       <c r="R246" s="1" t="inlineStr"/>
@@ -12187,11 +10451,7 @@
       <c r="H247" s="1" t="inlineStr"/>
       <c r="I247" s="1" t="inlineStr"/>
       <c r="J247" s="1" t="inlineStr"/>
-      <c r="K247" s="1" t="inlineStr">
-        <is>
-          <t>L1394: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: : HÃ©lÃ¨ne Normand, ThÃ©rien Village ...............</t>
-        </is>
-      </c>
+      <c r="K247" s="1" t="inlineStr"/>
       <c r="L247" s="1" t="inlineStr"/>
       <c r="M247" s="1" t="inlineStr"/>
       <c r="N247" s="1" t="inlineStr">
@@ -12230,11 +10490,7 @@
       <c r="H248" s="1" t="inlineStr"/>
       <c r="I248" s="1" t="inlineStr"/>
       <c r="J248" s="1" t="inlineStr"/>
-      <c r="K248" s="1" t="inlineStr">
-        <is>
-          <t>L1396: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Robert BÃ©rubÃ©. Beaumont</t>
-        </is>
-      </c>
+      <c r="K248" s="1" t="inlineStr"/>
       <c r="L248" s="1" t="inlineStr"/>
       <c r="M248" s="1" t="inlineStr"/>
       <c r="N248" s="1" t="inlineStr">
@@ -12273,11 +10529,7 @@
       <c r="H249" s="1" t="inlineStr"/>
       <c r="I249" s="1" t="inlineStr"/>
       <c r="J249" s="1" t="inlineStr"/>
-      <c r="K249" s="1" t="inlineStr">
-        <is>
-          <t>L1398: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierrette Lauzon, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K249" s="1" t="inlineStr"/>
       <c r="L249" s="1" t="inlineStr"/>
       <c r="M249" s="1" t="inlineStr"/>
       <c r="N249" s="1" t="inlineStr">
@@ -12293,7 +10545,7 @@
       <c r="P249" s="1" t="inlineStr"/>
       <c r="Q249" s="1" t="inlineStr">
         <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: PhilomÃ¨ne Frigon, Saint-Vincent ...................</t>
+          <t>L552: punctuation artifact: repeated periods :: Philomène Frigon, Saint-Vincent ...................</t>
         </is>
       </c>
       <c r="R249" s="1" t="inlineStr"/>
@@ -12316,11 +10568,7 @@
       <c r="H250" s="1" t="inlineStr"/>
       <c r="I250" s="1" t="inlineStr"/>
       <c r="J250" s="1" t="inlineStr"/>
-      <c r="K250" s="1" t="inlineStr">
-        <is>
-          <t>L1400: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: IrÃ¨ne Paul, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K250" s="1" t="inlineStr"/>
       <c r="L250" s="1" t="inlineStr"/>
       <c r="M250" s="1" t="inlineStr"/>
       <c r="N250" s="1" t="inlineStr">
@@ -12336,7 +10584,7 @@
       <c r="P250" s="1" t="inlineStr"/>
       <c r="Q250" s="1" t="inlineStr">
         <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Dame, Ã©cole Grandin .........................</t>
+          <t>L554: punctuation artifact: repeated periods :: Alice Dame, école Grandin .........................</t>
         </is>
       </c>
       <c r="R250" s="1" t="inlineStr"/>
@@ -12359,16 +10607,12 @@
       <c r="H251" s="1" t="inlineStr"/>
       <c r="I251" s="1" t="inlineStr"/>
       <c r="J251" s="1" t="inlineStr"/>
-      <c r="K251" s="1" t="inlineStr">
-        <is>
-          <t>L1404: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: GÃ©rald Lapointe, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K251" s="1" t="inlineStr"/>
       <c r="L251" s="1" t="inlineStr"/>
       <c r="M251" s="1" t="inlineStr"/>
       <c r="N251" s="1" t="inlineStr">
         <is>
-          <t>L588: symbol-only separator/garbage line :: (1815-1871)</t>
+          <t>L583: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
         </is>
       </c>
       <c r="O251" s="1" t="inlineStr">
@@ -12402,16 +10646,12 @@
       <c r="H252" s="1" t="inlineStr"/>
       <c r="I252" s="1" t="inlineStr"/>
       <c r="J252" s="1" t="inlineStr"/>
-      <c r="K252" s="1" t="inlineStr">
-        <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Maurier, Legal ...........................</t>
-        </is>
-      </c>
+      <c r="K252" s="1" t="inlineStr"/>
       <c r="L252" s="1" t="inlineStr"/>
       <c r="M252" s="1" t="inlineStr"/>
       <c r="N252" s="1" t="inlineStr">
         <is>
-          <t>L605: isolated marker/symbol line :: *</t>
+          <t>L588: symbol-only separator/garbage line :: (1815-1871)</t>
         </is>
       </c>
       <c r="O252" s="1" t="inlineStr">
@@ -12445,16 +10685,12 @@
       <c r="H253" s="1" t="inlineStr"/>
       <c r="I253" s="1" t="inlineStr"/>
       <c r="J253" s="1" t="inlineStr"/>
-      <c r="K253" s="1" t="inlineStr">
-        <is>
-          <t>L1412: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rita TieuliÃ©, Legal</t>
-        </is>
-      </c>
+      <c r="K253" s="1" t="inlineStr"/>
       <c r="L253" s="1" t="inlineStr"/>
       <c r="M253" s="1" t="inlineStr"/>
       <c r="N253" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: *</t>
+          <t>L605: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O253" s="1" t="inlineStr">
@@ -12488,16 +10724,12 @@
       <c r="H254" s="1" t="inlineStr"/>
       <c r="I254" s="1" t="inlineStr"/>
       <c r="J254" s="1" t="inlineStr"/>
-      <c r="K254" s="1" t="inlineStr">
-        <is>
-          <t>L1414: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©on Schayes, Ã©cole Thibeault</t>
-        </is>
-      </c>
+      <c r="K254" s="1" t="inlineStr"/>
       <c r="L254" s="1" t="inlineStr"/>
       <c r="M254" s="1" t="inlineStr"/>
       <c r="N254" s="1" t="inlineStr">
         <is>
-          <t>L607: isolated marker/symbol line :: *</t>
+          <t>L606: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O254" s="1" t="inlineStr">
@@ -12508,7 +10740,7 @@
       <c r="P254" s="1" t="inlineStr"/>
       <c r="Q254" s="1" t="inlineStr">
         <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alfred ThÃ©berge, Legal ............................</t>
+          <t>L564: punctuation artifact: repeated periods :: Alfred Théberge, Legal ............................</t>
         </is>
       </c>
       <c r="R254" s="1" t="inlineStr"/>
@@ -12531,16 +10763,12 @@
       <c r="H255" s="1" t="inlineStr"/>
       <c r="I255" s="1" t="inlineStr"/>
       <c r="J255" s="1" t="inlineStr"/>
-      <c r="K255" s="1" t="inlineStr">
-        <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© La Brie, Fort Kent .................</t>
-        </is>
-      </c>
+      <c r="K255" s="1" t="inlineStr"/>
       <c r="L255" s="1" t="inlineStr"/>
       <c r="M255" s="1" t="inlineStr"/>
       <c r="N255" s="1" t="inlineStr">
         <is>
-          <t>L616: symbol-only separator/garbage line :: (1767-1844)</t>
+          <t>L607: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O255" s="1" t="inlineStr">
@@ -12551,7 +10779,7 @@
       <c r="P255" s="1" t="inlineStr"/>
       <c r="Q255" s="1" t="inlineStr">
         <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: CÃ©cile Bonin, La Corey ............................</t>
+          <t>L566: punctuation artifact: repeated periods :: Cécile Bonin, La Corey ............................</t>
         </is>
       </c>
       <c r="R255" s="1" t="inlineStr"/>
@@ -12574,16 +10802,12 @@
       <c r="H256" s="1" t="inlineStr"/>
       <c r="I256" s="1" t="inlineStr"/>
       <c r="J256" s="1" t="inlineStr"/>
-      <c r="K256" s="1" t="inlineStr">
-        <is>
-          <t>L1418: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 86 : Pierre Despins, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K256" s="1" t="inlineStr"/>
       <c r="L256" s="1" t="inlineStr"/>
       <c r="M256" s="1" t="inlineStr"/>
       <c r="N256" s="1" t="inlineStr">
         <is>
-          <t>L631: isolated marker/symbol line :: S</t>
+          <t>L616: symbol-only separator/garbage line :: (1767-1844)</t>
         </is>
       </c>
       <c r="O256" s="1" t="inlineStr">
@@ -12594,7 +10818,7 @@
       <c r="P256" s="1" t="inlineStr"/>
       <c r="Q256" s="1" t="inlineStr">
         <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: I NoÃ«l ChÃ©nard, Tangente ........................</t>
+          <t>L568: punctuation artifact: repeated periods :: I Noël Chénard, Tangente ........................</t>
         </is>
       </c>
       <c r="R256" s="1" t="inlineStr"/>
@@ -12617,16 +10841,12 @@
       <c r="H257" s="1" t="inlineStr"/>
       <c r="I257" s="1" t="inlineStr"/>
       <c r="J257" s="1" t="inlineStr"/>
-      <c r="K257" s="1" t="inlineStr">
-        <is>
-          <t>L1442: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Petersen, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="K257" s="1" t="inlineStr"/>
       <c r="L257" s="1" t="inlineStr"/>
       <c r="M257" s="1" t="inlineStr"/>
       <c r="N257" s="1" t="inlineStr">
         <is>
-          <t>L638: isolated marker/symbol line :: *</t>
+          <t>L631: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O257" s="1" t="inlineStr">
@@ -12637,7 +10857,7 @@
       <c r="P257" s="1" t="inlineStr"/>
       <c r="Q257" s="1" t="inlineStr">
         <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Anita St-Arneault, Ã©cole Grandin ................</t>
+          <t>L570: punctuation artifact: repeated periods :: Anita St-Arneault, école Grandin ................</t>
         </is>
       </c>
       <c r="R257" s="1" t="inlineStr"/>
@@ -12660,16 +10880,12 @@
       <c r="H258" s="1" t="inlineStr"/>
       <c r="I258" s="1" t="inlineStr"/>
       <c r="J258" s="1" t="inlineStr"/>
-      <c r="K258" s="1" t="inlineStr">
-        <is>
-          <t>L1446: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©cile Isabel, Ã©cole consolidÃ©e, Falher ...........86</t>
-        </is>
-      </c>
+      <c r="K258" s="1" t="inlineStr"/>
       <c r="L258" s="1" t="inlineStr"/>
       <c r="M258" s="1" t="inlineStr"/>
       <c r="N258" s="1" t="inlineStr">
         <is>
-          <t>L639: isolated marker/symbol line :: *</t>
+          <t>L638: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O258" s="1" t="inlineStr">
@@ -12680,7 +10896,7 @@
       <c r="P258" s="1" t="inlineStr"/>
       <c r="Q258" s="1" t="inlineStr">
         <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorette Tellier, Ã©cole Thibeault ................</t>
+          <t>L574: punctuation artifact: repeated periods :: Lorette Tellier, école Thibeault ................</t>
         </is>
       </c>
       <c r="R258" s="1" t="inlineStr"/>
@@ -12703,16 +10919,12 @@
       <c r="H259" s="1" t="inlineStr"/>
       <c r="I259" s="1" t="inlineStr"/>
       <c r="J259" s="1" t="inlineStr"/>
-      <c r="K259" s="1" t="inlineStr">
-        <is>
-          <t>L1448: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: CÃ©line Coulombe, Ã©cole Dunrobin 86</t>
-        </is>
-      </c>
+      <c r="K259" s="1" t="inlineStr"/>
       <c r="L259" s="1" t="inlineStr"/>
       <c r="M259" s="1" t="inlineStr"/>
       <c r="N259" s="1" t="inlineStr">
         <is>
-          <t>L640: isolated marker/symbol line :: *</t>
+          <t>L639: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O259" s="1" t="inlineStr">
@@ -12746,16 +10958,12 @@
       <c r="H260" s="1" t="inlineStr"/>
       <c r="I260" s="1" t="inlineStr"/>
       <c r="J260" s="1" t="inlineStr"/>
-      <c r="K260" s="1" t="inlineStr">
-        <is>
-          <t>L1452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Billy Dubois, Ã©cole Dunrobin ..............</t>
-        </is>
-      </c>
+      <c r="K260" s="1" t="inlineStr"/>
       <c r="L260" s="1" t="inlineStr"/>
       <c r="M260" s="1" t="inlineStr"/>
       <c r="N260" s="1" t="inlineStr">
         <is>
-          <t>L654: symbol-only separator/garbage line :: (1831-?)</t>
+          <t>L640: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O260" s="1" t="inlineStr">
@@ -12766,7 +10974,7 @@
       <c r="P260" s="1" t="inlineStr"/>
       <c r="Q260" s="1" t="inlineStr">
         <is>
-          <t>L580: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© BeauprÃ©, Bonnyville .......................</t>
+          <t>L580: punctuation artifact: repeated periods :: André Beaupré, Bonnyville .......................</t>
         </is>
       </c>
       <c r="R260" s="1" t="inlineStr"/>
@@ -12789,16 +10997,12 @@
       <c r="H261" s="1" t="inlineStr"/>
       <c r="I261" s="1" t="inlineStr"/>
       <c r="J261" s="1" t="inlineStr"/>
-      <c r="K261" s="1" t="inlineStr">
-        <is>
-          <t>L1453: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jacques Johnson, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K261" s="1" t="inlineStr"/>
       <c r="L261" s="1" t="inlineStr"/>
       <c r="M261" s="1" t="inlineStr"/>
       <c r="N261" s="1" t="inlineStr">
         <is>
-          <t>L788: isolated marker/symbol line :: 4</t>
+          <t>L654: symbol-only separator/garbage line :: (1831-?)</t>
         </is>
       </c>
       <c r="O261" s="1" t="inlineStr">
@@ -12832,14 +11036,14 @@
       <c r="H262" s="1" t="inlineStr"/>
       <c r="I262" s="1" t="inlineStr"/>
       <c r="J262" s="1" t="inlineStr"/>
-      <c r="K262" s="1" t="inlineStr">
-        <is>
-          <t>L1482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard Rousseau, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="K262" s="1" t="inlineStr"/>
       <c r="L262" s="1" t="inlineStr"/>
       <c r="M262" s="1" t="inlineStr"/>
-      <c r="N262" s="1" t="inlineStr"/>
+      <c r="N262" s="1" t="inlineStr">
+        <is>
+          <t>L788: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="O262" s="1" t="inlineStr">
         <is>
           <t>L1334: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...65</t>
@@ -12848,7 +11052,7 @@
       <c r="P262" s="1" t="inlineStr"/>
       <c r="Q262" s="1" t="inlineStr">
         <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland Carriere, Ã©cole Dunrobin .................</t>
+          <t>L586: punctuation artifact: repeated periods :: Roland Carriere, école Dunrobin .................</t>
         </is>
       </c>
       <c r="R262" s="1" t="inlineStr"/>
@@ -12871,11 +11075,7 @@
       <c r="H263" s="1" t="inlineStr"/>
       <c r="I263" s="1" t="inlineStr"/>
       <c r="J263" s="1" t="inlineStr"/>
-      <c r="K263" s="1" t="inlineStr">
-        <is>
-          <t>L1484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Charles Ouellette, ThÃ©rien Village ..........</t>
-        </is>
-      </c>
+      <c r="K263" s="1" t="inlineStr"/>
       <c r="L263" s="1" t="inlineStr"/>
       <c r="M263" s="1" t="inlineStr"/>
       <c r="N263" s="1" t="inlineStr"/>
@@ -12887,7 +11087,7 @@
       <c r="P263" s="1" t="inlineStr"/>
       <c r="Q263" s="1" t="inlineStr">
         <is>
-          <t>L590: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: HervÃ© Ouellette, Sainte-Lina ....................</t>
+          <t>L590: punctuation artifact: repeated periods :: Hervé Ouellette, Sainte-Lina ....................</t>
         </is>
       </c>
       <c r="R263" s="1" t="inlineStr"/>
@@ -12910,11 +11110,7 @@
       <c r="H264" s="1" t="inlineStr"/>
       <c r="I264" s="1" t="inlineStr"/>
       <c r="J264" s="1" t="inlineStr"/>
-      <c r="K264" s="1" t="inlineStr">
-        <is>
-          <t>L1486: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Adonis Emard, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K264" s="1" t="inlineStr"/>
       <c r="L264" s="1" t="inlineStr"/>
       <c r="M264" s="1" t="inlineStr"/>
       <c r="N264" s="1" t="inlineStr"/>
@@ -12949,11 +11145,7 @@
       <c r="H265" s="1" t="inlineStr"/>
       <c r="I265" s="1" t="inlineStr"/>
       <c r="J265" s="1" t="inlineStr"/>
-      <c r="K265" s="1" t="inlineStr">
-        <is>
-          <t>L1488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gagnon, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="K265" s="1" t="inlineStr"/>
       <c r="L265" s="1" t="inlineStr"/>
       <c r="M265" s="1" t="inlineStr"/>
       <c r="N265" s="1" t="inlineStr"/>
@@ -12988,11 +11180,7 @@
       <c r="H266" s="1" t="inlineStr"/>
       <c r="I266" s="1" t="inlineStr"/>
       <c r="J266" s="1" t="inlineStr"/>
-      <c r="K266" s="1" t="inlineStr">
-        <is>
-          <t>L1490: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Annette Lessard, Ã©cole consolidÃ©e, Falher ...</t>
-        </is>
-      </c>
+      <c r="K266" s="1" t="inlineStr"/>
       <c r="L266" s="1" t="inlineStr"/>
       <c r="M266" s="1" t="inlineStr"/>
       <c r="N266" s="1" t="inlineStr"/>
@@ -13004,7 +11192,7 @@
       <c r="P266" s="1" t="inlineStr"/>
       <c r="Q266" s="1" t="inlineStr">
         <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Philippe HÃ©bert, Saint-Vincent ..................</t>
+          <t>L604: punctuation artifact: repeated periods :: Philippe Hébert, Saint-Vincent ..................</t>
         </is>
       </c>
       <c r="R266" s="1" t="inlineStr"/>
@@ -13027,11 +11215,7 @@
       <c r="H267" s="1" t="inlineStr"/>
       <c r="I267" s="1" t="inlineStr"/>
       <c r="J267" s="1" t="inlineStr"/>
-      <c r="K267" s="1" t="inlineStr">
-        <is>
-          <t>L1498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lilianne Doran, Ã©cole consolidÃ©e, Falher ....</t>
-        </is>
-      </c>
+      <c r="K267" s="1" t="inlineStr"/>
       <c r="L267" s="1" t="inlineStr"/>
       <c r="M267" s="1" t="inlineStr"/>
       <c r="N267" s="1" t="inlineStr"/>
@@ -13043,7 +11227,7 @@
       <c r="P267" s="1" t="inlineStr"/>
       <c r="Q267" s="1" t="inlineStr">
         <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GisÃ¨le SÃ©guin, Bonnyville........................</t>
+          <t>L606: punctuation artifact: repeated periods :: Gisèle Séguin, Bonnyville........................</t>
         </is>
       </c>
       <c r="R267" s="1" t="inlineStr"/>
@@ -13066,11 +11250,7 @@
       <c r="H268" s="1" t="inlineStr"/>
       <c r="I268" s="1" t="inlineStr"/>
       <c r="J268" s="1" t="inlineStr"/>
-      <c r="K268" s="1" t="inlineStr">
-        <is>
-          <t>L1502: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se ChÃ©nard. Tangente ...................</t>
-        </is>
-      </c>
+      <c r="K268" s="1" t="inlineStr"/>
       <c r="L268" s="1" t="inlineStr"/>
       <c r="M268" s="1" t="inlineStr"/>
       <c r="N268" s="1" t="inlineStr"/>
@@ -13105,11 +11285,7 @@
       <c r="H269" s="1" t="inlineStr"/>
       <c r="I269" s="1" t="inlineStr"/>
       <c r="J269" s="1" t="inlineStr"/>
-      <c r="K269" s="1" t="inlineStr">
-        <is>
-          <t>L1505: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Fortin, Tangente..................</t>
-        </is>
-      </c>
+      <c r="K269" s="1" t="inlineStr"/>
       <c r="L269" s="1" t="inlineStr"/>
       <c r="M269" s="1" t="inlineStr"/>
       <c r="N269" s="1" t="inlineStr"/>
@@ -13121,7 +11297,7 @@
       <c r="P269" s="1" t="inlineStr"/>
       <c r="Q269" s="1" t="inlineStr">
         <is>
-          <t>L610: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: AdÃ¨le Couture, Bonnyville .......................</t>
+          <t>L610: punctuation artifact: repeated periods :: Adèle Couture, Bonnyville .......................</t>
         </is>
       </c>
       <c r="R269" s="1" t="inlineStr"/>
@@ -13144,11 +11320,7 @@
       <c r="H270" s="1" t="inlineStr"/>
       <c r="I270" s="1" t="inlineStr"/>
       <c r="J270" s="1" t="inlineStr"/>
-      <c r="K270" s="1" t="inlineStr">
-        <is>
-          <t>L1509: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Roger BÃ©land, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K270" s="1" t="inlineStr"/>
       <c r="L270" s="1" t="inlineStr"/>
       <c r="M270" s="1" t="inlineStr"/>
       <c r="N270" s="1" t="inlineStr"/>
@@ -13183,11 +11355,7 @@
       <c r="H271" s="1" t="inlineStr"/>
       <c r="I271" s="1" t="inlineStr"/>
       <c r="J271" s="1" t="inlineStr"/>
-      <c r="K271" s="1" t="inlineStr">
-        <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Michel Voyer, Ã©cole Grandin ................</t>
-        </is>
-      </c>
+      <c r="K271" s="1" t="inlineStr"/>
       <c r="L271" s="1" t="inlineStr"/>
       <c r="M271" s="1" t="inlineStr"/>
       <c r="N271" s="1" t="inlineStr"/>
@@ -13222,11 +11390,7 @@
       <c r="H272" s="1" t="inlineStr"/>
       <c r="I272" s="1" t="inlineStr"/>
       <c r="J272" s="1" t="inlineStr"/>
-      <c r="K272" s="1" t="inlineStr">
-        <is>
-          <t>L1515: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o BÃ©dard, Tangente .....................</t>
-        </is>
-      </c>
+      <c r="K272" s="1" t="inlineStr"/>
       <c r="L272" s="1" t="inlineStr"/>
       <c r="M272" s="1" t="inlineStr"/>
       <c r="N272" s="1" t="inlineStr"/>
@@ -13238,7 +11402,7 @@
       <c r="P272" s="1" t="inlineStr"/>
       <c r="Q272" s="1" t="inlineStr">
         <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: â€¢ IrÃ¨ne Lambert, Bonnyville .....................</t>
+          <t>L621: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | line starts with punctuation glued to text :: • Irène Lambert, Bonnyville .....................</t>
         </is>
       </c>
       <c r="R272" s="1" t="inlineStr"/>
@@ -13261,11 +11425,7 @@
       <c r="H273" s="1" t="inlineStr"/>
       <c r="I273" s="1" t="inlineStr"/>
       <c r="J273" s="1" t="inlineStr"/>
-      <c r="K273" s="1" t="inlineStr">
-        <is>
-          <t>L1520: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paul Boulet, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K273" s="1" t="inlineStr"/>
       <c r="L273" s="1" t="inlineStr"/>
       <c r="M273" s="1" t="inlineStr"/>
       <c r="N273" s="1" t="inlineStr"/>
@@ -13277,7 +11437,7 @@
       <c r="P273" s="1" t="inlineStr"/>
       <c r="Q273" s="1" t="inlineStr">
         <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1CÃ©cile Lacombe, Bonnyville.................</t>
+          <t>L623: punctuation artifact: repeated periods | suspicious token(s): 1C (letter/digit mix) :: 1Cécile Lacombe, Bonnyville.................</t>
         </is>
       </c>
       <c r="R273" s="1" t="inlineStr"/>
@@ -13300,11 +11460,7 @@
       <c r="H274" s="1" t="inlineStr"/>
       <c r="I274" s="1" t="inlineStr"/>
       <c r="J274" s="1" t="inlineStr"/>
-      <c r="K274" s="1" t="inlineStr">
-        <is>
-          <t>L1565: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Madeleine GÃ©linas, pensionnat de l'Assomption</t>
-        </is>
-      </c>
+      <c r="K274" s="1" t="inlineStr"/>
       <c r="L274" s="1" t="inlineStr"/>
       <c r="M274" s="1" t="inlineStr"/>
       <c r="N274" s="1" t="inlineStr"/>
@@ -13339,11 +11495,7 @@
       <c r="H275" s="1" t="inlineStr"/>
       <c r="I275" s="1" t="inlineStr"/>
       <c r="J275" s="1" t="inlineStr"/>
-      <c r="K275" s="1" t="inlineStr">
-        <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorraine BÃ©rubÃ©. Beaumont .......................</t>
-        </is>
-      </c>
+      <c r="K275" s="1" t="inlineStr"/>
       <c r="L275" s="1" t="inlineStr"/>
       <c r="M275" s="1" t="inlineStr"/>
       <c r="N275" s="1" t="inlineStr"/>
@@ -13378,11 +11530,7 @@
       <c r="H276" s="1" t="inlineStr"/>
       <c r="I276" s="1" t="inlineStr"/>
       <c r="J276" s="1" t="inlineStr"/>
-      <c r="K276" s="1" t="inlineStr">
-        <is>
-          <t>L1571: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alberta LabontÃ©, Ã©cole Thibeault ................</t>
-        </is>
-      </c>
+      <c r="K276" s="1" t="inlineStr"/>
       <c r="L276" s="1" t="inlineStr"/>
       <c r="M276" s="1" t="inlineStr"/>
       <c r="N276" s="1" t="inlineStr"/>
@@ -13417,11 +11565,7 @@
       <c r="H277" s="1" t="inlineStr"/>
       <c r="I277" s="1" t="inlineStr"/>
       <c r="J277" s="1" t="inlineStr"/>
-      <c r="K277" s="1" t="inlineStr">
-        <is>
-          <t>L1573: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fleurette Rousseau, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="K277" s="1" t="inlineStr"/>
       <c r="L277" s="1" t="inlineStr"/>
       <c r="M277" s="1" t="inlineStr"/>
       <c r="N277" s="1" t="inlineStr"/>
@@ -13456,11 +11600,7 @@
       <c r="H278" s="1" t="inlineStr"/>
       <c r="I278" s="1" t="inlineStr"/>
       <c r="J278" s="1" t="inlineStr"/>
-      <c r="K278" s="1" t="inlineStr">
-        <is>
-          <t>L1577: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ontine Aubin, Ã©cole consolidÃ©e, Falher ........</t>
-        </is>
-      </c>
+      <c r="K278" s="1" t="inlineStr"/>
       <c r="L278" s="1" t="inlineStr"/>
       <c r="M278" s="1" t="inlineStr"/>
       <c r="N278" s="1" t="inlineStr"/>
@@ -13472,7 +11612,7 @@
       <c r="P278" s="1" t="inlineStr"/>
       <c r="Q278" s="1" t="inlineStr">
         <is>
-          <t>L635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, Ã©cole Dunrobin</t>
+          <t>L635: punctuation artifact: repeated periods :: ..61 i Vivianne Nobert, école Dunrobin</t>
         </is>
       </c>
       <c r="R278" s="1" t="inlineStr"/>
@@ -13495,11 +11635,7 @@
       <c r="H279" s="1" t="inlineStr"/>
       <c r="I279" s="1" t="inlineStr"/>
       <c r="J279" s="1" t="inlineStr"/>
-      <c r="K279" s="1" t="inlineStr">
-        <is>
-          <t>L1585: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: OrigÃ¨ne Caouette, Bonnyville ....................</t>
-        </is>
-      </c>
+      <c r="K279" s="1" t="inlineStr"/>
       <c r="L279" s="1" t="inlineStr"/>
       <c r="M279" s="1" t="inlineStr"/>
       <c r="N279" s="1" t="inlineStr"/>
@@ -13534,11 +11670,7 @@
       <c r="H280" s="1" t="inlineStr"/>
       <c r="I280" s="1" t="inlineStr"/>
       <c r="J280" s="1" t="inlineStr"/>
-      <c r="K280" s="1" t="inlineStr">
-        <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Etiennette SÃ©guin, Bonnyville ...................</t>
-        </is>
-      </c>
+      <c r="K280" s="1" t="inlineStr"/>
       <c r="L280" s="1" t="inlineStr"/>
       <c r="M280" s="1" t="inlineStr"/>
       <c r="N280" s="1" t="inlineStr"/>
@@ -13550,7 +11682,7 @@
       <c r="P280" s="1" t="inlineStr"/>
       <c r="Q280" s="1" t="inlineStr">
         <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 581 AndrÃ© Bouchard, Tangente ..........</t>
+          <t>L645: punctuation artifact: repeated periods :: 581 André Bouchard, Tangente ..........</t>
         </is>
       </c>
       <c r="R280" s="1" t="inlineStr"/>
@@ -13573,11 +11705,7 @@
       <c r="H281" s="1" t="inlineStr"/>
       <c r="I281" s="1" t="inlineStr"/>
       <c r="J281" s="1" t="inlineStr"/>
-      <c r="K281" s="1" t="inlineStr">
-        <is>
-          <t>L1591: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ©e Meunier Ã©cole Thibeault ...................</t>
-        </is>
-      </c>
+      <c r="K281" s="1" t="inlineStr"/>
       <c r="L281" s="1" t="inlineStr"/>
       <c r="M281" s="1" t="inlineStr"/>
       <c r="N281" s="1" t="inlineStr"/>
@@ -13612,11 +11740,7 @@
       <c r="H282" s="1" t="inlineStr"/>
       <c r="I282" s="1" t="inlineStr"/>
       <c r="J282" s="1" t="inlineStr"/>
-      <c r="K282" s="1" t="inlineStr">
-        <is>
-          <t>L1593: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©vis Chiasson, Sainte-Lina .....................</t>
-        </is>
-      </c>
+      <c r="K282" s="1" t="inlineStr"/>
       <c r="L282" s="1" t="inlineStr"/>
       <c r="M282" s="1" t="inlineStr"/>
       <c r="N282" s="1" t="inlineStr"/>
@@ -13651,11 +11775,7 @@
       <c r="H283" s="1" t="inlineStr"/>
       <c r="I283" s="1" t="inlineStr"/>
       <c r="J283" s="1" t="inlineStr"/>
-      <c r="K283" s="1" t="inlineStr">
-        <is>
-          <t>L1595: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Legris, Ã©cole Grandin ....................</t>
-        </is>
-      </c>
+      <c r="K283" s="1" t="inlineStr"/>
       <c r="L283" s="1" t="inlineStr"/>
       <c r="M283" s="1" t="inlineStr"/>
       <c r="N283" s="1" t="inlineStr"/>
@@ -13690,11 +11810,7 @@
       <c r="H284" s="1" t="inlineStr"/>
       <c r="I284" s="1" t="inlineStr"/>
       <c r="J284" s="1" t="inlineStr"/>
-      <c r="K284" s="1" t="inlineStr">
-        <is>
-          <t>L1601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, ThÃ©rien ...................</t>
-        </is>
-      </c>
+      <c r="K284" s="1" t="inlineStr"/>
       <c r="L284" s="1" t="inlineStr"/>
       <c r="M284" s="1" t="inlineStr"/>
       <c r="N284" s="1" t="inlineStr"/>
@@ -13729,11 +11845,7 @@
       <c r="H285" s="1" t="inlineStr"/>
       <c r="I285" s="1" t="inlineStr"/>
       <c r="J285" s="1" t="inlineStr"/>
-      <c r="K285" s="1" t="inlineStr">
-        <is>
-          <t>L1603: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ,ThÃ©rÃ¨se Rochette. Tangente.................</t>
-        </is>
-      </c>
+      <c r="K285" s="1" t="inlineStr"/>
       <c r="L285" s="1" t="inlineStr"/>
       <c r="M285" s="1" t="inlineStr"/>
       <c r="N285" s="1" t="inlineStr"/>
@@ -13768,11 +11880,7 @@
       <c r="H286" s="1" t="inlineStr"/>
       <c r="I286" s="1" t="inlineStr"/>
       <c r="J286" s="1" t="inlineStr"/>
-      <c r="K286" s="1" t="inlineStr">
-        <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Lussier, Tangente......................</t>
-        </is>
-      </c>
+      <c r="K286" s="1" t="inlineStr"/>
       <c r="L286" s="1" t="inlineStr"/>
       <c r="M286" s="1" t="inlineStr"/>
       <c r="N286" s="1" t="inlineStr"/>
@@ -13807,11 +11915,7 @@
       <c r="H287" s="1" t="inlineStr"/>
       <c r="I287" s="1" t="inlineStr"/>
       <c r="J287" s="1" t="inlineStr"/>
-      <c r="K287" s="1" t="inlineStr">
-        <is>
-          <t>L1609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ;ThÃ©rÃ¨se Gauthier, Plamondon................</t>
-        </is>
-      </c>
+      <c r="K287" s="1" t="inlineStr"/>
       <c r="L287" s="1" t="inlineStr"/>
       <c r="M287" s="1" t="inlineStr"/>
       <c r="N287" s="1" t="inlineStr"/>
@@ -13846,11 +11950,7 @@
       <c r="H288" s="1" t="inlineStr"/>
       <c r="I288" s="1" t="inlineStr"/>
       <c r="J288" s="1" t="inlineStr"/>
-      <c r="K288" s="1" t="inlineStr">
-        <is>
-          <t>L1613: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elise Chartrand, Ã©cole Grandin .............</t>
-        </is>
-      </c>
+      <c r="K288" s="1" t="inlineStr"/>
       <c r="L288" s="1" t="inlineStr"/>
       <c r="M288" s="1" t="inlineStr"/>
       <c r="N288" s="1" t="inlineStr"/>
@@ -13885,11 +11985,7 @@
       <c r="H289" s="1" t="inlineStr"/>
       <c r="I289" s="1" t="inlineStr"/>
       <c r="J289" s="1" t="inlineStr"/>
-      <c r="K289" s="1" t="inlineStr">
-        <is>
-          <t>L1615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o Dechaine, Sainte-Lina ................</t>
-        </is>
-      </c>
+      <c r="K289" s="1" t="inlineStr"/>
       <c r="L289" s="1" t="inlineStr"/>
       <c r="M289" s="1" t="inlineStr"/>
       <c r="N289" s="1" t="inlineStr"/>
@@ -13924,11 +12020,7 @@
       <c r="H290" s="1" t="inlineStr"/>
       <c r="I290" s="1" t="inlineStr"/>
       <c r="J290" s="1" t="inlineStr"/>
-      <c r="K290" s="1" t="inlineStr">
-        <is>
-          <t>L1617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Bouchard, Tangente .................</t>
-        </is>
-      </c>
+      <c r="K290" s="1" t="inlineStr"/>
       <c r="L290" s="1" t="inlineStr"/>
       <c r="M290" s="1" t="inlineStr"/>
       <c r="N290" s="1" t="inlineStr"/>
@@ -13963,11 +12055,7 @@
       <c r="H291" s="1" t="inlineStr"/>
       <c r="I291" s="1" t="inlineStr"/>
       <c r="J291" s="1" t="inlineStr"/>
-      <c r="K291" s="1" t="inlineStr">
-        <is>
-          <t>L1623: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: Laurier CarriÃ¨re, Legal ....................</t>
-        </is>
-      </c>
+      <c r="K291" s="1" t="inlineStr"/>
       <c r="L291" s="1" t="inlineStr"/>
       <c r="M291" s="1" t="inlineStr"/>
       <c r="N291" s="1" t="inlineStr"/>
@@ -14002,11 +12090,7 @@
       <c r="H292" s="1" t="inlineStr"/>
       <c r="I292" s="1" t="inlineStr"/>
       <c r="J292" s="1" t="inlineStr"/>
-      <c r="K292" s="1" t="inlineStr">
-        <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette Lafond, Ã©cole Thibeault ...........</t>
-        </is>
-      </c>
+      <c r="K292" s="1" t="inlineStr"/>
       <c r="L292" s="1" t="inlineStr"/>
       <c r="M292" s="1" t="inlineStr"/>
       <c r="N292" s="1" t="inlineStr"/>
@@ -14041,11 +12125,7 @@
       <c r="H293" s="1" t="inlineStr"/>
       <c r="I293" s="1" t="inlineStr"/>
       <c r="J293" s="1" t="inlineStr"/>
-      <c r="K293" s="1" t="inlineStr">
-        <is>
-          <t>L1631: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doreen Stelte, Ã©cole Thibeault .............</t>
-        </is>
-      </c>
+      <c r="K293" s="1" t="inlineStr"/>
       <c r="L293" s="1" t="inlineStr"/>
       <c r="M293" s="1" t="inlineStr"/>
       <c r="N293" s="1" t="inlineStr"/>
@@ -14080,11 +12160,7 @@
       <c r="H294" s="1" t="inlineStr"/>
       <c r="I294" s="1" t="inlineStr"/>
       <c r="J294" s="1" t="inlineStr"/>
-      <c r="K294" s="1" t="inlineStr">
-        <is>
-          <t>L1635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Magant, Sainte-Lina ......-</t>
-        </is>
-      </c>
+      <c r="K294" s="1" t="inlineStr"/>
       <c r="L294" s="1" t="inlineStr"/>
       <c r="M294" s="1" t="inlineStr"/>
       <c r="N294" s="1" t="inlineStr"/>
@@ -14119,11 +12195,7 @@
       <c r="H295" s="1" t="inlineStr"/>
       <c r="I295" s="1" t="inlineStr"/>
       <c r="J295" s="1" t="inlineStr"/>
-      <c r="K295" s="1" t="inlineStr">
-        <is>
-          <t>L1643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RÃ©jeanne Rochette, Tangente ................</t>
-        </is>
-      </c>
+      <c r="K295" s="1" t="inlineStr"/>
       <c r="L295" s="1" t="inlineStr"/>
       <c r="M295" s="1" t="inlineStr"/>
       <c r="N295" s="1" t="inlineStr"/>
@@ -14158,11 +12230,7 @@
       <c r="H296" s="1" t="inlineStr"/>
       <c r="I296" s="1" t="inlineStr"/>
       <c r="J296" s="1" t="inlineStr"/>
-      <c r="K296" s="1" t="inlineStr">
-        <is>
-          <t>L1645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: Rachel Ouellette, Tangente .............â€”...</t>
-        </is>
-      </c>
+      <c r="K296" s="1" t="inlineStr"/>
       <c r="L296" s="1" t="inlineStr"/>
       <c r="M296" s="1" t="inlineStr"/>
       <c r="N296" s="1" t="inlineStr"/>
@@ -14197,11 +12265,7 @@
       <c r="H297" s="1" t="inlineStr"/>
       <c r="I297" s="1" t="inlineStr"/>
       <c r="J297" s="1" t="inlineStr"/>
-      <c r="K297" s="1" t="inlineStr">
-        <is>
-          <t>L1647: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Albert Benoit, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K297" s="1" t="inlineStr"/>
       <c r="L297" s="1" t="inlineStr"/>
       <c r="M297" s="1" t="inlineStr"/>
       <c r="N297" s="1" t="inlineStr"/>
@@ -14236,11 +12300,7 @@
       <c r="H298" s="1" t="inlineStr"/>
       <c r="I298" s="1" t="inlineStr"/>
       <c r="J298" s="1" t="inlineStr"/>
-      <c r="K298" s="1" t="inlineStr">
-        <is>
-          <t>L1649: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Lucille LaverdiÃ¨re, Ã©cole consolidÃ©e, Falher</t>
-        </is>
-      </c>
+      <c r="K298" s="1" t="inlineStr"/>
       <c r="L298" s="1" t="inlineStr"/>
       <c r="M298" s="1" t="inlineStr"/>
       <c r="N298" s="1" t="inlineStr"/>
@@ -14275,11 +12335,7 @@
       <c r="H299" s="1" t="inlineStr"/>
       <c r="I299" s="1" t="inlineStr"/>
       <c r="J299" s="1" t="inlineStr"/>
-      <c r="K299" s="1" t="inlineStr">
-        <is>
-          <t>L1651: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marc Voyer, Ã©cole Grandin ..................</t>
-        </is>
-      </c>
+      <c r="K299" s="1" t="inlineStr"/>
       <c r="L299" s="1" t="inlineStr"/>
       <c r="M299" s="1" t="inlineStr"/>
       <c r="N299" s="1" t="inlineStr"/>
@@ -14314,11 +12370,7 @@
       <c r="H300" s="1" t="inlineStr"/>
       <c r="I300" s="1" t="inlineStr"/>
       <c r="J300" s="1" t="inlineStr"/>
-      <c r="K300" s="1" t="inlineStr">
-        <is>
-          <t>L1661: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Despins, Ã©cole Dunrobin ..........................</t>
-        </is>
-      </c>
+      <c r="K300" s="1" t="inlineStr"/>
       <c r="L300" s="1" t="inlineStr"/>
       <c r="M300" s="1" t="inlineStr"/>
       <c r="N300" s="1" t="inlineStr"/>
@@ -14353,11 +12405,7 @@
       <c r="H301" s="1" t="inlineStr"/>
       <c r="I301" s="1" t="inlineStr"/>
       <c r="J301" s="1" t="inlineStr"/>
-      <c r="K301" s="1" t="inlineStr">
-        <is>
-          <t>L1663: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 82 Antonia Villeneuve, Ã©cole consolidÃ©e, Falher ........</t>
-        </is>
-      </c>
+      <c r="K301" s="1" t="inlineStr"/>
       <c r="L301" s="1" t="inlineStr"/>
       <c r="M301" s="1" t="inlineStr"/>
       <c r="N301" s="1" t="inlineStr"/>
@@ -14369,7 +12417,7 @@
       <c r="P301" s="1" t="inlineStr"/>
       <c r="Q301" s="1" t="inlineStr">
         <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: EvangÃ©line Gillon, Tangente .................</t>
+          <t>L696: punctuation artifact: repeated periods :: Evangéline Gillon, Tangente .................</t>
         </is>
       </c>
       <c r="R301" s="1" t="inlineStr"/>
@@ -14392,11 +12440,7 @@
       <c r="H302" s="1" t="inlineStr"/>
       <c r="I302" s="1" t="inlineStr"/>
       <c r="J302" s="1" t="inlineStr"/>
-      <c r="K302" s="1" t="inlineStr">
-        <is>
-          <t>L1669: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Cloutier, Tangente</t>
-        </is>
-      </c>
+      <c r="K302" s="1" t="inlineStr"/>
       <c r="L302" s="1" t="inlineStr"/>
       <c r="M302" s="1" t="inlineStr"/>
       <c r="N302" s="1" t="inlineStr"/>
@@ -14408,7 +12452,7 @@
       <c r="P302" s="1" t="inlineStr"/>
       <c r="Q302" s="1" t="inlineStr">
         <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Euclide BÃ©rubÃ©, Beaumont .........</t>
+          <t>L698: punctuation artifact: repeated periods :: Euclide Bérubé, Beaumont .........</t>
         </is>
       </c>
       <c r="R302" s="1" t="inlineStr"/>
@@ -14431,11 +12475,7 @@
       <c r="H303" s="1" t="inlineStr"/>
       <c r="I303" s="1" t="inlineStr"/>
       <c r="J303" s="1" t="inlineStr"/>
-      <c r="K303" s="1" t="inlineStr">
-        <is>
-          <t>L1671: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Diane Ouellette, Ã©cole consolidÃ©e, Donnelly .............</t>
-        </is>
-      </c>
+      <c r="K303" s="1" t="inlineStr"/>
       <c r="L303" s="1" t="inlineStr"/>
       <c r="M303" s="1" t="inlineStr"/>
       <c r="N303" s="1" t="inlineStr"/>
@@ -14470,11 +12510,7 @@
       <c r="H304" s="1" t="inlineStr"/>
       <c r="I304" s="1" t="inlineStr"/>
       <c r="J304" s="1" t="inlineStr"/>
-      <c r="K304" s="1" t="inlineStr">
-        <is>
-          <t>L1678: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ....85 Denise Plaquin, ThÃ©rien:</t>
-        </is>
-      </c>
+      <c r="K304" s="1" t="inlineStr"/>
       <c r="L304" s="1" t="inlineStr"/>
       <c r="M304" s="1" t="inlineStr"/>
       <c r="N304" s="1" t="inlineStr"/>
@@ -14486,7 +12522,7 @@
       <c r="P304" s="1" t="inlineStr"/>
       <c r="Q304" s="1" t="inlineStr">
         <is>
-          <t>L704: punctuation artifact: repeated periods :: NoÃ«l Martel, La Corey........................</t>
+          <t>L704: punctuation artifact: repeated periods :: Noël Martel, La Corey........................</t>
         </is>
       </c>
       <c r="R304" s="1" t="inlineStr"/>
@@ -14509,11 +12545,7 @@
       <c r="H305" s="1" t="inlineStr"/>
       <c r="I305" s="1" t="inlineStr"/>
       <c r="J305" s="1" t="inlineStr"/>
-      <c r="K305" s="1" t="inlineStr">
-        <is>
-          <t>L1680: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 851 Lorraine Bachoffer, ThÃ©rien</t>
-        </is>
-      </c>
+      <c r="K305" s="1" t="inlineStr"/>
       <c r="L305" s="1" t="inlineStr"/>
       <c r="M305" s="1" t="inlineStr"/>
       <c r="N305" s="1" t="inlineStr"/>
@@ -14548,11 +12580,7 @@
       <c r="H306" s="1" t="inlineStr"/>
       <c r="I306" s="1" t="inlineStr"/>
       <c r="J306" s="1" t="inlineStr"/>
-      <c r="K306" s="1" t="inlineStr">
-        <is>
-          <t>L1686: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claude BÃ©rubÃ©, Beaumont</t>
-        </is>
-      </c>
+      <c r="K306" s="1" t="inlineStr"/>
       <c r="L306" s="1" t="inlineStr"/>
       <c r="M306" s="1" t="inlineStr"/>
       <c r="N306" s="1" t="inlineStr"/>
@@ -14587,11 +12615,7 @@
       <c r="H307" s="1" t="inlineStr"/>
       <c r="I307" s="1" t="inlineStr"/>
       <c r="J307" s="1" t="inlineStr"/>
-      <c r="K307" s="1" t="inlineStr">
-        <is>
-          <t>L1687: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: HÃ©lÃ¨ne Chouinard, La Corey</t>
-        </is>
-      </c>
+      <c r="K307" s="1" t="inlineStr"/>
       <c r="L307" s="1" t="inlineStr"/>
       <c r="M307" s="1" t="inlineStr"/>
       <c r="N307" s="1" t="inlineStr"/>
@@ -14626,11 +12650,7 @@
       <c r="H308" s="1" t="inlineStr"/>
       <c r="I308" s="1" t="inlineStr"/>
       <c r="J308" s="1" t="inlineStr"/>
-      <c r="K308" s="1" t="inlineStr">
-        <is>
-          <t>L1694: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ©a Trudel, Saint-Paul ................</t>
-        </is>
-      </c>
+      <c r="K308" s="1" t="inlineStr"/>
       <c r="L308" s="1" t="inlineStr"/>
       <c r="M308" s="1" t="inlineStr"/>
       <c r="N308" s="1" t="inlineStr"/>
@@ -14665,11 +12685,7 @@
       <c r="H309" s="1" t="inlineStr"/>
       <c r="I309" s="1" t="inlineStr"/>
       <c r="J309" s="1" t="inlineStr"/>
-      <c r="K309" s="1" t="inlineStr">
-        <is>
-          <t>L1698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Emile Isabel, Ã©cole consolidÃ©e, Falher ..</t>
-        </is>
-      </c>
+      <c r="K309" s="1" t="inlineStr"/>
       <c r="L309" s="1" t="inlineStr"/>
       <c r="M309" s="1" t="inlineStr"/>
       <c r="N309" s="1" t="inlineStr"/>
@@ -14704,11 +12720,7 @@
       <c r="H310" s="1" t="inlineStr"/>
       <c r="I310" s="1" t="inlineStr"/>
       <c r="J310" s="1" t="inlineStr"/>
-      <c r="K310" s="1" t="inlineStr">
-        <is>
-          <t>L1702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gratton, ThÃ©rien Village .........</t>
-        </is>
-      </c>
+      <c r="K310" s="1" t="inlineStr"/>
       <c r="L310" s="1" t="inlineStr"/>
       <c r="M310" s="1" t="inlineStr"/>
       <c r="N310" s="1" t="inlineStr"/>
@@ -14720,7 +12732,7 @@
       <c r="P310" s="1" t="inlineStr"/>
       <c r="Q310" s="1" t="inlineStr">
         <is>
-          <t>L732: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Dolores Comeau, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L732: punctuation artifact: repeated periods :: Dolores Comeau, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R310" s="1" t="inlineStr"/>
@@ -14743,11 +12755,7 @@
       <c r="H311" s="1" t="inlineStr"/>
       <c r="I311" s="1" t="inlineStr"/>
       <c r="J311" s="1" t="inlineStr"/>
-      <c r="K311" s="1" t="inlineStr">
-        <is>
-          <t>L1704: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucien Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K311" s="1" t="inlineStr"/>
       <c r="L311" s="1" t="inlineStr"/>
       <c r="M311" s="1" t="inlineStr"/>
       <c r="N311" s="1" t="inlineStr"/>
@@ -14782,11 +12790,7 @@
       <c r="H312" s="1" t="inlineStr"/>
       <c r="I312" s="1" t="inlineStr"/>
       <c r="J312" s="1" t="inlineStr"/>
-      <c r="K312" s="1" t="inlineStr">
-        <is>
-          <t>L1710: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lucille Fortier, Ã©cole consolidÃ©e, Donnelly</t>
-        </is>
-      </c>
+      <c r="K312" s="1" t="inlineStr"/>
       <c r="L312" s="1" t="inlineStr"/>
       <c r="M312" s="1" t="inlineStr"/>
       <c r="N312" s="1" t="inlineStr"/>
@@ -14798,7 +12802,7 @@
       <c r="P312" s="1" t="inlineStr"/>
       <c r="Q312" s="1" t="inlineStr">
         <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Yolande Robert, Ã©cole Thibeault .............</t>
+          <t>L738: punctuation artifact: repeated periods :: Yolande Robert, école Thibeault .............</t>
         </is>
       </c>
       <c r="R312" s="1" t="inlineStr"/>
@@ -14821,11 +12825,7 @@
       <c r="H313" s="1" t="inlineStr"/>
       <c r="I313" s="1" t="inlineStr"/>
       <c r="J313" s="1" t="inlineStr"/>
-      <c r="K313" s="1" t="inlineStr">
-        <is>
-          <t>L1712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Roy, Ã©cole consolidÃ©e, Falher .....</t>
-        </is>
-      </c>
+      <c r="K313" s="1" t="inlineStr"/>
       <c r="L313" s="1" t="inlineStr"/>
       <c r="M313" s="1" t="inlineStr"/>
       <c r="N313" s="1" t="inlineStr"/>
@@ -14860,11 +12860,7 @@
       <c r="H314" s="1" t="inlineStr"/>
       <c r="I314" s="1" t="inlineStr"/>
       <c r="J314" s="1" t="inlineStr"/>
-      <c r="K314" s="1" t="inlineStr">
-        <is>
-          <t>L1784: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Claire HÃ©bert, Saint-Vincent ................,....99</t>
-        </is>
-      </c>
+      <c r="K314" s="1" t="inlineStr"/>
       <c r="L314" s="1" t="inlineStr"/>
       <c r="M314" s="1" t="inlineStr"/>
       <c r="N314" s="1" t="inlineStr"/>
@@ -14899,11 +12895,7 @@
       <c r="H315" s="1" t="inlineStr"/>
       <c r="I315" s="1" t="inlineStr"/>
       <c r="J315" s="1" t="inlineStr"/>
-      <c r="K315" s="1" t="inlineStr">
-        <is>
-          <t>L1786: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bernard LavallÃ©e, Ã©cole Thibeault ................98</t>
-        </is>
-      </c>
+      <c r="K315" s="1" t="inlineStr"/>
       <c r="L315" s="1" t="inlineStr"/>
       <c r="M315" s="1" t="inlineStr"/>
       <c r="N315" s="1" t="inlineStr"/>
@@ -14915,7 +12907,7 @@
       <c r="P315" s="1" t="inlineStr"/>
       <c r="Q315" s="1" t="inlineStr">
         <is>
-          <t>L748: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Ronald Patry, Ã©cole Thibeault .....</t>
+          <t>L748: punctuation artifact: repeated periods :: Ronald Patry, école Thibeault .....</t>
         </is>
       </c>
       <c r="R315" s="1" t="inlineStr"/>
@@ -14938,11 +12930,7 @@
       <c r="H316" s="1" t="inlineStr"/>
       <c r="I316" s="1" t="inlineStr"/>
       <c r="J316" s="1" t="inlineStr"/>
-      <c r="K316" s="1" t="inlineStr">
-        <is>
-          <t>L1788: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Carole Lefebvre, Ã©cole Grandin ...................98</t>
-        </is>
-      </c>
+      <c r="K316" s="1" t="inlineStr"/>
       <c r="L316" s="1" t="inlineStr"/>
       <c r="M316" s="1" t="inlineStr"/>
       <c r="N316" s="1" t="inlineStr"/>
@@ -14977,11 +12965,7 @@
       <c r="H317" s="1" t="inlineStr"/>
       <c r="I317" s="1" t="inlineStr"/>
       <c r="J317" s="1" t="inlineStr"/>
-      <c r="K317" s="1" t="inlineStr">
-        <is>
-          <t>L1790: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Simonne LavallÃ©e, pensionnat de l'Assomption .....97</t>
-        </is>
-      </c>
+      <c r="K317" s="1" t="inlineStr"/>
       <c r="L317" s="1" t="inlineStr"/>
       <c r="M317" s="1" t="inlineStr"/>
       <c r="N317" s="1" t="inlineStr"/>
@@ -15016,11 +13000,7 @@
       <c r="H318" s="1" t="inlineStr"/>
       <c r="I318" s="1" t="inlineStr"/>
       <c r="J318" s="1" t="inlineStr"/>
-      <c r="K318" s="1" t="inlineStr">
-        <is>
-          <t>L1792: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Marie St-Arnaud, Ã©cole Dunrobin, Vimy 97</t>
-        </is>
-      </c>
+      <c r="K318" s="1" t="inlineStr"/>
       <c r="L318" s="1" t="inlineStr"/>
       <c r="M318" s="1" t="inlineStr"/>
       <c r="N318" s="1" t="inlineStr"/>
@@ -15032,7 +13012,7 @@
       <c r="P318" s="1" t="inlineStr"/>
       <c r="Q318" s="1" t="inlineStr">
         <is>
-          <t>L757: punctuation artifact: repeated periods :: Jean-Paul NoÃ«l. Saint-Paul .............</t>
+          <t>L757: punctuation artifact: repeated periods :: Jean-Paul Noël. Saint-Paul .............</t>
         </is>
       </c>
       <c r="R318" s="1" t="inlineStr"/>
@@ -15055,11 +13035,7 @@
       <c r="H319" s="1" t="inlineStr"/>
       <c r="I319" s="1" t="inlineStr"/>
       <c r="J319" s="1" t="inlineStr"/>
-      <c r="K319" s="1" t="inlineStr">
-        <is>
-          <t>L1798: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Une leÃ§on de rÃ©alisme</t>
-        </is>
-      </c>
+      <c r="K319" s="1" t="inlineStr"/>
       <c r="L319" s="1" t="inlineStr"/>
       <c r="M319" s="1" t="inlineStr"/>
       <c r="N319" s="1" t="inlineStr"/>
@@ -15094,11 +13070,7 @@
       <c r="H320" s="1" t="inlineStr"/>
       <c r="I320" s="1" t="inlineStr"/>
       <c r="J320" s="1" t="inlineStr"/>
-      <c r="K320" s="1" t="inlineStr">
-        <is>
-          <t>L1800: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Gentile Bellini, peintre vÃ©nitien, fut :</t>
-        </is>
-      </c>
+      <c r="K320" s="1" t="inlineStr"/>
       <c r="L320" s="1" t="inlineStr"/>
       <c r="M320" s="1" t="inlineStr"/>
       <c r="N320" s="1" t="inlineStr"/>
@@ -15133,11 +13105,7 @@
       <c r="H321" s="1" t="inlineStr"/>
       <c r="I321" s="1" t="inlineStr"/>
       <c r="J321" s="1" t="inlineStr"/>
-      <c r="K321" s="1" t="inlineStr">
-        <is>
-          <t>L1801: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: appelÃ© Ã Constantinople par Mahomet :</t>
-        </is>
-      </c>
+      <c r="K321" s="1" t="inlineStr"/>
       <c r="L321" s="1" t="inlineStr"/>
       <c r="M321" s="1" t="inlineStr"/>
       <c r="N321" s="1" t="inlineStr"/>
@@ -15172,11 +13140,7 @@
       <c r="H322" s="1" t="inlineStr"/>
       <c r="I322" s="1" t="inlineStr"/>
       <c r="J322" s="1" t="inlineStr"/>
-      <c r="K322" s="1" t="inlineStr">
-        <is>
-          <t>L1803: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme dÃ©ca--</t>
-        </is>
-      </c>
+      <c r="K322" s="1" t="inlineStr"/>
       <c r="L322" s="1" t="inlineStr"/>
       <c r="M322" s="1" t="inlineStr"/>
       <c r="N322" s="1" t="inlineStr"/>
@@ -15211,11 +13175,7 @@
       <c r="H323" s="1" t="inlineStr"/>
       <c r="I323" s="1" t="inlineStr"/>
       <c r="J323" s="1" t="inlineStr"/>
-      <c r="K323" s="1" t="inlineStr">
-        <is>
-          <t>L1804: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pitÃ©. Le grand seigneur apprÃ©cia l'art</t>
-        </is>
-      </c>
+      <c r="K323" s="1" t="inlineStr"/>
       <c r="L323" s="1" t="inlineStr"/>
       <c r="M323" s="1" t="inlineStr"/>
       <c r="N323" s="1" t="inlineStr"/>
@@ -15227,7 +13187,7 @@
       <c r="P323" s="1" t="inlineStr"/>
       <c r="Q323" s="1" t="inlineStr">
         <is>
-          <t>L780: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Albert Anctil, Ã©cole Thibeault ...........</t>
+          <t>L780: punctuation artifact: repeated periods :: Albert Anctil, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R323" s="1" t="inlineStr"/>
@@ -15250,11 +13210,7 @@
       <c r="H324" s="1" t="inlineStr"/>
       <c r="I324" s="1" t="inlineStr"/>
       <c r="J324" s="1" t="inlineStr"/>
-      <c r="K324" s="1" t="inlineStr">
-        <is>
-          <t>L1805: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de l'Italien; nÃ©anmoins, il releva un</t>
-        </is>
-      </c>
+      <c r="K324" s="1" t="inlineStr"/>
       <c r="L324" s="1" t="inlineStr"/>
       <c r="M324" s="1" t="inlineStr"/>
       <c r="N324" s="1" t="inlineStr"/>
@@ -15266,7 +13222,7 @@
       <c r="P324" s="1" t="inlineStr"/>
       <c r="Q324" s="1" t="inlineStr">
         <is>
-          <t>L783: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alice Aquin, Ã©cole Thibeault ................</t>
+          <t>L783: punctuation artifact: repeated periods :: Alice Aquin, école Thibeault ................</t>
         </is>
       </c>
       <c r="R324" s="1" t="inlineStr"/>
@@ -15289,11 +13245,7 @@
       <c r="H325" s="1" t="inlineStr"/>
       <c r="I325" s="1" t="inlineStr"/>
       <c r="J325" s="1" t="inlineStr"/>
-      <c r="K325" s="1" t="inlineStr">
-        <is>
-          <t>L1806: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©faut qui le choquait: la tÃªte sanglan-</t>
-        </is>
-      </c>
+      <c r="K325" s="1" t="inlineStr"/>
       <c r="L325" s="1" t="inlineStr"/>
       <c r="M325" s="1" t="inlineStr"/>
       <c r="N325" s="1" t="inlineStr"/>
@@ -15328,11 +13280,7 @@
       <c r="H326" s="1" t="inlineStr"/>
       <c r="I326" s="1" t="inlineStr"/>
       <c r="J326" s="1" t="inlineStr"/>
-      <c r="K326" s="1" t="inlineStr">
-        <is>
-          <t>L1807: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: te n'Ã©tait pas telle qu'il fallait.</t>
-        </is>
-      </c>
+      <c r="K326" s="1" t="inlineStr"/>
       <c r="L326" s="1" t="inlineStr"/>
       <c r="M326" s="1" t="inlineStr"/>
       <c r="N326" s="1" t="inlineStr"/>
@@ -15367,11 +13315,7 @@
       <c r="H327" s="1" t="inlineStr"/>
       <c r="I327" s="1" t="inlineStr"/>
       <c r="J327" s="1" t="inlineStr"/>
-      <c r="K327" s="1" t="inlineStr">
-        <is>
-          <t>L1809: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€”Quand un homme est dÃ©capitÃ©, dit-1</t>
-        </is>
-      </c>
+      <c r="K327" s="1" t="inlineStr"/>
       <c r="L327" s="1" t="inlineStr"/>
       <c r="M327" s="1" t="inlineStr"/>
       <c r="N327" s="1" t="inlineStr"/>
@@ -15406,11 +13350,7 @@
       <c r="H328" s="1" t="inlineStr"/>
       <c r="I328" s="1" t="inlineStr"/>
       <c r="J328" s="1" t="inlineStr"/>
-      <c r="K328" s="1" t="inlineStr">
-        <is>
-          <t>L1814: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): l'artiste1 (letter/digit mix) :: clave tomba et fut prÃ©sentÃ©e Ã l'artiste1</t>
-        </is>
-      </c>
+      <c r="K328" s="1" t="inlineStr"/>
       <c r="L328" s="1" t="inlineStr"/>
       <c r="M328" s="1" t="inlineStr"/>
       <c r="N328" s="1" t="inlineStr"/>
@@ -15445,11 +13385,7 @@
       <c r="H329" s="1" t="inlineStr"/>
       <c r="I329" s="1" t="inlineStr"/>
       <c r="J329" s="1" t="inlineStr"/>
-      <c r="K329" s="1" t="inlineStr">
-        <is>
-          <t>L1815: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: pour qu'il l'examinÃ¢t.1</t>
-        </is>
-      </c>
+      <c r="K329" s="1" t="inlineStr"/>
       <c r="L329" s="1" t="inlineStr"/>
       <c r="M329" s="1" t="inlineStr"/>
       <c r="N329" s="1" t="inlineStr"/>
@@ -15484,11 +13420,7 @@
       <c r="H330" s="1" t="inlineStr"/>
       <c r="I330" s="1" t="inlineStr"/>
       <c r="J330" s="1" t="inlineStr"/>
-      <c r="K330" s="1" t="inlineStr">
-        <is>
-          <t>L1817: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bellini fut tellement Ã©pouvantÃ©, qu'il!</t>
-        </is>
-      </c>
+      <c r="K330" s="1" t="inlineStr"/>
       <c r="L330" s="1" t="inlineStr"/>
       <c r="M330" s="1" t="inlineStr"/>
       <c r="N330" s="1" t="inlineStr"/>
@@ -15523,11 +13455,7 @@
       <c r="H331" s="1" t="inlineStr"/>
       <c r="I331" s="1" t="inlineStr"/>
       <c r="J331" s="1" t="inlineStr"/>
-      <c r="K331" s="1" t="inlineStr">
-        <is>
-          <t>L1819: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: promptement un tel maÃ®tre.</t>
-        </is>
-      </c>
+      <c r="K331" s="1" t="inlineStr"/>
       <c r="L331" s="1" t="inlineStr"/>
       <c r="M331" s="1" t="inlineStr"/>
       <c r="N331" s="1" t="inlineStr"/>
@@ -15562,11 +13490,7 @@
       <c r="H332" s="1" t="inlineStr"/>
       <c r="I332" s="1" t="inlineStr"/>
       <c r="J332" s="1" t="inlineStr"/>
-      <c r="K332" s="1" t="inlineStr">
-        <is>
-          <t>L1821: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: on classe l'historien amÃ©ricain School-</t>
-        </is>
-      </c>
+      <c r="K332" s="1" t="inlineStr"/>
       <c r="L332" s="1" t="inlineStr"/>
       <c r="M332" s="1" t="inlineStr"/>
       <c r="N332" s="1" t="inlineStr"/>
@@ -15578,7 +13502,7 @@
       <c r="P332" s="1" t="inlineStr"/>
       <c r="Q332" s="1" t="inlineStr">
         <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette PrÃ©fentaine, Legal ........</t>
+          <t>L954: punctuation artifact: repeated periods :: Laurette Préfentaine, Legal ........</t>
         </is>
       </c>
       <c r="R332" s="1" t="inlineStr"/>
@@ -15601,11 +13525,7 @@
       <c r="H333" s="1" t="inlineStr"/>
       <c r="I333" s="1" t="inlineStr"/>
       <c r="J333" s="1" t="inlineStr"/>
-      <c r="K333" s="1" t="inlineStr">
-        <is>
-          <t>L1822: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: craft, qui s'en servit pour pÃ©nÃ©trer au</t>
-        </is>
-      </c>
+      <c r="K333" s="1" t="inlineStr"/>
       <c r="L333" s="1" t="inlineStr"/>
       <c r="M333" s="1" t="inlineStr"/>
       <c r="N333" s="1" t="inlineStr"/>
@@ -15640,11 +13560,7 @@
       <c r="H334" s="1" t="inlineStr"/>
       <c r="I334" s="1" t="inlineStr"/>
       <c r="J334" s="1" t="inlineStr"/>
-      <c r="K334" s="1" t="inlineStr">
-        <is>
-          <t>L1823: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: coeur des tribus indiennes et les Ã©tudier</t>
-        </is>
-      </c>
+      <c r="K334" s="1" t="inlineStr"/>
       <c r="L334" s="1" t="inlineStr"/>
       <c r="M334" s="1" t="inlineStr"/>
       <c r="N334" s="1" t="inlineStr"/>
@@ -15679,11 +13595,7 @@
       <c r="H335" s="1" t="inlineStr"/>
       <c r="I335" s="1" t="inlineStr"/>
       <c r="J335" s="1" t="inlineStr"/>
-      <c r="K335" s="1" t="inlineStr">
-        <is>
-          <t>L1825: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: d'aventures, dont il ne se tira que grÃ¢ce</t>
-        </is>
-      </c>
+      <c r="K335" s="1" t="inlineStr"/>
       <c r="L335" s="1" t="inlineStr"/>
       <c r="M335" s="1" t="inlineStr"/>
       <c r="N335" s="1" t="inlineStr"/>
@@ -15718,11 +13630,7 @@
       <c r="H336" s="1" t="inlineStr"/>
       <c r="I336" s="1" t="inlineStr"/>
       <c r="J336" s="1" t="inlineStr"/>
-      <c r="K336" s="1" t="inlineStr">
-        <is>
-          <t>L1826: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã son extrÃªme habiletÃ©. Il mourut Ã</t>
-        </is>
-      </c>
+      <c r="K336" s="1" t="inlineStr"/>
       <c r="L336" s="1" t="inlineStr"/>
       <c r="M336" s="1" t="inlineStr"/>
       <c r="N336" s="1" t="inlineStr"/>
@@ -15757,11 +13665,7 @@
       <c r="H337" s="1" t="inlineStr"/>
       <c r="I337" s="1" t="inlineStr"/>
       <c r="J337" s="1" t="inlineStr"/>
-      <c r="K337" s="1" t="inlineStr">
-        <is>
-          <t>L1831: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Pierre MÃ©nard</t>
-        </is>
-      </c>
+      <c r="K337" s="1" t="inlineStr"/>
       <c r="L337" s="1" t="inlineStr"/>
       <c r="M337" s="1" t="inlineStr"/>
       <c r="N337" s="1" t="inlineStr"/>
@@ -15773,7 +13677,7 @@
       <c r="P337" s="1" t="inlineStr"/>
       <c r="Q337" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Robert Despins, Ã©cole Dunrobin .......</t>
+          <t>L966: punctuation artifact: repeated periods :: Robert Despins, école Dunrobin .......</t>
         </is>
       </c>
       <c r="R337" s="1" t="inlineStr"/>
@@ -15796,11 +13700,7 @@
       <c r="H338" s="1" t="inlineStr"/>
       <c r="I338" s="1" t="inlineStr"/>
       <c r="J338" s="1" t="inlineStr"/>
-      <c r="K338" s="1" t="inlineStr">
-        <is>
-          <t>L1839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: des Canadiens franÃ§ais de lâ€™Alberta.</t>
-        </is>
-      </c>
+      <c r="K338" s="1" t="inlineStr"/>
       <c r="L338" s="1" t="inlineStr"/>
       <c r="M338" s="1" t="inlineStr"/>
       <c r="N338" s="1" t="inlineStr"/>
@@ -15835,11 +13735,7 @@
       <c r="H339" s="1" t="inlineStr"/>
       <c r="I339" s="1" t="inlineStr"/>
       <c r="J339" s="1" t="inlineStr"/>
-      <c r="K339" s="1" t="inlineStr">
-        <is>
-          <t>L1844: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Autre fondateur de ville amÃ©ricaine,</t>
-        </is>
-      </c>
+      <c r="K339" s="1" t="inlineStr"/>
       <c r="L339" s="1" t="inlineStr"/>
       <c r="M339" s="1" t="inlineStr"/>
       <c r="N339" s="1" t="inlineStr"/>
@@ -15874,11 +13770,7 @@
       <c r="H340" s="1" t="inlineStr"/>
       <c r="I340" s="1" t="inlineStr"/>
       <c r="J340" s="1" t="inlineStr"/>
-      <c r="K340" s="1" t="inlineStr">
-        <is>
-          <t>L1851: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: , 1 ents qui se rendaient a washing- te et finit par s'Ã©tablir, en 1853, Ã Supe-</t>
-        </is>
-      </c>
+      <c r="K340" s="1" t="inlineStr"/>
       <c r="L340" s="1" t="inlineStr"/>
       <c r="M340" s="1" t="inlineStr"/>
       <c r="N340" s="1" t="inlineStr"/>
@@ -15890,7 +13782,7 @@
       <c r="P340" s="1" t="inlineStr"/>
       <c r="Q340" s="1" t="inlineStr">
         <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Huguette HÃ©tu. Bonnyville .....................</t>
+          <t>L972: punctuation artifact: repeated periods :: Huguette Hétu. Bonnyville .....................</t>
         </is>
       </c>
       <c r="R340" s="1" t="inlineStr"/>
@@ -15913,11 +13805,7 @@
       <c r="H341" s="1" t="inlineStr"/>
       <c r="I341" s="1" t="inlineStr"/>
       <c r="J341" s="1" t="inlineStr"/>
-      <c r="K341" s="1" t="inlineStr">
-        <is>
-          <t>L1852: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: ese comporta dans cette tÃ¢che en rior-City en compagnie de trois Cana-</t>
-        </is>
-      </c>
+      <c r="K341" s="1" t="inlineStr"/>
       <c r="L341" s="1" t="inlineStr"/>
       <c r="M341" s="1" t="inlineStr"/>
       <c r="N341" s="1" t="inlineStr"/>
@@ -15929,7 +13817,7 @@
       <c r="P341" s="1" t="inlineStr"/>
       <c r="Q341" s="1" t="inlineStr">
         <is>
-          <t>L974: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doris Aubin, Ã©cole consolidÃ©e, Falher .........</t>
+          <t>L974: punctuation artifact: repeated periods :: Doris Aubin, école consolidée, Falher .........</t>
         </is>
       </c>
       <c r="R341" s="1" t="inlineStr"/>
@@ -15952,11 +13840,7 @@
       <c r="H342" s="1" t="inlineStr"/>
       <c r="I342" s="1" t="inlineStr"/>
       <c r="J342" s="1" t="inlineStr"/>
-      <c r="K342" s="1" t="inlineStr">
-        <is>
-          <t>L1853: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: vrai patriote et en serviteur fidÃ¨le de la diens: Basile Saint-Denis, FranÃ§ois Roy</t>
-        </is>
-      </c>
+      <c r="K342" s="1" t="inlineStr"/>
       <c r="L342" s="1" t="inlineStr"/>
       <c r="M342" s="1" t="inlineStr"/>
       <c r="N342" s="1" t="inlineStr"/>
@@ -15991,11 +13875,7 @@
       <c r="H343" s="1" t="inlineStr"/>
       <c r="I343" s="1" t="inlineStr"/>
       <c r="J343" s="1" t="inlineStr"/>
-      <c r="K343" s="1" t="inlineStr">
-        <is>
-          <t>L1854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: patrie. On affirme, en effet, quâ€™il ne et Jean-Baptiste Samt-Jean.</t>
-        </is>
-      </c>
+      <c r="K343" s="1" t="inlineStr"/>
       <c r="L343" s="1" t="inlineStr"/>
       <c r="M343" s="1" t="inlineStr"/>
       <c r="N343" s="1" t="inlineStr"/>
@@ -16007,7 +13887,7 @@
       <c r="P343" s="1" t="inlineStr"/>
       <c r="Q343" s="1" t="inlineStr">
         <is>
-          <t>L978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Rosemary Heppeler, Ã©cole Thibeault ............</t>
+          <t>L978: punctuation artifact: repeated periods :: Rosemary Heppeler, école Thibeault ............</t>
         </is>
       </c>
       <c r="R343" s="1" t="inlineStr"/>
@@ -16030,11 +13910,7 @@
       <c r="H344" s="1" t="inlineStr"/>
       <c r="I344" s="1" t="inlineStr"/>
       <c r="J344" s="1" t="inlineStr"/>
-      <c r="K344" s="1" t="inlineStr">
-        <is>
-          <t>L1856: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vres avec l'Etat. Il est vrai que ce n'Ã©tait</t>
-        </is>
-      </c>
+      <c r="K344" s="1" t="inlineStr"/>
       <c r="L344" s="1" t="inlineStr"/>
       <c r="M344" s="1" t="inlineStr"/>
       <c r="N344" s="1" t="inlineStr"/>
@@ -16069,11 +13945,7 @@
       <c r="H345" s="1" t="inlineStr"/>
       <c r="I345" s="1" t="inlineStr"/>
       <c r="J345" s="1" t="inlineStr"/>
-      <c r="K345" s="1" t="inlineStr">
-        <is>
-          <t>L1859: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Loi sur la Taxation des Surplus de bÃ©nÃ©fices</t>
-        </is>
-      </c>
+      <c r="K345" s="1" t="inlineStr"/>
       <c r="L345" s="1" t="inlineStr"/>
       <c r="M345" s="1" t="inlineStr"/>
       <c r="N345" s="1" t="inlineStr"/>
@@ -16085,7 +13957,7 @@
       <c r="P345" s="1" t="inlineStr"/>
       <c r="Q345" s="1" t="inlineStr">
         <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Roland BÃ©rubÃ©. Beaumont .......................</t>
+          <t>L982: punctuation artifact: repeated periods :: Roland Bérubé. Beaumont .......................</t>
         </is>
       </c>
       <c r="R345" s="1" t="inlineStr"/>
@@ -16108,11 +13980,7 @@
       <c r="H346" s="1" t="inlineStr"/>
       <c r="I346" s="1" t="inlineStr"/>
       <c r="J346" s="1" t="inlineStr"/>
-      <c r="K346" s="1" t="inlineStr">
-        <is>
-          <t>L1860: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Demande concernant les bÃ©nÃ©fices normaux</t>
-        </is>
-      </c>
+      <c r="K346" s="1" t="inlineStr"/>
       <c r="L346" s="1" t="inlineStr"/>
       <c r="M346" s="1" t="inlineStr"/>
       <c r="N346" s="1" t="inlineStr"/>
@@ -16124,7 +13992,7 @@
       <c r="P346" s="1" t="inlineStr"/>
       <c r="Q346" s="1" t="inlineStr">
         <is>
-          <t>L984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claudette BÃ©rubÃ©, Beaumont ....................</t>
+          <t>L984: punctuation artifact: repeated periods :: Claudette Bérubé, Beaumont ....................</t>
         </is>
       </c>
       <c r="R346" s="1" t="inlineStr"/>
@@ -16147,11 +14015,7 @@
       <c r="H347" s="1" t="inlineStr"/>
       <c r="I347" s="1" t="inlineStr"/>
       <c r="J347" s="1" t="inlineStr"/>
-      <c r="K347" s="1" t="inlineStr">
-        <is>
-          <t>L1862: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: munitionnaire des vivres pour l'armÃ©e</t>
-        </is>
-      </c>
+      <c r="K347" s="1" t="inlineStr"/>
       <c r="L347" s="1" t="inlineStr"/>
       <c r="M347" s="1" t="inlineStr"/>
       <c r="N347" s="1" t="inlineStr"/>
@@ -16186,11 +14050,7 @@
       <c r="H348" s="1" t="inlineStr"/>
       <c r="I348" s="1" t="inlineStr"/>
       <c r="J348" s="1" t="inlineStr"/>
-      <c r="K348" s="1" t="inlineStr">
-        <is>
-          <t>L1864: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: rÃ©guliÃ¨re. Il suivit, en cette qualitÃ©, les</t>
-        </is>
-      </c>
+      <c r="K348" s="1" t="inlineStr"/>
       <c r="L348" s="1" t="inlineStr"/>
       <c r="M348" s="1" t="inlineStr"/>
       <c r="N348" s="1" t="inlineStr"/>
@@ -16225,11 +14085,7 @@
       <c r="H349" s="1" t="inlineStr"/>
       <c r="I349" s="1" t="inlineStr"/>
       <c r="J349" s="1" t="inlineStr"/>
-      <c r="K349" s="1" t="inlineStr">
-        <is>
-          <t>L1867: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Nous avons donnÃ©, la semaine der-</t>
-        </is>
-      </c>
+      <c r="K349" s="1" t="inlineStr"/>
       <c r="L349" s="1" t="inlineStr"/>
       <c r="M349" s="1" t="inlineStr"/>
       <c r="N349" s="1" t="inlineStr"/>
@@ -16241,7 +14097,7 @@
       <c r="P349" s="1" t="inlineStr"/>
       <c r="Q349" s="1" t="inlineStr">
         <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: FranÃ§oise Turcotte, Ã©cole Grandin .............</t>
+          <t>L990: punctuation artifact: repeated periods :: Françoise Turcotte, école Grandin .............</t>
         </is>
       </c>
       <c r="R349" s="1" t="inlineStr"/>
@@ -16264,11 +14120,7 @@
       <c r="H350" s="1" t="inlineStr"/>
       <c r="I350" s="1" t="inlineStr"/>
       <c r="J350" s="1" t="inlineStr"/>
-      <c r="K350" s="1" t="inlineStr">
-        <is>
-          <t>L1868: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: miÃ¨re, une courte biographie de trois</t>
-        </is>
-      </c>
+      <c r="K350" s="1" t="inlineStr"/>
       <c r="L350" s="1" t="inlineStr"/>
       <c r="M350" s="1" t="inlineStr"/>
       <c r="N350" s="1" t="inlineStr"/>
@@ -16303,11 +14155,7 @@
       <c r="H351" s="1" t="inlineStr"/>
       <c r="I351" s="1" t="inlineStr"/>
       <c r="J351" s="1" t="inlineStr"/>
-      <c r="K351" s="1" t="inlineStr">
-        <is>
-          <t>L1869: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN :: des nÃ´tres qui ont fondÃ© des villes aux</t>
-        </is>
-      </c>
+      <c r="K351" s="1" t="inlineStr"/>
       <c r="L351" s="1" t="inlineStr"/>
       <c r="M351" s="1" t="inlineStr"/>
       <c r="N351" s="1" t="inlineStr"/>
@@ -16342,11 +14190,7 @@
       <c r="H352" s="1" t="inlineStr"/>
       <c r="I352" s="1" t="inlineStr"/>
       <c r="J352" s="1" t="inlineStr"/>
-      <c r="K352" s="1" t="inlineStr">
-        <is>
-          <t>L1871: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: les noms sont inscrits dans le dÃ©velop-</t>
-        </is>
-      </c>
+      <c r="K352" s="1" t="inlineStr"/>
       <c r="L352" s="1" t="inlineStr"/>
       <c r="M352" s="1" t="inlineStr"/>
       <c r="N352" s="1" t="inlineStr"/>
@@ -16381,11 +14225,7 @@
       <c r="H353" s="1" t="inlineStr"/>
       <c r="I353" s="1" t="inlineStr"/>
       <c r="J353" s="1" t="inlineStr"/>
-      <c r="K353" s="1" t="inlineStr">
-        <is>
-          <t>L1872: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pement de la grande rÃ©publique amÃ©ri-</t>
-        </is>
-      </c>
+      <c r="K353" s="1" t="inlineStr"/>
       <c r="L353" s="1" t="inlineStr"/>
       <c r="M353" s="1" t="inlineStr"/>
       <c r="N353" s="1" t="inlineStr"/>
@@ -16420,11 +14260,7 @@
       <c r="H354" s="1" t="inlineStr"/>
       <c r="I354" s="1" t="inlineStr"/>
       <c r="J354" s="1" t="inlineStr"/>
-      <c r="K354" s="1" t="inlineStr">
-        <is>
-          <t>L1877: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Victor Beaudry</t>
-        </is>
-      </c>
+      <c r="K354" s="1" t="inlineStr"/>
       <c r="L354" s="1" t="inlineStr"/>
       <c r="M354" s="1" t="inlineStr"/>
       <c r="N354" s="1" t="inlineStr"/>
@@ -16436,7 +14272,7 @@
       <c r="P354" s="1" t="inlineStr"/>
       <c r="Q354" s="1" t="inlineStr">
         <is>
-          <t>L1002: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Arcand, Ã©cole Grandin ..................</t>
+          <t>L1002: punctuation artifact: repeated periods :: Marcel Arcand, école Grandin ..................</t>
         </is>
       </c>
       <c r="R354" s="1" t="inlineStr"/>
@@ -16459,11 +14295,7 @@
       <c r="H355" s="1" t="inlineStr"/>
       <c r="I355" s="1" t="inlineStr"/>
       <c r="J355" s="1" t="inlineStr"/>
-      <c r="K355" s="1" t="inlineStr">
-        <is>
-          <t>L1882: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont illustrÃ©s aux Etats-Unis, il n'en est</t>
-        </is>
-      </c>
+      <c r="K355" s="1" t="inlineStr"/>
       <c r="L355" s="1" t="inlineStr"/>
       <c r="M355" s="1" t="inlineStr"/>
       <c r="N355" s="1" t="inlineStr"/>
@@ -16498,11 +14330,7 @@
       <c r="H356" s="1" t="inlineStr"/>
       <c r="I356" s="1" t="inlineStr"/>
       <c r="J356" s="1" t="inlineStr"/>
-      <c r="K356" s="1" t="inlineStr">
-        <is>
-          <t>L1889: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nom, Ã©crit TassÃ©, mais l'annÃ©e suivante, honneur Ã leur pays d'origine que Pierre</t>
-        </is>
-      </c>
+      <c r="K356" s="1" t="inlineStr"/>
       <c r="L356" s="1" t="inlineStr"/>
       <c r="M356" s="1" t="inlineStr"/>
       <c r="N356" s="1" t="inlineStr"/>
@@ -16537,11 +14365,7 @@
       <c r="H357" s="1" t="inlineStr"/>
       <c r="I357" s="1" t="inlineStr"/>
       <c r="J357" s="1" t="inlineStr"/>
-      <c r="K357" s="1" t="inlineStr">
-        <is>
-          <t>L1890: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: elle voyait accourir des milliers de spÃ©-</t>
-        </is>
-      </c>
+      <c r="K357" s="1" t="inlineStr"/>
       <c r="L357" s="1" t="inlineStr"/>
       <c r="M357" s="1" t="inlineStr"/>
       <c r="N357" s="1" t="inlineStr"/>
@@ -16576,11 +14400,7 @@
       <c r="H358" s="1" t="inlineStr"/>
       <c r="I358" s="1" t="inlineStr"/>
       <c r="J358" s="1" t="inlineStr"/>
-      <c r="K358" s="1" t="inlineStr">
-        <is>
-          <t>L1892: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: MÃ©nard.</t>
-        </is>
-      </c>
+      <c r="K358" s="1" t="inlineStr"/>
       <c r="L358" s="1" t="inlineStr"/>
       <c r="M358" s="1" t="inlineStr"/>
       <c r="N358" s="1" t="inlineStr"/>
@@ -16615,11 +14435,7 @@
       <c r="H359" s="1" t="inlineStr"/>
       <c r="I359" s="1" t="inlineStr"/>
       <c r="J359" s="1" t="inlineStr"/>
-      <c r="K359" s="1" t="inlineStr">
-        <is>
-          <t>L1894: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Il naquit Ã QuÃ©bec en 1767. A dix-neuf</t>
-        </is>
-      </c>
+      <c r="K359" s="1" t="inlineStr"/>
       <c r="L359" s="1" t="inlineStr"/>
       <c r="M359" s="1" t="inlineStr"/>
       <c r="N359" s="1" t="inlineStr"/>
@@ -16631,7 +14447,7 @@
       <c r="P359" s="1" t="inlineStr"/>
       <c r="Q359" s="1" t="inlineStr">
         <is>
-          <t>L1012: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Bernard HÃ©bert, Saint-Vincent .................</t>
+          <t>L1012: punctuation artifact: repeated periods :: Bernard Hébert, Saint-Vincent .................</t>
         </is>
       </c>
       <c r="R359" s="1" t="inlineStr"/>
@@ -16654,11 +14470,7 @@
       <c r="H360" s="1" t="inlineStr"/>
       <c r="I360" s="1" t="inlineStr"/>
       <c r="J360" s="1" t="inlineStr"/>
-      <c r="K360" s="1" t="inlineStr">
-        <is>
-          <t>L1896: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans la sociÃ©tÃ© commerciale Lisa &amp; Cie,</t>
-        </is>
-      </c>
+      <c r="K360" s="1" t="inlineStr"/>
       <c r="L360" s="1" t="inlineStr"/>
       <c r="M360" s="1" t="inlineStr"/>
       <c r="N360" s="1" t="inlineStr"/>
@@ -16670,7 +14482,7 @@
       <c r="P360" s="1" t="inlineStr"/>
       <c r="Q360" s="1" t="inlineStr">
         <is>
-          <t>L1014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Tarcienne Meunier, Ã©cole Thibeault ............</t>
+          <t>L1014: punctuation artifact: repeated periods :: Tarcienne Meunier, école Thibeault ............</t>
         </is>
       </c>
       <c r="R360" s="1" t="inlineStr"/>
@@ -16693,11 +14505,7 @@
       <c r="H361" s="1" t="inlineStr"/>
       <c r="I361" s="1" t="inlineStr"/>
       <c r="J361" s="1" t="inlineStr"/>
-      <c r="K361" s="1" t="inlineStr">
-        <is>
-          <t>L1898: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: De rÃ©centes modifications apportÃ©es Ã la loi ci-dessus</t>
-        </is>
-      </c>
+      <c r="K361" s="1" t="inlineStr"/>
       <c r="L361" s="1" t="inlineStr"/>
       <c r="M361" s="1" t="inlineStr"/>
       <c r="N361" s="1" t="inlineStr"/>
@@ -16728,11 +14536,7 @@
       <c r="H362" s="1" t="inlineStr"/>
       <c r="I362" s="1" t="inlineStr"/>
       <c r="J362" s="1" t="inlineStr"/>
-      <c r="K362" s="1" t="inlineStr">
-        <is>
-          <t>L1899: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: portent que toute demande concernant les bÃ©nÃ©fices</t>
-        </is>
-      </c>
+      <c r="K362" s="1" t="inlineStr"/>
       <c r="L362" s="1" t="inlineStr"/>
       <c r="M362" s="1" t="inlineStr"/>
       <c r="N362" s="1" t="inlineStr"/>
@@ -16763,11 +14567,7 @@
       <c r="H363" s="1" t="inlineStr"/>
       <c r="I363" s="1" t="inlineStr"/>
       <c r="J363" s="1" t="inlineStr"/>
-      <c r="K363" s="1" t="inlineStr">
-        <is>
-          <t>L1900: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: normaux doit Ãªtre produite au MinistÃ¨re du Revenu</t>
-        </is>
-      </c>
+      <c r="K363" s="1" t="inlineStr"/>
       <c r="L363" s="1" t="inlineStr"/>
       <c r="M363" s="1" t="inlineStr"/>
       <c r="N363" s="1" t="inlineStr"/>
@@ -16798,11 +14598,7 @@
       <c r="H364" s="1" t="inlineStr"/>
       <c r="I364" s="1" t="inlineStr"/>
       <c r="J364" s="1" t="inlineStr"/>
-      <c r="K364" s="1" t="inlineStr">
-        <is>
-          <t>L1907: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ferme pas les renseignements exigÃ©s.</t>
-        </is>
-      </c>
+      <c r="K364" s="1" t="inlineStr"/>
       <c r="L364" s="1" t="inlineStr"/>
       <c r="M364" s="1" t="inlineStr"/>
       <c r="N364" s="1" t="inlineStr"/>
@@ -16833,11 +14629,7 @@
       <c r="H365" s="1" t="inlineStr"/>
       <c r="I365" s="1" t="inlineStr"/>
       <c r="J365" s="1" t="inlineStr"/>
-      <c r="K365" s="1" t="inlineStr">
-        <is>
-          <t>L1910: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: bureau de district de l'impÃ´t sur le revenu du gouverne-</t>
-        </is>
-      </c>
+      <c r="K365" s="1" t="inlineStr"/>
       <c r="L365" s="1" t="inlineStr"/>
       <c r="M365" s="1" t="inlineStr"/>
       <c r="N365" s="1" t="inlineStr"/>
@@ -16845,7 +14637,7 @@
       <c r="P365" s="1" t="inlineStr"/>
       <c r="Q365" s="1" t="inlineStr">
         <is>
-          <t>L1024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AdÃ©lard SÃ©guin, Bonnyville ....................</t>
+          <t>L1024: punctuation artifact: repeated periods :: Adélard Séguin, Bonnyville ....................</t>
         </is>
       </c>
       <c r="R365" s="1" t="inlineStr"/>
@@ -16868,11 +14660,7 @@
       <c r="H366" s="1" t="inlineStr"/>
       <c r="I366" s="1" t="inlineStr"/>
       <c r="J366" s="1" t="inlineStr"/>
-      <c r="K366" s="1" t="inlineStr">
-        <is>
-          <t>L1911: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ment fÃ©dÃ©ral.</t>
-        </is>
-      </c>
+      <c r="K366" s="1" t="inlineStr"/>
       <c r="L366" s="1" t="inlineStr"/>
       <c r="M366" s="1" t="inlineStr"/>
       <c r="N366" s="1" t="inlineStr"/>
@@ -16880,7 +14668,7 @@
       <c r="P366" s="1" t="inlineStr"/>
       <c r="Q366" s="1" t="inlineStr">
         <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Carmen Tellier, Ã©cole Thibeault ...............</t>
+          <t>L1028: punctuation artifact: repeated periods :: Carmen Tellier, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R366" s="1" t="inlineStr"/>
@@ -16903,11 +14691,7 @@
       <c r="H367" s="1" t="inlineStr"/>
       <c r="I367" s="1" t="inlineStr"/>
       <c r="J367" s="1" t="inlineStr"/>
-      <c r="K367" s="1" t="inlineStr">
-        <is>
-          <t>L1913: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les renseignements pertinents exigÃ©s dans la formule</t>
-        </is>
-      </c>
+      <c r="K367" s="1" t="inlineStr"/>
       <c r="L367" s="1" t="inlineStr"/>
       <c r="M367" s="1" t="inlineStr"/>
       <c r="N367" s="1" t="inlineStr"/>
@@ -16915,7 +14699,7 @@
       <c r="P367" s="1" t="inlineStr"/>
       <c r="Q367" s="1" t="inlineStr">
         <is>
-          <t>L1030: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Muriel Walker, Ã©cole Thibeault ...............</t>
+          <t>L1030: punctuation artifact: repeated periods :: Muriel Walker, école Thibeault ...............</t>
         </is>
       </c>
       <c r="R367" s="1" t="inlineStr"/>
@@ -16938,11 +14722,7 @@
       <c r="H368" s="1" t="inlineStr"/>
       <c r="I368" s="1" t="inlineStr"/>
       <c r="J368" s="1" t="inlineStr"/>
-      <c r="K368" s="1" t="inlineStr">
-        <is>
-          <t>L1915: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: formules d'essai et les formulÃ©s incomplÃ¨tes, de mÃªme</t>
-        </is>
-      </c>
+      <c r="K368" s="1" t="inlineStr"/>
       <c r="L368" s="1" t="inlineStr"/>
       <c r="M368" s="1" t="inlineStr"/>
       <c r="N368" s="1" t="inlineStr"/>
@@ -16973,11 +14753,7 @@
       <c r="H369" s="1" t="inlineStr"/>
       <c r="I369" s="1" t="inlineStr"/>
       <c r="J369" s="1" t="inlineStr"/>
-      <c r="K369" s="1" t="inlineStr">
-        <is>
-          <t>L1916: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: que celles produites aprÃ¨s le 31 aoÃ»t 1947, ne seront pas</t>
-        </is>
-      </c>
+      <c r="K369" s="1" t="inlineStr"/>
       <c r="L369" s="1" t="inlineStr"/>
       <c r="M369" s="1" t="inlineStr"/>
       <c r="N369" s="1" t="inlineStr"/>
@@ -17008,11 +14784,7 @@
       <c r="H370" s="1" t="inlineStr"/>
       <c r="I370" s="1" t="inlineStr"/>
       <c r="J370" s="1" t="inlineStr"/>
-      <c r="K370" s="1" t="inlineStr">
-        <is>
-          <t>L1917: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: acceptÃ©es.</t>
-        </is>
-      </c>
+      <c r="K370" s="1" t="inlineStr"/>
       <c r="L370" s="1" t="inlineStr"/>
       <c r="M370" s="1" t="inlineStr"/>
       <c r="N370" s="1" t="inlineStr"/>
@@ -17043,11 +14815,7 @@
       <c r="H371" s="1" t="inlineStr"/>
       <c r="I371" s="1" t="inlineStr"/>
       <c r="J371" s="1" t="inlineStr"/>
-      <c r="K371" s="1" t="inlineStr">
-        <is>
-          <t>L1919: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: MinistÃ¨re du Revenu National</t>
-        </is>
-      </c>
+      <c r="K371" s="1" t="inlineStr"/>
       <c r="L371" s="1" t="inlineStr"/>
       <c r="M371" s="1" t="inlineStr"/>
       <c r="N371" s="1" t="inlineStr"/>
@@ -17055,7 +14823,7 @@
       <c r="P371" s="1" t="inlineStr"/>
       <c r="Q371" s="1" t="inlineStr">
         <is>
-          <t>L1042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: GÃ©rard-Meunier, Ã©cole Thibeault ..</t>
+          <t>L1042: punctuation artifact: repeated periods :: Gérard-Meunier, école Thibeault ..</t>
         </is>
       </c>
       <c r="R371" s="1" t="inlineStr"/>
@@ -17078,11 +14846,7 @@
       <c r="H372" s="1" t="inlineStr"/>
       <c r="I372" s="1" t="inlineStr"/>
       <c r="J372" s="1" t="inlineStr"/>
-      <c r="K372" s="1" t="inlineStr">
-        <is>
-          <t>L1926: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: geaient rien moins qu'Ã dÃ©trÃ´ner Chica-</t>
-        </is>
-      </c>
+      <c r="K372" s="1" t="inlineStr"/>
       <c r="L372" s="1" t="inlineStr"/>
       <c r="M372" s="1" t="inlineStr"/>
       <c r="N372" s="1" t="inlineStr"/>
@@ -17113,11 +14877,7 @@
       <c r="H373" s="1" t="inlineStr"/>
       <c r="I373" s="1" t="inlineStr"/>
       <c r="J373" s="1" t="inlineStr"/>
-      <c r="K373" s="1" t="inlineStr">
-        <is>
-          <t>L1928: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: go. Ils s'imaginaient qu'elle Ã©tait appe-</t>
-        </is>
-      </c>
+      <c r="K373" s="1" t="inlineStr"/>
       <c r="L373" s="1" t="inlineStr"/>
       <c r="M373" s="1" t="inlineStr"/>
       <c r="N373" s="1" t="inlineStr"/>
@@ -17148,11 +14908,7 @@
       <c r="H374" s="1" t="inlineStr"/>
       <c r="I374" s="1" t="inlineStr"/>
       <c r="J374" s="1" t="inlineStr"/>
-      <c r="K374" s="1" t="inlineStr">
-        <is>
-          <t>L1929: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT, U+20AC EURO SIGN | punctuation artifact: repeated periods :: la fonte des mine- lÃ©e Ã devenir l'entrepÃ´t des produits du ..........__â€ž</t>
-        </is>
-      </c>
+      <c r="K374" s="1" t="inlineStr"/>
       <c r="L374" s="1" t="inlineStr"/>
       <c r="M374" s="1" t="inlineStr"/>
       <c r="N374" s="1" t="inlineStr"/>
@@ -17183,11 +14939,7 @@
       <c r="H375" s="1" t="inlineStr"/>
       <c r="I375" s="1" t="inlineStr"/>
       <c r="J375" s="1" t="inlineStr"/>
-      <c r="K375" s="1" t="inlineStr">
-        <is>
-          <t>L1931: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Nord-Ouest, le port le plus frÃ©quente de quâ€™aux Rocheuses. NommÃ© plus tard a-</t>
-        </is>
-      </c>
+      <c r="K375" s="1" t="inlineStr"/>
       <c r="L375" s="1" t="inlineStr"/>
       <c r="M375" s="1" t="inlineStr"/>
       <c r="N375" s="1" t="inlineStr"/>
@@ -17218,11 +14970,7 @@
       <c r="H376" s="1" t="inlineStr"/>
       <c r="I376" s="1" t="inlineStr"/>
       <c r="J376" s="1" t="inlineStr"/>
-      <c r="K376" s="1" t="inlineStr">
-        <is>
-          <t>L1932: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tous les lacs. Ils n'avaient pas songÃ© que</t>
-        </is>
-      </c>
+      <c r="K376" s="1" t="inlineStr"/>
       <c r="L376" s="1" t="inlineStr"/>
       <c r="M376" s="1" t="inlineStr"/>
       <c r="N376" s="1" t="inlineStr"/>
@@ -17253,11 +15001,7 @@
       <c r="H377" s="1" t="inlineStr"/>
       <c r="I377" s="1" t="inlineStr"/>
       <c r="J377" s="1" t="inlineStr"/>
-      <c r="K377" s="1" t="inlineStr">
-        <is>
-          <t>L1936: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã Independance. Il dÃ©couvrit un nou-</t>
-        </is>
-      </c>
+      <c r="K377" s="1" t="inlineStr"/>
       <c r="L377" s="1" t="inlineStr"/>
       <c r="M377" s="1" t="inlineStr"/>
       <c r="N377" s="1" t="inlineStr"/>
@@ -17288,11 +15032,7 @@
       <c r="H378" s="1" t="inlineStr"/>
       <c r="I378" s="1" t="inlineStr"/>
       <c r="J378" s="1" t="inlineStr"/>
-      <c r="K378" s="1" t="inlineStr">
-        <is>
-          <t>L1938: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: veau procÃ©dÃ© pour</t>
-        </is>
-      </c>
+      <c r="K378" s="1" t="inlineStr"/>
       <c r="L378" s="1" t="inlineStr"/>
       <c r="M378" s="1" t="inlineStr"/>
       <c r="N378" s="1" t="inlineStr"/>
@@ -17323,11 +15063,7 @@
       <c r="H379" s="1" t="inlineStr"/>
       <c r="I379" s="1" t="inlineStr"/>
       <c r="J379" s="1" t="inlineStr"/>
-      <c r="K379" s="1" t="inlineStr">
-        <is>
-          <t>L1940: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: lui assurÃ¨rent un revenu considÃ©rable.</t>
-        </is>
-      </c>
+      <c r="K379" s="1" t="inlineStr"/>
       <c r="L379" s="1" t="inlineStr"/>
       <c r="M379" s="1" t="inlineStr"/>
       <c r="N379" s="1" t="inlineStr"/>
@@ -17358,11 +15094,7 @@
       <c r="H380" s="1" t="inlineStr"/>
       <c r="I380" s="1" t="inlineStr"/>
       <c r="J380" s="1" t="inlineStr"/>
-      <c r="K380" s="1" t="inlineStr">
-        <is>
-          <t>L1942: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Personne n'a manifestÃ© plus d'esprit</t>
-        </is>
-      </c>
+      <c r="K380" s="1" t="inlineStr"/>
       <c r="L380" s="1" t="inlineStr"/>
       <c r="M380" s="1" t="inlineStr"/>
       <c r="N380" s="1" t="inlineStr"/>
@@ -17370,7 +15102,7 @@
       <c r="P380" s="1" t="inlineStr"/>
       <c r="Q380" s="1" t="inlineStr">
         <is>
-          <t>L1095: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. Ã©cole consolidÃ©e, Donnelly ............7C</t>
+          <t>L1095: punctuation artifact: repeated periods | suspicious token(s): 7C (letter/digit mix) :: 89 Monique Roy. école consolidée, Donnelly ............7C</t>
         </is>
       </c>
       <c r="R380" s="1" t="inlineStr"/>
@@ -17393,11 +15125,7 @@
       <c r="H381" s="1" t="inlineStr"/>
       <c r="I381" s="1" t="inlineStr"/>
       <c r="J381" s="1" t="inlineStr"/>
-      <c r="K381" s="1" t="inlineStr">
-        <is>
-          <t>L1943: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'initiative dans le dÃ©veloppement de</t>
-        </is>
-      </c>
+      <c r="K381" s="1" t="inlineStr"/>
       <c r="L381" s="1" t="inlineStr"/>
       <c r="M381" s="1" t="inlineStr"/>
       <c r="N381" s="1" t="inlineStr"/>
@@ -17428,11 +15156,7 @@
       <c r="H382" s="1" t="inlineStr"/>
       <c r="I382" s="1" t="inlineStr"/>
       <c r="J382" s="1" t="inlineStr"/>
-      <c r="K382" s="1" t="inlineStr">
-        <is>
-          <t>L1944: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: : l'Ouest amÃ©ricain que les frÃ¨res Beau-</t>
-        </is>
-      </c>
+      <c r="K382" s="1" t="inlineStr"/>
       <c r="L382" s="1" t="inlineStr"/>
       <c r="M382" s="1" t="inlineStr"/>
       <c r="N382" s="1" t="inlineStr"/>
@@ -17463,11 +15187,7 @@
       <c r="H383" s="1" t="inlineStr"/>
       <c r="I383" s="1" t="inlineStr"/>
       <c r="J383" s="1" t="inlineStr"/>
-      <c r="K383" s="1" t="inlineStr">
-        <is>
-          <t>L1948: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: carriÃ¨re presque aussi Ã©tonnante. Il na-</t>
-        </is>
-      </c>
+      <c r="K383" s="1" t="inlineStr"/>
       <c r="L383" s="1" t="inlineStr"/>
       <c r="M383" s="1" t="inlineStr"/>
       <c r="N383" s="1" t="inlineStr"/>
@@ -17498,11 +15218,7 @@
       <c r="H384" s="1" t="inlineStr"/>
       <c r="I384" s="1" t="inlineStr"/>
       <c r="J384" s="1" t="inlineStr"/>
-      <c r="K384" s="1" t="inlineStr">
-        <is>
-          <t>L1950: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: -fÃ©vrier 1831. Il n'avait que dix-huit ans</t>
-        </is>
-      </c>
+      <c r="K384" s="1" t="inlineStr"/>
       <c r="L384" s="1" t="inlineStr"/>
       <c r="M384" s="1" t="inlineStr"/>
       <c r="N384" s="1" t="inlineStr"/>
@@ -17533,11 +15249,7 @@
       <c r="H385" s="1" t="inlineStr"/>
       <c r="I385" s="1" t="inlineStr"/>
       <c r="J385" s="1" t="inlineStr"/>
-      <c r="K385" s="1" t="inlineStr">
-        <is>
-          <t>L1954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s'Ã©tendaient jus-</t>
-        </is>
-      </c>
+      <c r="K385" s="1" t="inlineStr"/>
       <c r="L385" s="1" t="inlineStr"/>
       <c r="M385" s="1" t="inlineStr"/>
       <c r="N385" s="1" t="inlineStr"/>
@@ -17568,11 +15280,7 @@
       <c r="H386" s="1" t="inlineStr"/>
       <c r="I386" s="1" t="inlineStr"/>
       <c r="J386" s="1" t="inlineStr"/>
-      <c r="K386" s="1" t="inlineStr">
-        <is>
-          <t>L1956: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dont les opÃ©rations</t>
-        </is>
-      </c>
+      <c r="K386" s="1" t="inlineStr"/>
       <c r="L386" s="1" t="inlineStr"/>
       <c r="M386" s="1" t="inlineStr"/>
       <c r="N386" s="1" t="inlineStr"/>
@@ -17603,11 +15311,7 @@
       <c r="H387" s="1" t="inlineStr"/>
       <c r="I387" s="1" t="inlineStr"/>
       <c r="J387" s="1" t="inlineStr"/>
-      <c r="K387" s="1" t="inlineStr">
-        <is>
-          <t>L1959: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des Etats-Unis, il rÃ©ussit Ã conclure des</t>
-        </is>
-      </c>
+      <c r="K387" s="1" t="inlineStr"/>
       <c r="L387" s="1" t="inlineStr"/>
       <c r="M387" s="1" t="inlineStr"/>
       <c r="N387" s="1" t="inlineStr"/>
@@ -17638,11 +15342,7 @@
       <c r="H388" s="1" t="inlineStr"/>
       <c r="I388" s="1" t="inlineStr"/>
       <c r="J388" s="1" t="inlineStr"/>
-      <c r="K388" s="1" t="inlineStr">
-        <is>
-          <t>L1960: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: traitÃ©s avec plusieurs tribus. Aux Ã©lec-</t>
-        </is>
-      </c>
+      <c r="K388" s="1" t="inlineStr"/>
       <c r="L388" s="1" t="inlineStr"/>
       <c r="M388" s="1" t="inlineStr"/>
       <c r="N388" s="1" t="inlineStr"/>
@@ -17673,11 +15373,7 @@
       <c r="H389" s="1" t="inlineStr"/>
       <c r="I389" s="1" t="inlineStr"/>
       <c r="J389" s="1" t="inlineStr"/>
-      <c r="K389" s="1" t="inlineStr">
-        <is>
-          <t>L1961: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: tions de 1803, il obtint un siÃ¨ge Ã la</t>
-        </is>
-      </c>
+      <c r="K389" s="1" t="inlineStr"/>
       <c r="L389" s="1" t="inlineStr"/>
       <c r="M389" s="1" t="inlineStr"/>
       <c r="N389" s="1" t="inlineStr"/>
@@ -17708,11 +15404,7 @@
       <c r="H390" s="1" t="inlineStr"/>
       <c r="I390" s="1" t="inlineStr"/>
       <c r="J390" s="1" t="inlineStr"/>
-      <c r="K390" s="1" t="inlineStr">
-        <is>
-          <t>L1962: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LÃ©gislature de lâ€™Indiana. Plus tard, on le</t>
-        </is>
-      </c>
+      <c r="K390" s="1" t="inlineStr"/>
       <c r="L390" s="1" t="inlineStr"/>
       <c r="M390" s="1" t="inlineStr"/>
       <c r="N390" s="1" t="inlineStr"/>
@@ -17743,11 +15435,7 @@
       <c r="H391" s="1" t="inlineStr"/>
       <c r="I391" s="1" t="inlineStr"/>
       <c r="J391" s="1" t="inlineStr"/>
-      <c r="K391" s="1" t="inlineStr">
-        <is>
-          <t>L1963: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©signa unanimement comme prÃ©sident</t>
-        </is>
-      </c>
+      <c r="K391" s="1" t="inlineStr"/>
       <c r="L391" s="1" t="inlineStr"/>
       <c r="M391" s="1" t="inlineStr"/>
       <c r="N391" s="1" t="inlineStr"/>
@@ -17778,11 +15466,7 @@
       <c r="H392" s="1" t="inlineStr"/>
       <c r="I392" s="1" t="inlineStr"/>
       <c r="J392" s="1" t="inlineStr"/>
-      <c r="K392" s="1" t="inlineStr">
-        <is>
-          <t>L1964: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: du Conseil lÃ©gislatif. Le scrutin mÃªme</t>
-        </is>
-      </c>
+      <c r="K392" s="1" t="inlineStr"/>
       <c r="L392" s="1" t="inlineStr"/>
       <c r="M392" s="1" t="inlineStr"/>
       <c r="N392" s="1" t="inlineStr"/>
@@ -17813,11 +15497,7 @@
       <c r="H393" s="1" t="inlineStr"/>
       <c r="I393" s="1" t="inlineStr"/>
       <c r="J393" s="1" t="inlineStr"/>
-      <c r="K393" s="1" t="inlineStr">
-        <is>
-          <t>L1966: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: aprÃ¨s que l'on eut modifiÃ© spÃ©cialement</t>
-        </is>
-      </c>
+      <c r="K393" s="1" t="inlineStr"/>
       <c r="L393" s="1" t="inlineStr"/>
       <c r="M393" s="1" t="inlineStr"/>
       <c r="N393" s="1" t="inlineStr"/>
@@ -17848,11 +15528,7 @@
       <c r="H394" s="1" t="inlineStr"/>
       <c r="I394" s="1" t="inlineStr"/>
       <c r="J394" s="1" t="inlineStr"/>
-      <c r="K394" s="1" t="inlineStr">
-        <is>
-          <t>L1967: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la Constitution afin de rendre son Ã©lec-</t>
-        </is>
-      </c>
+      <c r="K394" s="1" t="inlineStr"/>
       <c r="L394" s="1" t="inlineStr"/>
       <c r="M394" s="1" t="inlineStr"/>
       <c r="N394" s="1" t="inlineStr"/>
@@ -17883,11 +15559,7 @@
       <c r="H395" s="1" t="inlineStr"/>
       <c r="I395" s="1" t="inlineStr"/>
       <c r="J395" s="1" t="inlineStr"/>
-      <c r="K395" s="1" t="inlineStr">
-        <is>
-          <t>L1973: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: L'hon. MÃ©nard avait su l'acquÃ©rir grÃ¢ce</t>
-        </is>
-      </c>
+      <c r="K395" s="1" t="inlineStr"/>
       <c r="L395" s="1" t="inlineStr"/>
       <c r="M395" s="1" t="inlineStr"/>
       <c r="N395" s="1" t="inlineStr"/>
@@ -17918,11 +15590,7 @@
       <c r="H396" s="1" t="inlineStr"/>
       <c r="I396" s="1" t="inlineStr"/>
       <c r="J396" s="1" t="inlineStr"/>
-      <c r="K396" s="1" t="inlineStr">
-        <is>
-          <t>L1978: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la CitÃ© du SupÃ©rieur n'avait pas encore</t>
-        </is>
-      </c>
+      <c r="K396" s="1" t="inlineStr"/>
       <c r="L396" s="1" t="inlineStr"/>
       <c r="M396" s="1" t="inlineStr"/>
       <c r="N396" s="1" t="inlineStr"/>
@@ -17953,11 +15621,7 @@
       <c r="H397" s="1" t="inlineStr"/>
       <c r="I397" s="1" t="inlineStr"/>
       <c r="J397" s="1" t="inlineStr"/>
-      <c r="K397" s="1" t="inlineStr">
-        <is>
-          <t>L1979: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: derriÃ¨re elle de campagnes cultivÃ©es, ni</t>
-        </is>
-      </c>
+      <c r="K397" s="1" t="inlineStr"/>
       <c r="L397" s="1" t="inlineStr"/>
       <c r="M397" s="1" t="inlineStr"/>
       <c r="N397" s="1" t="inlineStr"/>
@@ -17988,11 +15652,7 @@
       <c r="H398" s="1" t="inlineStr"/>
       <c r="I398" s="1" t="inlineStr"/>
       <c r="J398" s="1" t="inlineStr"/>
-      <c r="K398" s="1" t="inlineStr">
-        <is>
-          <t>L1980: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mÃªme une voie ferrÃ©e. Aussi elle est pas-</t>
-        </is>
-      </c>
+      <c r="K398" s="1" t="inlineStr"/>
       <c r="L398" s="1" t="inlineStr"/>
       <c r="M398" s="1" t="inlineStr"/>
       <c r="N398" s="1" t="inlineStr"/>
@@ -18023,11 +15683,7 @@
       <c r="H399" s="1" t="inlineStr"/>
       <c r="I399" s="1" t="inlineStr"/>
       <c r="J399" s="1" t="inlineStr"/>
-      <c r="K399" s="1" t="inlineStr">
-        <is>
-          <t>L1981: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sÃ©e, la pauvre ville, comme passent les</t>
-        </is>
-      </c>
+      <c r="K399" s="1" t="inlineStr"/>
       <c r="L399" s="1" t="inlineStr"/>
       <c r="M399" s="1" t="inlineStr"/>
       <c r="N399" s="1" t="inlineStr"/>
@@ -18058,11 +15714,7 @@
       <c r="H400" s="1" t="inlineStr"/>
       <c r="I400" s="1" t="inlineStr"/>
       <c r="J400" s="1" t="inlineStr"/>
-      <c r="K400" s="1" t="inlineStr">
-        <is>
-          <t>L1984: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: "Lefebvre Ã©tait l'un des plus intrÃ©pi-1</t>
-        </is>
-      </c>
+      <c r="K400" s="1" t="inlineStr"/>
       <c r="L400" s="1" t="inlineStr"/>
       <c r="M400" s="1" t="inlineStr"/>
       <c r="N400" s="1" t="inlineStr"/>
@@ -18093,11 +15745,7 @@
       <c r="H401" s="1" t="inlineStr"/>
       <c r="I401" s="1" t="inlineStr"/>
       <c r="J401" s="1" t="inlineStr"/>
-      <c r="K401" s="1" t="inlineStr">
-        <is>
-          <t>L1988: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ses jambes. La diligence Ã©tait inconnue</t>
-        </is>
-      </c>
+      <c r="K401" s="1" t="inlineStr"/>
       <c r="L401" s="1" t="inlineStr"/>
       <c r="M401" s="1" t="inlineStr"/>
       <c r="N401" s="1" t="inlineStr"/>
@@ -18128,11 +15776,7 @@
       <c r="H402" s="1" t="inlineStr"/>
       <c r="I402" s="1" t="inlineStr"/>
       <c r="J402" s="1" t="inlineStr"/>
-      <c r="K402" s="1" t="inlineStr">
-        <is>
-          <t>L1990: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vait pas encore fait retentir les Ã©chos du</t>
-        </is>
-      </c>
+      <c r="K402" s="1" t="inlineStr"/>
       <c r="L402" s="1" t="inlineStr"/>
       <c r="M402" s="1" t="inlineStr"/>
       <c r="N402" s="1" t="inlineStr"/>
@@ -18163,11 +15807,7 @@
       <c r="H403" s="1" t="inlineStr"/>
       <c r="I403" s="1" t="inlineStr"/>
       <c r="J403" s="1" t="inlineStr"/>
-      <c r="K403" s="1" t="inlineStr">
-        <is>
-          <t>L1992: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Quatre jeunes gens ont passÃ© la moi lac SupÃ©rieur." Les voyageurs ne pou-</t>
-        </is>
-      </c>
+      <c r="K403" s="1" t="inlineStr"/>
       <c r="L403" s="1" t="inlineStr"/>
       <c r="M403" s="1" t="inlineStr"/>
       <c r="N403" s="1" t="inlineStr"/>
@@ -18198,11 +15838,7 @@
       <c r="H404" s="1" t="inlineStr"/>
       <c r="I404" s="1" t="inlineStr"/>
       <c r="J404" s="1" t="inlineStr"/>
-      <c r="K404" s="1" t="inlineStr">
-        <is>
-          <t>L1993: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tiÃ© de la nuit Ã jouer. En se sÃ©parant, ! vaient trouver de meilleur guide que Le-</t>
-        </is>
-      </c>
+      <c r="K404" s="1" t="inlineStr"/>
       <c r="L404" s="1" t="inlineStr"/>
       <c r="M404" s="1" t="inlineStr"/>
       <c r="N404" s="1" t="inlineStr"/>
@@ -18233,11 +15869,7 @@
       <c r="H405" s="1" t="inlineStr"/>
       <c r="I405" s="1" t="inlineStr"/>
       <c r="J405" s="1" t="inlineStr"/>
-      <c r="K405" s="1" t="inlineStr">
-        <is>
-          <t>L1995: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chacun a gagnÃ© 40 francs, et que per-!piaines et les forÃªts environnantes. Il</t>
-        </is>
-      </c>
+      <c r="K405" s="1" t="inlineStr"/>
       <c r="L405" s="1" t="inlineStr"/>
       <c r="M405" s="1" t="inlineStr"/>
       <c r="N405" s="1" t="inlineStr"/>
@@ -18268,11 +15900,7 @@
       <c r="H406" s="1" t="inlineStr"/>
       <c r="I406" s="1" t="inlineStr"/>
       <c r="J406" s="1" t="inlineStr"/>
-      <c r="K406" s="1" t="inlineStr">
-        <is>
-          <t>L1998: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Comment cela peut-il se faire? ses histoires dramatiques, faire oublier</t>
-        </is>
-      </c>
+      <c r="K406" s="1" t="inlineStr"/>
       <c r="L406" s="1" t="inlineStr"/>
       <c r="M406" s="1" t="inlineStr"/>
       <c r="N406" s="1" t="inlineStr"/>
@@ -18303,11 +15931,7 @@
       <c r="H407" s="1" t="inlineStr"/>
       <c r="I407" s="1" t="inlineStr"/>
       <c r="J407" s="1" t="inlineStr"/>
-      <c r="K407" s="1" t="inlineStr">
-        <is>
-          <t>L1999: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: â€”C'est que tous les quatre sont des les fatigues de la journÃ©e. Parmi ceux</t>
-        </is>
-      </c>
+      <c r="K407" s="1" t="inlineStr"/>
       <c r="L407" s="1" t="inlineStr"/>
       <c r="M407" s="1" t="inlineStr"/>
       <c r="N407" s="1" t="inlineStr"/>
@@ -18338,11 +15962,7 @@
       <c r="H408" s="1" t="inlineStr"/>
       <c r="I408" s="1" t="inlineStr"/>
       <c r="J408" s="1" t="inlineStr"/>
-      <c r="K408" s="1" t="inlineStr">
-        <is>
-          <t>L2000: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: joueurs de violon. qui bÃ©nÃ©ficiÃ¨rent de ses connaissances,</t>
-        </is>
-      </c>
+      <c r="K408" s="1" t="inlineStr"/>
       <c r="L408" s="1" t="inlineStr"/>
       <c r="M408" s="1" t="inlineStr"/>
       <c r="N408" s="1" t="inlineStr"/>
@@ -18373,11 +15993,7 @@
       <c r="H409" s="1" t="inlineStr"/>
       <c r="I409" s="1" t="inlineStr"/>
       <c r="J409" s="1" t="inlineStr"/>
-      <c r="K409" s="1" t="inlineStr">
-        <is>
-          <t>L2002: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: vie de grandes entreprises, dâ€™as-</t>
-        </is>
-      </c>
+      <c r="K409" s="1" t="inlineStr"/>
       <c r="L409" s="1" t="inlineStr"/>
       <c r="M409" s="1" t="inlineStr"/>
       <c r="N409" s="1" t="inlineStr"/>
@@ -18408,11 +16024,7 @@
       <c r="H410" s="1" t="inlineStr"/>
       <c r="I410" s="1" t="inlineStr"/>
       <c r="J410" s="1" t="inlineStr"/>
-      <c r="K410" s="1" t="inlineStr">
-        <is>
-          <t>L2005: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: quoi satisfaire les amateurs dâ€™a-</t>
-        </is>
-      </c>
+      <c r="K410" s="1" t="inlineStr"/>
       <c r="L410" s="1" t="inlineStr"/>
       <c r="M410" s="1" t="inlineStr"/>
       <c r="N410" s="1" t="inlineStr"/>
@@ -18443,11 +16055,7 @@
       <c r="H411" s="1" t="inlineStr"/>
       <c r="I411" s="1" t="inlineStr"/>
       <c r="J411" s="1" t="inlineStr"/>
-      <c r="K411" s="1" t="inlineStr">
-        <is>
-          <t>L2013: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: aussi les menaces de la ruine dÃ©finitive.</t>
-        </is>
-      </c>
+      <c r="K411" s="1" t="inlineStr"/>
       <c r="L411" s="1" t="inlineStr"/>
       <c r="M411" s="1" t="inlineStr"/>
       <c r="N411" s="1" t="inlineStr"/>
@@ -18478,11 +16086,7 @@
       <c r="H412" s="1" t="inlineStr"/>
       <c r="I412" s="1" t="inlineStr"/>
       <c r="J412" s="1" t="inlineStr"/>
-      <c r="K412" s="1" t="inlineStr">
-        <is>
-          <t>L2014: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: MalgrÃ© toutes les pertes que Beaudry</t>
-        </is>
-      </c>
+      <c r="K412" s="1" t="inlineStr"/>
       <c r="L412" s="1" t="inlineStr"/>
       <c r="M412" s="1" t="inlineStr"/>
       <c r="N412" s="1" t="inlineStr"/>
@@ -18513,11 +16117,7 @@
       <c r="H413" s="1" t="inlineStr"/>
       <c r="I413" s="1" t="inlineStr"/>
       <c r="J413" s="1" t="inlineStr"/>
-      <c r="K413" s="1" t="inlineStr">
-        <is>
-          <t>L2015: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: eut Ã subir, il rÃ©ussit Ã se constituer une</t>
-        </is>
-      </c>
+      <c r="K413" s="1" t="inlineStr"/>
       <c r="L413" s="1" t="inlineStr"/>
       <c r="M413" s="1" t="inlineStr"/>
       <c r="N413" s="1" t="inlineStr"/>
@@ -18548,11 +16148,7 @@
       <c r="H414" s="1" t="inlineStr"/>
       <c r="I414" s="1" t="inlineStr"/>
       <c r="J414" s="1" t="inlineStr"/>
-      <c r="K414" s="1" t="inlineStr">
-        <is>
-          <t>L2019: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dire autant que "tÃ©moin", et pour avoir</t>
-        </is>
-      </c>
+      <c r="K414" s="1" t="inlineStr"/>
       <c r="L414" s="1" t="inlineStr"/>
       <c r="M414" s="1" t="inlineStr"/>
       <c r="N414" s="1" t="inlineStr"/>
@@ -18583,11 +16179,7 @@
       <c r="H415" s="1" t="inlineStr"/>
       <c r="I415" s="1" t="inlineStr"/>
       <c r="J415" s="1" t="inlineStr"/>
-      <c r="K415" s="1" t="inlineStr">
-        <is>
-          <t>L2020: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©tÃ© tout trempÃ© du sang des chrÃ©tiens,</t>
-        </is>
-      </c>
+      <c r="K415" s="1" t="inlineStr"/>
       <c r="L415" s="1" t="inlineStr"/>
       <c r="M415" s="1" t="inlineStr"/>
       <c r="N415" s="1" t="inlineStr"/>
@@ -18618,11 +16210,7 @@
       <c r="H416" s="1" t="inlineStr"/>
       <c r="I416" s="1" t="inlineStr"/>
       <c r="J416" s="1" t="inlineStr"/>
-      <c r="K416" s="1" t="inlineStr">
-        <is>
-          <t>L2023: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: "victimes", quelquefois mÃªme trÃ¨s di-</t>
-        </is>
-      </c>
+      <c r="K416" s="1" t="inlineStr"/>
       <c r="L416" s="1" t="inlineStr"/>
       <c r="M416" s="1" t="inlineStr"/>
       <c r="N416" s="1" t="inlineStr"/>
@@ -18653,11 +16241,7 @@
       <c r="H417" s="1" t="inlineStr"/>
       <c r="I417" s="1" t="inlineStr"/>
       <c r="J417" s="1" t="inlineStr"/>
-      <c r="K417" s="1" t="inlineStr">
-        <is>
-          <t>L2024: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnes de pitiÃ©; mais la vÃ©ritÃ© seule a des</t>
-        </is>
-      </c>
+      <c r="K417" s="1" t="inlineStr"/>
       <c r="L417" s="1" t="inlineStr"/>
       <c r="M417" s="1" t="inlineStr"/>
       <c r="N417" s="1" t="inlineStr"/>
@@ -18688,11 +16272,7 @@
       <c r="H418" s="1" t="inlineStr"/>
       <c r="I418" s="1" t="inlineStr"/>
       <c r="J418" s="1" t="inlineStr"/>
-      <c r="K418" s="1" t="inlineStr">
-        <is>
-          <t>L2025: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: "martyrs". Ainsi l'ont entendu les PÃ¨-</t>
-        </is>
-      </c>
+      <c r="K418" s="1" t="inlineStr"/>
       <c r="L418" s="1" t="inlineStr"/>
       <c r="M418" s="1" t="inlineStr"/>
       <c r="N418" s="1" t="inlineStr"/>
@@ -18723,11 +16303,7 @@
       <c r="H419" s="1" t="inlineStr"/>
       <c r="I419" s="1" t="inlineStr"/>
       <c r="J419" s="1" t="inlineStr"/>
-      <c r="K419" s="1" t="inlineStr">
-        <is>
-          <t>L2031: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: diens franÃ§ais attirÃ©s par les dÃ©couver-</t>
-        </is>
-      </c>
+      <c r="K419" s="1" t="inlineStr"/>
       <c r="L419" s="1" t="inlineStr"/>
       <c r="M419" s="1" t="inlineStr"/>
       <c r="N419" s="1" t="inlineStr"/>
@@ -18758,11 +16334,7 @@
       <c r="H420" s="1" t="inlineStr"/>
       <c r="I420" s="1" t="inlineStr"/>
       <c r="J420" s="1" t="inlineStr"/>
-      <c r="K420" s="1" t="inlineStr">
-        <is>
-          <t>L2033: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gnala en fondant une agence de goÃ©let-</t>
-        </is>
-      </c>
+      <c r="K420" s="1" t="inlineStr"/>
       <c r="L420" s="1" t="inlineStr"/>
       <c r="M420" s="1" t="inlineStr"/>
       <c r="N420" s="1" t="inlineStr"/>
@@ -18793,11 +16365,7 @@
       <c r="H421" s="1" t="inlineStr"/>
       <c r="I421" s="1" t="inlineStr"/>
       <c r="J421" s="1" t="inlineStr"/>
-      <c r="K421" s="1" t="inlineStr">
-        <is>
-          <t>L2036: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: compagnie de son frÃ¨re, Prudent, il or-</t>
-        </is>
-      </c>
+      <c r="K421" s="1" t="inlineStr"/>
       <c r="L421" s="1" t="inlineStr"/>
       <c r="M421" s="1" t="inlineStr"/>
       <c r="N421" s="1" t="inlineStr"/>
@@ -18828,11 +16396,7 @@
       <c r="H422" s="1" t="inlineStr"/>
       <c r="I422" s="1" t="inlineStr"/>
       <c r="J422" s="1" t="inlineStr"/>
-      <c r="K422" s="1" t="inlineStr">
-        <is>
-          <t>L2038: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tion le tenta de nouveau et il Ã©tablit</t>
-        </is>
-      </c>
+      <c r="K422" s="1" t="inlineStr"/>
       <c r="L422" s="1" t="inlineStr"/>
       <c r="M422" s="1" t="inlineStr"/>
       <c r="N422" s="1" t="inlineStr"/>
@@ -18863,11 +16427,7 @@
       <c r="H423" s="1" t="inlineStr"/>
       <c r="I423" s="1" t="inlineStr"/>
       <c r="J423" s="1" t="inlineStr"/>
-      <c r="K423" s="1" t="inlineStr">
-        <is>
-          <t>L2041: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Los Angeles deux annÃ©es plus tard. La</t>
-        </is>
-      </c>
+      <c r="K423" s="1" t="inlineStr"/>
       <c r="L423" s="1" t="inlineStr"/>
       <c r="M423" s="1" t="inlineStr"/>
       <c r="N423" s="1" t="inlineStr"/>
@@ -18898,11 +16458,7 @@
       <c r="H424" s="1" t="inlineStr"/>
       <c r="I424" s="1" t="inlineStr"/>
       <c r="J424" s="1" t="inlineStr"/>
-      <c r="K424" s="1" t="inlineStr">
-        <is>
-          <t>L2042: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: terrible guerre de sÃ©cession lui permit</t>
-        </is>
-      </c>
+      <c r="K424" s="1" t="inlineStr"/>
       <c r="L424" s="1" t="inlineStr"/>
       <c r="M424" s="1" t="inlineStr"/>
       <c r="N424" s="1" t="inlineStr"/>
@@ -18933,11 +16489,7 @@
       <c r="H425" s="1" t="inlineStr"/>
       <c r="I425" s="1" t="inlineStr"/>
       <c r="J425" s="1" t="inlineStr"/>
-      <c r="K425" s="1" t="inlineStr">
-        <is>
-          <t>L2043: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: de jouer un rÃ´le important. Il devint</t>
-        </is>
-      </c>
+      <c r="K425" s="1" t="inlineStr"/>
       <c r="L425" s="1" t="inlineStr"/>
       <c r="M425" s="1" t="inlineStr"/>
       <c r="N425" s="1" t="inlineStr"/>
@@ -18968,11 +16520,7 @@
       <c r="H426" s="1" t="inlineStr"/>
       <c r="I426" s="1" t="inlineStr"/>
       <c r="J426" s="1" t="inlineStr"/>
-      <c r="K426" s="1" t="inlineStr">
-        <is>
-          <t>L2048: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | suspicious token(s): sa1 (letter/digit mix) :: Ã l'Ã¢ge de 77 ans. Cinq ans avant sa1</t>
-        </is>
-      </c>
+      <c r="K426" s="1" t="inlineStr"/>
       <c r="L426" s="1" t="inlineStr"/>
       <c r="M426" s="1" t="inlineStr"/>
       <c r="N426" s="1" t="inlineStr"/>
@@ -19003,11 +16551,7 @@
       <c r="H427" s="1" t="inlineStr"/>
       <c r="I427" s="1" t="inlineStr"/>
       <c r="J427" s="1" t="inlineStr"/>
-      <c r="K427" s="1" t="inlineStr">
-        <is>
-          <t>L2049: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mort les autoritÃ©s avaient donnÃ© le nom :</t>
-        </is>
-      </c>
+      <c r="K427" s="1" t="inlineStr"/>
       <c r="L427" s="1" t="inlineStr"/>
       <c r="M427" s="1" t="inlineStr"/>
       <c r="N427" s="1" t="inlineStr"/>
@@ -19038,11 +16582,7 @@
       <c r="H428" s="1" t="inlineStr"/>
       <c r="I428" s="1" t="inlineStr"/>
       <c r="J428" s="1" t="inlineStr"/>
-      <c r="K428" s="1" t="inlineStr">
-        <is>
-          <t>L2050: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de MÃ©nard Ã l'un des comtÃ©s les plus</t>
-        </is>
-      </c>
+      <c r="K428" s="1" t="inlineStr"/>
       <c r="L428" s="1" t="inlineStr"/>
       <c r="M428" s="1" t="inlineStr"/>
       <c r="N428" s="1" t="inlineStr"/>
@@ -19050,7 +16590,7 @@
       <c r="P428" s="1" t="inlineStr"/>
       <c r="Q428" s="1" t="inlineStr">
         <is>
-          <t>L1272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fernande TieuliÃ©, Legal .................</t>
+          <t>L1272: punctuation artifact: repeated periods :: Fernande Tieulié, Legal .................</t>
         </is>
       </c>
       <c r="R428" s="1" t="inlineStr"/>
@@ -19073,11 +16613,7 @@
       <c r="H429" s="1" t="inlineStr"/>
       <c r="I429" s="1" t="inlineStr"/>
       <c r="J429" s="1" t="inlineStr"/>
-      <c r="K429" s="1" t="inlineStr">
-        <is>
-          <t>L2054: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©e presque lÃ©gendaire jusqu'Ã nos jours.</t>
-        </is>
-      </c>
+      <c r="K429" s="1" t="inlineStr"/>
       <c r="L429" s="1" t="inlineStr"/>
       <c r="M429" s="1" t="inlineStr"/>
       <c r="N429" s="1" t="inlineStr"/>
@@ -19085,7 +16621,7 @@
       <c r="P429" s="1" t="inlineStr"/>
       <c r="Q429" s="1" t="inlineStr">
         <is>
-          <t>L1274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Guy Tessier, Ã©cole Grandin ..............</t>
+          <t>L1274: punctuation artifact: repeated periods :: Guy Tessier, école Grandin ..............</t>
         </is>
       </c>
       <c r="R429" s="1" t="inlineStr"/>
@@ -19108,11 +16644,7 @@
       <c r="H430" s="1" t="inlineStr"/>
       <c r="I430" s="1" t="inlineStr"/>
       <c r="J430" s="1" t="inlineStr"/>
-      <c r="K430" s="1" t="inlineStr">
-        <is>
-          <t>L2056: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Parkman a dÃ©signÃ© Pierre MÃ©nard</t>
-        </is>
-      </c>
+      <c r="K430" s="1" t="inlineStr"/>
       <c r="L430" s="1" t="inlineStr"/>
       <c r="M430" s="1" t="inlineStr"/>
       <c r="N430" s="1" t="inlineStr"/>
@@ -19120,7 +16652,7 @@
       <c r="P430" s="1" t="inlineStr"/>
       <c r="Q430" s="1" t="inlineStr">
         <is>
-          <t>L1276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Jacques Voyer, Ã©cole Thibeault .........</t>
+          <t>L1276: punctuation artifact: repeated periods :: Jacques Voyer, école Thibeault .........</t>
         </is>
       </c>
       <c r="R430" s="1" t="inlineStr"/>
@@ -19143,11 +16675,7 @@
       <c r="H431" s="1" t="inlineStr"/>
       <c r="I431" s="1" t="inlineStr"/>
       <c r="J431" s="1" t="inlineStr"/>
-      <c r="K431" s="1" t="inlineStr">
-        <is>
-          <t>L2057: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: comme "le vÃ©nÃ©rable patriarche de lâ€™Il-</t>
-        </is>
-      </c>
+      <c r="K431" s="1" t="inlineStr"/>
       <c r="L431" s="1" t="inlineStr"/>
       <c r="M431" s="1" t="inlineStr"/>
       <c r="N431" s="1" t="inlineStr"/>
@@ -19186,7 +16714,7 @@
       <c r="P432" s="1" t="inlineStr"/>
       <c r="Q432" s="1" t="inlineStr">
         <is>
-          <t>L1280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: BÃ©atrice Hurtubise, Saint-Paul .......</t>
+          <t>L1280: punctuation artifact: repeated periods :: Béatrice Hurtubise, Saint-Paul .......</t>
         </is>
       </c>
       <c r="R432" s="1" t="inlineStr"/>
@@ -19217,7 +16745,7 @@
       <c r="P433" s="1" t="inlineStr"/>
       <c r="Q433" s="1" t="inlineStr">
         <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86 RÃ©al Demers, Beaumont..........................</t>
+          <t>L1292: punctuation artifact: repeated periods :: ...86 Réal Demers, Beaumont..........................</t>
         </is>
       </c>
       <c r="R433" s="1" t="inlineStr"/>
@@ -19248,7 +16776,7 @@
       <c r="P434" s="1" t="inlineStr"/>
       <c r="Q434" s="1" t="inlineStr">
         <is>
-          <t>L1302: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, Ã©cole consolidÃ©e, Donnelly</t>
+          <t>L1302: punctuation artifact: repeated periods :: ...861 Constant Maisonneuve, école consolidée, Donnelly</t>
         </is>
       </c>
       <c r="R434" s="1" t="inlineStr"/>
@@ -19279,7 +16807,7 @@
       <c r="P435" s="1" t="inlineStr"/>
       <c r="Q435" s="1" t="inlineStr">
         <is>
-          <t>L1304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ...86, Roland SÃ©guin, Ã©cole Dunrobin .................</t>
+          <t>L1304: punctuation artifact: repeated periods :: ...86, Roland Séguin, école Dunrobin .................</t>
         </is>
       </c>
       <c r="R435" s="1" t="inlineStr"/>
@@ -19341,7 +16869,7 @@
       <c r="P437" s="1" t="inlineStr"/>
       <c r="Q437" s="1" t="inlineStr">
         <is>
-          <t>L1312: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) :: 86Edouard Garneau, Ã©cole Grandin ..........</t>
+          <t>L1312: punctuation artifact: repeated periods | suspicious token(s): 86Edouard (letter/digit mix) :: 86Edouard Garneau, école Grandin ..........</t>
         </is>
       </c>
       <c r="R437" s="1" t="inlineStr"/>
@@ -19961,7 +17489,7 @@
       <c r="P457" s="1" t="inlineStr"/>
       <c r="Q457" s="1" t="inlineStr">
         <is>
-          <t>L1382: punctuation artifact: repeated periods :: Georgette NoÃ«l, Saint-Paul ...........</t>
+          <t>L1382: punctuation artifact: repeated periods :: Georgette Noël, Saint-Paul ...........</t>
         </is>
       </c>
       <c r="R457" s="1" t="inlineStr"/>
@@ -20054,7 +17582,7 @@
       <c r="P460" s="1" t="inlineStr"/>
       <c r="Q460" s="1" t="inlineStr">
         <is>
-          <t>L1394: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: : HÃ©lÃ¨ne Normand, ThÃ©rien Village ...............</t>
+          <t>L1394: punctuation artifact: repeated periods :: : Hélène Normand, Thérien Village ...............</t>
         </is>
       </c>
       <c r="R460" s="1" t="inlineStr"/>
@@ -20147,7 +17675,7 @@
       <c r="P463" s="1" t="inlineStr"/>
       <c r="Q463" s="1" t="inlineStr">
         <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Maurier, Legal ...........................</t>
+          <t>L1410: punctuation artifact: repeated periods :: René Maurier, Legal ...........................</t>
         </is>
       </c>
       <c r="R463" s="1" t="inlineStr"/>
@@ -20178,7 +17706,7 @@
       <c r="P464" s="1" t="inlineStr"/>
       <c r="Q464" s="1" t="inlineStr">
         <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ© La Brie, Fort Kent .................</t>
+          <t>L1416: punctuation artifact: repeated periods :: André La Brie, Fort Kent .................</t>
         </is>
       </c>
       <c r="R464" s="1" t="inlineStr"/>
@@ -20395,7 +17923,7 @@
       <c r="P471" s="1" t="inlineStr"/>
       <c r="Q471" s="1" t="inlineStr">
         <is>
-          <t>L1442: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Claire Petersen, Ã©cole Grandin ................</t>
+          <t>L1442: punctuation artifact: repeated periods :: Claire Petersen, école Grandin ................</t>
         </is>
       </c>
       <c r="R471" s="1" t="inlineStr"/>
@@ -20426,7 +17954,7 @@
       <c r="P472" s="1" t="inlineStr"/>
       <c r="Q472" s="1" t="inlineStr">
         <is>
-          <t>L1450: punctuation artifact: repeated periods :: NoÃ«l Gour, Bonnyville ......................</t>
+          <t>L1450: punctuation artifact: repeated periods :: Noël Gour, Bonnyville ......................</t>
         </is>
       </c>
       <c r="R472" s="1" t="inlineStr"/>
@@ -20457,7 +17985,7 @@
       <c r="P473" s="1" t="inlineStr"/>
       <c r="Q473" s="1" t="inlineStr">
         <is>
-          <t>L1452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Billy Dubois, Ã©cole Dunrobin ..............</t>
+          <t>L1452: punctuation artifact: repeated periods :: Billy Dubois, école Dunrobin ..............</t>
         </is>
       </c>
       <c r="R473" s="1" t="inlineStr"/>
@@ -20550,7 +18078,7 @@
       <c r="P476" s="1" t="inlineStr"/>
       <c r="Q476" s="1" t="inlineStr">
         <is>
-          <t>L1482: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©onard Rousseau, Ã©cole Thibeault ...........</t>
+          <t>L1482: punctuation artifact: repeated periods :: Léonard Rousseau, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R476" s="1" t="inlineStr"/>
@@ -20581,7 +18109,7 @@
       <c r="P477" s="1" t="inlineStr"/>
       <c r="Q477" s="1" t="inlineStr">
         <is>
-          <t>L1484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Charles Ouellette, ThÃ©rien Village ..........</t>
+          <t>L1484: punctuation artifact: repeated periods :: Charles Ouellette, Thérien Village ..........</t>
         </is>
       </c>
       <c r="R477" s="1" t="inlineStr"/>
@@ -20612,7 +18140,7 @@
       <c r="P478" s="1" t="inlineStr"/>
       <c r="Q478" s="1" t="inlineStr">
         <is>
-          <t>L1488: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gagnon, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L1488: punctuation artifact: repeated periods :: Lucien Gagnon, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R478" s="1" t="inlineStr"/>
@@ -20643,7 +18171,7 @@
       <c r="P479" s="1" t="inlineStr"/>
       <c r="Q479" s="1" t="inlineStr">
         <is>
-          <t>L1490: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Annette Lessard, Ã©cole consolidÃ©e, Falher ...</t>
+          <t>L1490: punctuation artifact: repeated periods :: Annette Lessard, école consolidée, Falher ...</t>
         </is>
       </c>
       <c r="R479" s="1" t="inlineStr"/>
@@ -20736,7 +18264,7 @@
       <c r="P482" s="1" t="inlineStr"/>
       <c r="Q482" s="1" t="inlineStr">
         <is>
-          <t>L1496: punctuation artifact: repeated periods :: FranÃ§oise Lissenden, Saint-Paul .............</t>
+          <t>L1496: punctuation artifact: repeated periods :: Françoise Lissenden, Saint-Paul .............</t>
         </is>
       </c>
       <c r="R482" s="1" t="inlineStr"/>
@@ -20767,7 +18295,7 @@
       <c r="P483" s="1" t="inlineStr"/>
       <c r="Q483" s="1" t="inlineStr">
         <is>
-          <t>L1498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lilianne Doran, Ã©cole consolidÃ©e, Falher ....</t>
+          <t>L1498: punctuation artifact: repeated periods :: Lilianne Doran, école consolidée, Falher ....</t>
         </is>
       </c>
       <c r="R483" s="1" t="inlineStr"/>
@@ -20829,7 +18357,7 @@
       <c r="P485" s="1" t="inlineStr"/>
       <c r="Q485" s="1" t="inlineStr">
         <is>
-          <t>L1502: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se ChÃ©nard. Tangente ...................</t>
+          <t>L1502: punctuation artifact: repeated periods :: Thérèse Chénard. Tangente ...................</t>
         </is>
       </c>
       <c r="R485" s="1" t="inlineStr"/>
@@ -20860,7 +18388,7 @@
       <c r="P486" s="1" t="inlineStr"/>
       <c r="Q486" s="1" t="inlineStr">
         <is>
-          <t>L1505: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Fortin, Tangente..................</t>
+          <t>L1505: punctuation artifact: repeated periods :: René Fortin, Tangente..................</t>
         </is>
       </c>
       <c r="R486" s="1" t="inlineStr"/>
@@ -20922,7 +18450,7 @@
       <c r="P488" s="1" t="inlineStr"/>
       <c r="Q488" s="1" t="inlineStr">
         <is>
-          <t>L1513: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Michel Voyer, Ã©cole Grandin ................</t>
+          <t>L1513: punctuation artifact: repeated periods :: Michel Voyer, école Grandin ................</t>
         </is>
       </c>
       <c r="R488" s="1" t="inlineStr"/>
@@ -20953,7 +18481,7 @@
       <c r="P489" s="1" t="inlineStr"/>
       <c r="Q489" s="1" t="inlineStr">
         <is>
-          <t>L1515: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o BÃ©dard, Tangente .....................</t>
+          <t>L1515: punctuation artifact: repeated periods :: Roméo Bédard, Tangente .....................</t>
         </is>
       </c>
       <c r="R489" s="1" t="inlineStr"/>
@@ -21666,7 +19194,7 @@
       <c r="P512" s="1" t="inlineStr"/>
       <c r="Q512" s="1" t="inlineStr">
         <is>
-          <t>L1569: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lorraine BÃ©rubÃ©. Beaumont .......................</t>
+          <t>L1569: punctuation artifact: repeated periods :: Lorraine Bérubé. Beaumont .......................</t>
         </is>
       </c>
       <c r="R512" s="1" t="inlineStr"/>
@@ -21697,7 +19225,7 @@
       <c r="P513" s="1" t="inlineStr"/>
       <c r="Q513" s="1" t="inlineStr">
         <is>
-          <t>L1571: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Alberta LabontÃ©, Ã©cole Thibeault ................</t>
+          <t>L1571: punctuation artifact: repeated periods :: Alberta Labonté, école Thibeault ................</t>
         </is>
       </c>
       <c r="R513" s="1" t="inlineStr"/>
@@ -21728,7 +19256,7 @@
       <c r="P514" s="1" t="inlineStr"/>
       <c r="Q514" s="1" t="inlineStr">
         <is>
-          <t>L1573: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Fleurette Rousseau, Ã©cole Thibeault .............</t>
+          <t>L1573: punctuation artifact: repeated periods :: Fleurette Rousseau, école Thibeault .............</t>
         </is>
       </c>
       <c r="R514" s="1" t="inlineStr"/>
@@ -21790,7 +19318,7 @@
       <c r="P516" s="1" t="inlineStr"/>
       <c r="Q516" s="1" t="inlineStr">
         <is>
-          <t>L1577: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©ontine Aubin, Ã©cole consolidÃ©e, Falher ........</t>
+          <t>L1577: punctuation artifact: repeated periods :: Léontine Aubin, école consolidée, Falher ........</t>
         </is>
       </c>
       <c r="R516" s="1" t="inlineStr"/>
@@ -21914,7 +19442,7 @@
       <c r="P520" s="1" t="inlineStr"/>
       <c r="Q520" s="1" t="inlineStr">
         <is>
-          <t>L1585: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: OrigÃ¨ne Caouette, Bonnyville ....................</t>
+          <t>L1585: punctuation artifact: repeated periods :: Origène Caouette, Bonnyville ....................</t>
         </is>
       </c>
       <c r="R520" s="1" t="inlineStr"/>
@@ -21945,7 +19473,7 @@
       <c r="P521" s="1" t="inlineStr"/>
       <c r="Q521" s="1" t="inlineStr">
         <is>
-          <t>L1587: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Etiennette SÃ©guin, Bonnyville ...................</t>
+          <t>L1587: punctuation artifact: repeated periods :: Etiennette Séguin, Bonnyville ...................</t>
         </is>
       </c>
       <c r="R521" s="1" t="inlineStr"/>
@@ -22007,7 +19535,7 @@
       <c r="P523" s="1" t="inlineStr"/>
       <c r="Q523" s="1" t="inlineStr">
         <is>
-          <t>L1591: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ©e Meunier Ã©cole Thibeault ...................</t>
+          <t>L1591: punctuation artifact: repeated periods :: Renée Meunier école Thibeault ...................</t>
         </is>
       </c>
       <c r="R523" s="1" t="inlineStr"/>
@@ -22038,7 +19566,7 @@
       <c r="P524" s="1" t="inlineStr"/>
       <c r="Q524" s="1" t="inlineStr">
         <is>
-          <t>L1593: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: LÃ©vis Chiasson, Sainte-Lina .....................</t>
+          <t>L1593: punctuation artifact: repeated periods :: Lévis Chiasson, Sainte-Lina .....................</t>
         </is>
       </c>
       <c r="R524" s="1" t="inlineStr"/>
@@ -22069,7 +19597,7 @@
       <c r="P525" s="1" t="inlineStr"/>
       <c r="Q525" s="1" t="inlineStr">
         <is>
-          <t>L1595: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marcel Legris, Ã©cole Grandin ....................</t>
+          <t>L1595: punctuation artifact: repeated periods :: Marcel Legris, école Grandin ....................</t>
         </is>
       </c>
       <c r="R525" s="1" t="inlineStr"/>
@@ -22162,7 +19690,7 @@
       <c r="P528" s="1" t="inlineStr"/>
       <c r="Q528" s="1" t="inlineStr">
         <is>
-          <t>L1601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, ThÃ©rien ...................</t>
+          <t>L1601: punctuation artifact: repeated periods :: 64 Rose-Marie Aubert, Thérien ...................</t>
         </is>
       </c>
       <c r="R528" s="1" t="inlineStr"/>
@@ -22193,7 +19721,7 @@
       <c r="P529" s="1" t="inlineStr"/>
       <c r="Q529" s="1" t="inlineStr">
         <is>
-          <t>L1603: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ,ThÃ©rÃ¨se Rochette. Tangente.................</t>
+          <t>L1603: punctuation artifact: repeated periods :: ,Thérèse Rochette. Tangente.................</t>
         </is>
       </c>
       <c r="R529" s="1" t="inlineStr"/>
@@ -22224,7 +19752,7 @@
       <c r="P530" s="1" t="inlineStr"/>
       <c r="Q530" s="1" t="inlineStr">
         <is>
-          <t>L1605: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Lussier, Tangente......................</t>
+          <t>L1605: punctuation artifact: repeated periods :: René Lussier, Tangente......................</t>
         </is>
       </c>
       <c r="R530" s="1" t="inlineStr"/>
@@ -22286,7 +19814,7 @@
       <c r="P532" s="1" t="inlineStr"/>
       <c r="Q532" s="1" t="inlineStr">
         <is>
-          <t>L1609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ;ThÃ©rÃ¨se Gauthier, Plamondon................</t>
+          <t>L1609: punctuation artifact: repeated periods :: ;Thérèse Gauthier, Plamondon................</t>
         </is>
       </c>
       <c r="R532" s="1" t="inlineStr"/>
@@ -22348,7 +19876,7 @@
       <c r="P534" s="1" t="inlineStr"/>
       <c r="Q534" s="1" t="inlineStr">
         <is>
-          <t>L1613: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Elise Chartrand, Ã©cole Grandin .............</t>
+          <t>L1613: punctuation artifact: repeated periods :: Elise Chartrand, école Grandin .............</t>
         </is>
       </c>
       <c r="R534" s="1" t="inlineStr"/>
@@ -22379,7 +19907,7 @@
       <c r="P535" s="1" t="inlineStr"/>
       <c r="Q535" s="1" t="inlineStr">
         <is>
-          <t>L1615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RomÃ©o Dechaine, Sainte-Lina ................</t>
+          <t>L1615: punctuation artifact: repeated periods :: Roméo Dechaine, Sainte-Lina ................</t>
         </is>
       </c>
       <c r="R535" s="1" t="inlineStr"/>
@@ -22410,7 +19938,7 @@
       <c r="P536" s="1" t="inlineStr"/>
       <c r="Q536" s="1" t="inlineStr">
         <is>
-          <t>L1617: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS | punctuation artifact: repeated periods :: ThÃ©rÃ¨se Bouchard, Tangente .................</t>
+          <t>L1617: punctuation artifact: repeated periods :: Thérèse Bouchard, Tangente .................</t>
         </is>
       </c>
       <c r="R536" s="1" t="inlineStr"/>
@@ -22503,7 +20031,7 @@
       <c r="P539" s="1" t="inlineStr"/>
       <c r="Q539" s="1" t="inlineStr">
         <is>
-          <t>L1623: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | punctuation artifact: repeated periods :: Laurier CarriÃ¨re, Legal ....................</t>
+          <t>L1623: punctuation artifact: repeated periods :: Laurier Carrière, Legal ....................</t>
         </is>
       </c>
       <c r="R539" s="1" t="inlineStr"/>
@@ -22596,7 +20124,7 @@
       <c r="P542" s="1" t="inlineStr"/>
       <c r="Q542" s="1" t="inlineStr">
         <is>
-          <t>L1629: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Laurette Lafond, Ã©cole Thibeault ...........</t>
+          <t>L1629: punctuation artifact: repeated periods :: Laurette Lafond, école Thibeault ...........</t>
         </is>
       </c>
       <c r="R542" s="1" t="inlineStr"/>
@@ -22627,7 +20155,7 @@
       <c r="P543" s="1" t="inlineStr"/>
       <c r="Q543" s="1" t="inlineStr">
         <is>
-          <t>L1631: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Doreen Stelte, Ã©cole Thibeault .............</t>
+          <t>L1631: punctuation artifact: repeated periods :: Doreen Stelte, école Thibeault .............</t>
         </is>
       </c>
       <c r="R543" s="1" t="inlineStr"/>
@@ -22689,7 +20217,7 @@
       <c r="P545" s="1" t="inlineStr"/>
       <c r="Q545" s="1" t="inlineStr">
         <is>
-          <t>L1635: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RenÃ© Magant, Sainte-Lina ......-</t>
+          <t>L1635: punctuation artifact: repeated periods :: René Magant, Sainte-Lina ......-</t>
         </is>
       </c>
       <c r="R545" s="1" t="inlineStr"/>
@@ -22813,7 +20341,7 @@
       <c r="P549" s="1" t="inlineStr"/>
       <c r="Q549" s="1" t="inlineStr">
         <is>
-          <t>L1643: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: RÃ©jeanne Rochette, Tangente ................</t>
+          <t>L1643: punctuation artifact: repeated periods :: Réjeanne Rochette, Tangente ................</t>
         </is>
       </c>
       <c r="R549" s="1" t="inlineStr"/>
@@ -22844,7 +20372,7 @@
       <c r="P550" s="1" t="inlineStr"/>
       <c r="Q550" s="1" t="inlineStr">
         <is>
-          <t>L1645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: Rachel Ouellette, Tangente .............â€”...</t>
+          <t>L1645: punctuation artifact: repeated periods :: Rachel Ouellette, Tangente .............—...</t>
         </is>
       </c>
       <c r="R550" s="1" t="inlineStr"/>
@@ -22875,7 +20403,7 @@
       <c r="P551" s="1" t="inlineStr"/>
       <c r="Q551" s="1" t="inlineStr">
         <is>
-          <t>L1651: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Marc Voyer, Ã©cole Grandin ..................</t>
+          <t>L1651: punctuation artifact: repeated periods :: Marc Voyer, école Grandin ..................</t>
         </is>
       </c>
       <c r="R551" s="1" t="inlineStr"/>
@@ -22937,7 +20465,7 @@
       <c r="P553" s="1" t="inlineStr"/>
       <c r="Q553" s="1" t="inlineStr">
         <is>
-          <t>L1661: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Denise Despins, Ã©cole Dunrobin ..........................</t>
+          <t>L1661: punctuation artifact: repeated periods :: Denise Despins, école Dunrobin ..........................</t>
         </is>
       </c>
       <c r="R553" s="1" t="inlineStr"/>
@@ -22968,7 +20496,7 @@
       <c r="P554" s="1" t="inlineStr"/>
       <c r="Q554" s="1" t="inlineStr">
         <is>
-          <t>L1663: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: 82 Antonia Villeneuve, Ã©cole consolidÃ©e, Falher ........</t>
+          <t>L1663: punctuation artifact: repeated periods :: 82 Antonia Villeneuve, école consolidée, Falher ........</t>
         </is>
       </c>
       <c r="R554" s="1" t="inlineStr"/>
@@ -23061,7 +20589,7 @@
       <c r="P557" s="1" t="inlineStr"/>
       <c r="Q557" s="1" t="inlineStr">
         <is>
-          <t>L1671: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Diane Ouellette, Ã©cole consolidÃ©e, Donnelly .............</t>
+          <t>L1671: punctuation artifact: repeated periods :: Diane Ouellette, école consolidée, Donnelly .............</t>
         </is>
       </c>
       <c r="R557" s="1" t="inlineStr"/>
@@ -23154,7 +20682,7 @@
       <c r="P560" s="1" t="inlineStr"/>
       <c r="Q560" s="1" t="inlineStr">
         <is>
-          <t>L1678: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: ....85 Denise Plaquin, ThÃ©rien:</t>
+          <t>L1678: punctuation artifact: repeated periods :: ....85 Denise Plaquin, Thérien:</t>
         </is>
       </c>
       <c r="R560" s="1" t="inlineStr"/>
@@ -23216,7 +20744,7 @@
       <c r="P562" s="1" t="inlineStr"/>
       <c r="Q562" s="1" t="inlineStr">
         <is>
-          <t>L1694: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: AndrÃ©a Trudel, Saint-Paul ................</t>
+          <t>L1694: punctuation artifact: repeated periods :: Andréa Trudel, Saint-Paul ................</t>
         </is>
       </c>
       <c r="R562" s="1" t="inlineStr"/>
@@ -23278,7 +20806,7 @@
       <c r="P564" s="1" t="inlineStr"/>
       <c r="Q564" s="1" t="inlineStr">
         <is>
-          <t>L1698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Emile Isabel, Ã©cole consolidÃ©e, Falher ..</t>
+          <t>L1698: punctuation artifact: repeated periods :: Emile Isabel, école consolidée, Falher ..</t>
         </is>
       </c>
       <c r="R564" s="1" t="inlineStr"/>
@@ -23340,7 +20868,7 @@
       <c r="P566" s="1" t="inlineStr"/>
       <c r="Q566" s="1" t="inlineStr">
         <is>
-          <t>L1702: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Gratton, ThÃ©rien Village .........</t>
+          <t>L1702: punctuation artifact: repeated periods :: Lucien Gratton, Thérien Village .........</t>
         </is>
       </c>
       <c r="R566" s="1" t="inlineStr"/>
@@ -23433,7 +20961,7 @@
       <c r="P569" s="1" t="inlineStr"/>
       <c r="Q569" s="1" t="inlineStr">
         <is>
-          <t>L1712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: repeated periods :: Lucien Roy, Ã©cole consolidÃ©e, Falher .....</t>
+          <t>L1712: punctuation artifact: repeated periods :: Lucien Roy, école consolidée, Falher .....</t>
         </is>
       </c>
       <c r="R569" s="1" t="inlineStr"/>
@@ -23619,7 +21147,7 @@
       <c r="P575" s="1" t="inlineStr"/>
       <c r="Q575" s="1" t="inlineStr">
         <is>
-          <t>L1803: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme dÃ©ca--</t>
+          <t>L1803: punctuation artifact: double/multiple hyphen :: tableau qui comportait un homme déca--</t>
         </is>
       </c>
       <c r="R575" s="1" t="inlineStr"/>
@@ -23650,7 +21178,7 @@
       <c r="P576" s="1" t="inlineStr"/>
       <c r="Q576" s="1" t="inlineStr">
         <is>
-          <t>L1929: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT, U+20AC EURO SIGN | punctuation artifact: repeated periods :: la fonte des mine- lÃ©e Ã devenir l'entrepÃ´t des produits du ..........__â€ž</t>
+          <t>L1929: punctuation artifact: repeated periods :: la fonte des mine- lée à devenir l'entrepôt des produits du ..........__„</t>
         </is>
       </c>
       <c r="R576" s="1" t="inlineStr"/>
